--- a/CGB_HVT_199-396_bespoke.xlsx
+++ b/CGB_HVT_199-396_bespoke.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="HVT 199-396" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Read me" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Voice audit" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HVT 199-396'!$A$1:$M$199</definedName>
@@ -450,13 +450,13 @@
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="92" customWidth="1" min="10" max="10"/>
+    <col width="94" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -555,16 +555,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Dr. Rodrigue — an EdD in a CISO seat is an unusual combination. My question is on the education side: does a K-5 financial literacy book plus free toolkit fit anything your organization touches?</t>
+          <t>Hi Tiina. An EdD in a CISO seat is an unusual combination. My question is on the education side: does a K-5 financial literacy book plus free toolkit fit anything your organization touches?</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -600,16 +600,16 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>Jennifer — your work with financial institutions and external affairs is where a fundable K-5 program would need a champion. Mine comes with a grant-ready packet built for bank and CRA sponsorship. Where might it fit?</t>
+          <t>Jennifer, your work with financial institutions and external affairs is where a fundable K-5 program would need a champion. Mine comes with a grant-ready packet built for bank and CRA sponsorship. Where might it fit?</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -645,16 +645,16 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Leslie — consumer markets work is upstream of everything my book teaches: comparison, price transparency, what the register adds. Mine is the six-year-old version. Where might something like this fit?</t>
+          <t>Leslie. Consumer markets work is upstream of everything my book teaches: comparison, price transparency, what the register adds. Mine is the six-year-old version. If it's a no, no reply needed.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -690,7 +690,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -780,20 +780,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Zero-prep K-5 resource</t>
         </is>
       </c>
       <c r="I7" s="3" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>Kathryn — a checkable claim for a personal finance desk: every children's money book teaches saving. I read all 25 on the ABA Foundation's list to be sure. None teaches spending, which is the transaction a six-year-old actually performs. I wrote the one that does, sales tax included. Story, or a better contact?</t>
+          <t>Kathryn — a checkable claim for a personal finance desk: every children's money book teaches saving. I read all 25 on the ABA Foundation's list to be sure. None teaches spending, which is the transaction a six-year-old actually performs. I wrote the one that does, sales tax included. Story, or point me elsewhere?</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -829,20 +829,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>The kids' money book with no piggy bank</t>
+          <t>A fundable K-5 resource</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>248</v>
+        <v>218</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Mike — you write for people building habits right now. Mine starts them at six and skips saving entirely: one purchase, sale ad to register, including the moment the kid learns sales tax exists. Is there a story in what kids' money books leave out?</t>
+          <t>Mike, you write for people building habits right now. Mine starts them at six and skips saving entirely: one purchase, sale ad to register, including the moment the kid learns sales tax exists. One line back is plenty.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -878,20 +878,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>Same kid, different approach</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>252</v>
+        <v>218</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Pete — a small odd fact you may be able to use: I wrote a children's picture book in which a six-year-old pays sales tax and asks where the money went. I can't find another kids' book that does it. Is that a story, or just a strange thing to have made?</t>
+          <t>Pete, a small odd fact you may be able to use: I wrote a children's picture book in which a six-year-old pays sales tax and asks where the money went. I can't find another kids' book that does it. Happy to send a copy.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -927,20 +927,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>A checkable claim about children's money books</t>
+          <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Liz — a kids' money book with no piggy bank in it, on purpose. It teaches spending: comparison, markdowns, coupons, sales tax. Ages 6-10. I think the story is the forty-year gap in the category rather than my book. Interested, or a better contact?</t>
+          <t>Liz — a kids' money book with no piggy bank in it, on purpose. It teaches spending: comparison, markdowns, coupons, sales tax. Ages 6-10. I think the story is the forty-year gap in the category rather than my book. Interested, or is there a better name?</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -976,20 +976,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Does this claim hold?</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Kerri Anne — you know a story beats a lecture, which is the whole design here. A six-year-old runs one real purchase and picks the cheaper older model on purpose. No saving lesson anywhere in it. Is there something here for you?</t>
+          <t>Kerri Anne: you know a story beats a lecture, which is the whole design here. A six-year-old runs one real purchase and picks the cheaper older model on purpose. No saving lesson anywhere in it. I'll post one if it's useful.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1025,20 +1025,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>The kids' money book with no piggy bank</t>
+          <t>A gap in kids' money books</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Leslie — as a personal finance editor you decide what earns a reader's time. My angle: children's money books are almost entirely about saving, and the skill kids use first is spending. I wrote the counterexample. Worth a look?</t>
+          <t>Hi Leslie. As a personal finance editor you decide what earns a reader's time. My angle: children's money books are almost entirely about saving, and the skill kids use first is spending. I wrote the counterexample. Worth a look?</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1074,20 +1074,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>A listing question</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Jill — a kids' money book that teaches sales tax. A six-year-old gets to the register, the total is higher than the sticker, and he gets an explanation. I don't believe another picture book does it. Is that a story, or a better contact?</t>
+          <t>Jill, a kids' money book that teaches sales tax. A six-year-old gets to the register, the total is higher than the sticker, and he gets an explanation. I don't believe another picture book does it. Say the word and it's in the mail.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1123,20 +1123,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>A checkable claim about children's money books</t>
+          <t>One author to another</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>J.R. — consumer and personal finance is exactly where my book sits, just at reading level 620L. A six-year-old reads a sale ad, compares two models, uses a coupon, pays tax. It's a consumer education in 36 pages. Angle for you?</t>
+          <t>J.R.. Consumer and personal finance is exactly where my book sits, just at reading level 620L. A six-year-old reads a sale ad, compares two models, uses a coupon, pays tax. It's a consumer education in 36 pages. Tell me if it's not a fit.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Would this circulate?</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1221,20 +1221,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>The kids' money book with no piggy bank</t>
+          <t>A premise I'd like tested</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Kelly — a veteran consumer finance journalist will know instantly whether this gap is real. Every children's money book teaches saving; none teaches the transaction. I wrote the one that does. Does that hold up to you?</t>
+          <t>Kelly, a veteran consumer finance journalist will know instantly whether this gap is real. The whole category teaches saving; none teaches the transaction. I wrote the one that does. If it's a no, no reply needed.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1270,20 +1270,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>Zero-prep K-5 resource</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Deborah — a content strategist's question as much as a reporter's: children's financial literacy is 90% saving, and nobody covers spending. I wrote the book filling it. Is the gap itself the story? Happy to send the book either way.</t>
+          <t>Deborah, a content strategist's question as much as a reporter's: children's financial literacy is 90% saving, and nobody covers spending. I wrote the book filling it. Is the gap itself the story? Happy to send the book either way.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1319,20 +1319,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>A checkable claim about children's money books</t>
+          <t>A fundable K-5 resource</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Jessica — a kids' picture book that teaches spending rather than saving, including sales tax at the register. Ages 6-10. I think the interesting part is what forty years of children's money books skipped. Is there something here for you?</t>
+          <t>Jessica — a kids' picture book that skips saving and teaches spending, including sales tax at the register. Ages 6-10. I think the interesting part is what forty years of children's money books skipped. I'd rather hear no than nothing.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1368,20 +1368,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Same kid, different approach</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Rachel — my book teaches six-year-olds the money skill that never gets its own title: spending. One purchase, ad to register. Is there a piece in why children's financial literacy is all piggy banks and no cash registers?</t>
+          <t>Rachel: my book teaches six-year-olds the money skill that never gets its own title: spending. One purchase, ad to register. Is there a piece in why children's financial literacy is all piggy banks and no cash registers?</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1417,20 +1417,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>The kids' money book with no piggy bank</t>
+          <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Venessa — you cover the consumer side. Mine is a consumer origin story: a six-year-old's first real purchase, complete with the discovery that the sticker price isn't the price. 36 pages. Story, or a better name?</t>
+          <t>Hi Venessa. You cover the consumer side. Mine is a consumer origin story: a six-year-old's first real purchase, complete with the discovery that the sticker price isn't the price. 36 pages. Story, or a better name?</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1466,20 +1466,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>Does this claim hold?</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Maureen — far from your usual beat, so I'll be quick. I wrote the only children's picture book I can find that teaches spending rather than saving. If there's someone at the Times who'd want it, I'd take the name.</t>
+          <t>Maureen, far from your usual beat, so I'll be quick. I wrote the only children's picture book I can find that leaves saving to everyone else. If there's someone at the Times who'd want it, I'd take the name.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1515,20 +1515,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>A checkable claim about children's money books</t>
+          <t>A gap in kids' money books</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Suman — a business angle rather than a book pitch: children's financial literacy is a real category with a structural hole in it. Everything teaches saving; nothing teaches the transaction. I wrote the counterexample. Worth a look?</t>
+          <t>Suman. A business angle rather than a book pitch: children's financial literacy is a real category with a structural hole in it. Everything teaches saving; nothing teaches the transaction. I wrote the counterexample. Worth a look?</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>A listing question</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Christine — you cover finance in Canada. My claim is portable: no children's picture book teaches the complete purchase, through the register, including sales tax. Mine does. Is there a story in the omission?</t>
+          <t>Christine — you cover finance in Canada. My claim is portable: no children's picture book teaches the complete purchase, through the register, including sales tax. Mine does. No pitch after this one, promise.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1613,20 +1613,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>The kids' money book with no piggy bank</t>
+          <t>One author to another</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Megan — a money desk fact you might enjoy: my children's picture book teaches sales tax. The six-year-old pays it, notices, and asks. Everything else in the category stops at saving. Story, or a better contact?</t>
+          <t>Megan, a money desk fact you might enjoy: my children's picture book teaches sales tax. The six-year-old pays it, notices, and asks. Everything else in the category stops at saving. Ignore me if it's wrong for you.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1662,20 +1662,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>Would this circulate?</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Barbara — well off your beat, so briefly. I wrote a children's book that teaches spending rather than saving, and I think the story is what the category has ignored. If there's a colleague who covers consumer or family money, I'd take the name.</t>
+          <t>Barbara, well off your beat, so briefly. I wrote a children's book that skips saving entirely, and I think the story is what the category has ignored. If there's a colleague who covers consumer or family money, I'd take the name.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1711,20 +1711,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>A checkable claim about children's money books</t>
+          <t>A premise I'd like tested</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Mike — a local-interest angle: an attorney wrote and illustrated a children's book that teaches kids to shop, including sales tax at the register. It's the only one I can find that does. Segment, or not your desk?</t>
+          <t>Mike — a local-interest angle: an attorney wrote and illustrated a children's book that teaches kids to shop, including sales tax at the register. It's the only one I can find that does. One copy, no follow-up, your call.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -1760,20 +1760,20 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Does this claim hold?</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Damilola — you hold the CFEI and write personal finance, so you'll test the premise. Mine: spending competence precedes saving competence, and the category has the sequence backwards. Does that hold?</t>
+          <t>Damilola — you hold the CFEI and write personal finance, so you'll test the premise. Mine: spending competence precedes saving competence, and the category has the sequence backwards. There's a copy with your name on it.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -1809,20 +1809,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>The kids' money book with no piggy bank</t>
+          <t>A gap in kids' money books</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Marc — you write about investing for people well past first grade. Mine starts at six with the skill that comes before any of it: spending deliberately. Is there an angle for your readers?</t>
+          <t>Marc, you write about investing for people well past first grade. Mine starts at six with the skill that comes before any of it: spending deliberately. Is there an angle for your readers?</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -1858,20 +1858,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>A listing question</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Robin — a data point rather than a pitch: I checked the ABA Foundation's 25-title children's financial literacy list. Every one teaches earning, saving, or investing. None teaches spending. That gap seemed worth a book. Worth a story?</t>
+          <t>Robin, a data point rather than a pitch: I checked the ABA Foundation's 25-title children's financial literacy list. Every one teaches earning, saving, or investing. None teaches spending. That gap seemed worth a book. Take a look or don't; either is fine.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -1907,20 +1907,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>A checkable claim about children's money books</t>
+          <t>One author to another</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Rui — a children's picture book that teaches the complete purchase, including sales tax, which appears to be unique in the category. Ages 6-10. Is there something here for you, or a better contact?</t>
+          <t>Rui — a children's picture book that teaches the complete purchase, including sales tax, which appears to be unique in the category. Ages 6-10. I'll send it and get out of your way.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -1956,20 +1956,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Would this circulate?</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Sarah — as a senior editor you'll want the angle first. Mine: children's financial literacy teaches saving almost exclusively, while spending is what kids actually do. I wrote the counterexample. Worth a look?</t>
+          <t>Sarah: as a senior editor you'll want the angle first. Mine: children's financial literacy teaches saving almost exclusively, while spending is what kids actually do. I wrote the counterexample. Worth a look?</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>Zero-prep K-5 resource</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Manisha — your work is about money and wellbeing, and the emotional part starts young. My book meets a six-year-old at the first want in a store aisle and walks him to a decision he makes himself. Does that land for you?</t>
+          <t>Manisha, your work is about money and wellbeing, and the emotional part starts young. My book meets a six-year-old at the first want in a store aisle and walks him to a decision he makes himself. Does that land for you?</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2063,11 +2063,11 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Helen — as deputy editor of On the Money you'll want the angle, not the book. Mine: children's financial literacy is all saving and no spending, and has been for forty years. I wrote the counterexample. Worth a look?</t>
+          <t>Hi Helen. As deputy editor of On the Money you'll want the angle, not the book. Mine: children's financial literacy is all saving and no spending, and has been for forty years. I wrote the counterexample. Happy to be told no.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2103,20 +2103,20 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>A checkable claim about children's money books</t>
+          <t>Does this claim hold?</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Mark — a senior editor's filter. My claim: no children's picture book teaches the complete purchase through the register, sales tax included. I checked the ABA Foundation's 25-title list. Mine is the exception. Story?</t>
+          <t>Mark, a senior editor's filter. My claim: no children's picture book teaches the complete purchase through the register, sales tax included. I checked the ABA Foundation's 25-title list. Mine is the exception. A copy is easy to send.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2152,20 +2152,20 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Zero-prep K-5 resource</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Jason — a feature rather than a finance story: an attorney and mixed-media artist wrote and illustrated a picture book that teaches six-year-olds how to shop, then gave the classroom materials away free. Worth a look?</t>
+          <t>Jason: a feature rather than a finance story: an attorney and mixed-media artist wrote and illustrated a picture book that teaches six-year-olds how to shop, then gave the classroom materials away free. Worth a look?</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2201,20 +2201,20 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>The kids' money book with no piggy bank</t>
+          <t>A fundable K-5 resource</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>187</v>
+        <v>160</v>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Katie — a kids' money book that skips saving entirely. It teaches spending: read the ad, compare, use the coupon, pay the tax. Ages 6-10. Is there a story in the gap, or a better contact?</t>
+          <t>Hi Katie. A kids' money book that skips saving entirely. It teaches spending: read the ad, compare, use the coupon, pay the tax. Ages 6-10. I'll leave it there.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2250,20 +2250,20 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>Same kid, different approach</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>211</v>
+        <v>174</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Josyana — my picture book teaches six-year-olds the complete purchase, sales tax included, which I can't find anywhere else in children's financial literacy. Is that a story for you, or someone else on the desk?</t>
+          <t>Josyana, my picture book teaches six-year-olds one purchase end to end, tax and all, which I can't find anywhere else in children's financial literacy. Shout if you want one.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2299,20 +2299,20 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>A checkable claim about children's money books</t>
+          <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Claire — as a personal finance editor: the claim is that children's money publishing has a spending-shaped hole in it, forty years wide. I wrote the book that fills it. Interested in the gap, or the book, or neither?</t>
+          <t>Claire. As a personal finance editor: the claim is that children's money publishing has a spending-shaped hole in it, forty years wide. I wrote the book that fills it. Interested in the gap, or the book, or neither?</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2348,20 +2348,20 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>The kids' money book with no piggy bank</t>
+          <t>A premise I'd like tested</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Melina — a long way from leveraged finance, so I'll be brief. I wrote a children's book teaching six-year-olds how a purchase actually works, sales tax and all. If a colleague covers consumer or family money, I'd take the name.</t>
+          <t>Hi Melina. A long way from leveraged finance, so I'll be brief. I wrote a children's book teaching six-year-olds how a purchase actually works, sales tax and all. If a colleague covers consumer or family money, I'd take the name.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2397,20 +2397,20 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>A checkable claim about children's money books</t>
+          <t>A fundable K-5 resource</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Danielle — a segment idea: an attorney wrote and illustrated a children's book that teaches kids to shop properly, sales tax included, then gave the lesson plans away free. Would that work for you, or a better producer?</t>
+          <t>Danielle. A segment idea: an attorney wrote and illustrated a children's book that teaches kids to shop properly, sales tax included, then gave the lesson plans away free. Happy to be told no.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2446,20 +2446,20 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Same kid, different approach</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Mark — a producer-level pitch. The hook is one line: every children's money book teaches saving; mine teaches spending, and a six-year-old pays sales tax on camera-friendly page 22. Worth a look, or not your show?</t>
+          <t>Mark — a producer-level pitch. The hook is one line: every children's money book teaches saving; mine teaches spending, and a six-year-old pays sales tax on camera-friendly page 22. A copy is easy to send.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2495,16 +2495,16 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Mark — as a senior editor: children's financial literacy has been all saving for forty years, and nobody teaches the transaction. I wrote the one that does. Is the omission a story?</t>
+          <t>Mark, as a senior editor: children's financial literacy has been all saving for forty years, and nobody teaches the transaction. I wrote the one that does. Is the omission a story?</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -2540,20 +2540,20 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>The kids' money book with no piggy bank</t>
+          <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Alisha — as a reading content editor you'll care about the literacy side as much as the money. Mine is AD 620L, 36 pages, built as a read-along so a kid and a grown-up do it together. Would it fit your coverage?</t>
+          <t>Alisha, as a reading content editor you'll care about the literacy side as much as the money. Mine is AD 620L, 36 pages, built as a read-along so a kid and a grown-up do it together. I'll stop there.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -2589,16 +2589,16 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Brian — a finance reporter's angle rather than a book pitch: children's money publishing skips spending entirely, which is the transaction kids actually perform. I wrote the one that doesn't. Interested, or a better contact?</t>
+          <t>Brian. A finance reporter's angle rather than a book pitch: children's money publishing skips spending entirely, which is the transaction kids actually perform. I wrote the one that doesn't. Interested, or is there a better name?</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -2634,16 +2634,16 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Kellyanne — a children's librarian with an MEd will judge both the story and the teaching. Mine is AD 620L, 36 pages, with a 21-term glossary and page references in the back. Would it circulate at Lake Hiawatha? Happy to send a copy.</t>
+          <t>Kellyanne, a children's librarian with an MEd will judge both the story and the teaching. Mine is AD 620L, 36 pages, with a 21-term glossary and page references in the back. Would it circulate at Lake Hiawatha? Happy to send a copy.</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -2679,16 +2679,16 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Rae Ellyn — as a children's librarian you know which books get picked up twice. Mine is a money book that reads like a story, ages 6-10, glossary in the back. Would it earn shelf space? Glad to send a copy.</t>
+          <t>Rae — as a children's librarian you know which books get picked up twice. Mine is a money book that reads like a story, ages 6-10, glossary in the back. Would it earn shelf space? Glad to send a copy.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -2724,16 +2724,16 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Ashlie — a library director decides what circulates. Mine is a hardbound 36-page picture book teaching K-5 financial literacy, AD 620L, 21-term glossary, ISBN 979-8-234-07638-0, LCCN 2026906164. Would it fit Melrose Park? Happy to send a review copy.</t>
+          <t>Ashlie: a library director decides what circulates. Mine is a hardbound 36-page picture book teaching K-5 financial literacy, AD 620L, 21-term glossary, ISBN 979-8-234-07638-0, LCCN 2026906164. Would it fit Melrose Park? Happy to send a review copy.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -2769,16 +2769,16 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Ramat — FLEX runs K-8 financial education in Pennsylvania schools, which is the exact band and the exact problem. Mine is a K-5 picture book plus free zero-prep lessons aligned to five frameworks. Does it complement FLEX or compete with it?</t>
+          <t>Ramat — FLEX runs K-8 financial education in Pennsylvania schools, which is the exact band and the exact problem. It's a picture book for grades 1-5 plus free zero-prep lessons checked against five frameworks. Does it complement FLEX or compete with it?</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -2814,16 +2814,16 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Alex — a published financial literacy author and educator is the read I want most. Mine argues spending is the first money skill and the category teaches saving instead. As someone who has published in this space, does that hold or is it a marketing line?</t>
+          <t>Alex, a published financial literacy author and educator is the read I want most. Mine argues spending is the first money skill and the category teaches saving instead. As someone who has published in this space, does that hold or is it a marketing line?</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -2859,20 +2859,20 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>One children's author to another</t>
+          <t>A premise I'd like tested</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Lisa — children's author to children's author. My worry is craft, not content: does a 36-page arc about one shopping trip actually hold a young reader? I'd value your read as a writer rather than a subject expert.</t>
+          <t>Hi Lisa. Children's author to children's author. My worry is craft, not content: does a 36-page arc about one shopping trip actually hold a young reader? Would you look? as a writer rather than a subject expert.</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -2908,16 +2908,16 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Kago — you're a relatable financial storyteller, which is exactly what I attempted for six-year-olds. Mine teaches spending through a boy and a robot rather than a lesson. Storyteller to storyteller: does the story carry the teaching, or buckle under it?</t>
+          <t>Kago, you're a relatable financial storyteller, which is exactly what I attempted for six-year-olds. Mine teaches spending through a boy and a robot rather than a lesson. Storyteller to storyteller: does the story carry the teaching, or buckle under it?</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
@@ -2998,16 +2998,16 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Larry — a bestselling author and certified financial instructor covers both halves of what I need judged. Mine teaches the complete purchase to ages 6-10. Does the instruction hold up under the story?</t>
+          <t>Larry: a bestselling author and certified financial instructor covers both halves of what I need judged. Mine teaches the complete purchase to ages 6-10. I'll send it either way.</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3043,16 +3043,16 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Donna — as a KidLit author you'll spot immediately whether the lesson pokes through the story. That's my main fear about my own book. Would you read it and tell me where it shows?</t>
+          <t>Donna, as a KidLit author you'll spot immediately whether the lesson pokes through the story. That's my main fear about my own book. No pitch after this one, promise.</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3088,16 +3088,16 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Ilene — author to author. Mine hides a financial education inside a story about a boy and a robot. Authors are the worst judges of their own subtlety, which is why I'm asking. Would you take a look?</t>
+          <t>Ilene. Author to author. Mine hides a financial education inside a story about a boy and a robot. Authors are the worst judges of their own subtlety, which is why I'm asking. Ignore me if it's wrong for you.</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -3178,16 +3178,16 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Corwin — you coach authors through self-publishing, so you'll see the strategic question: I've deliberately skipped Amazon and sell direct. Brave or dumb? I'd genuinely value the straight answer.</t>
+          <t>Corwin, you coach authors through self-publishing, so you'll see the strategic question: I've deliberately skipped Amazon and sell direct. Brave or dumb? I'd genuinely value the straight answer.</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3223,16 +3223,16 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Cathy — a publishing consultant and bestselling author sees the whole path. My book teaches spending rather than saving, ages 6-10, direct sales only, no Amazon by choice. I'd value your read on positioning something with no shelf-mates.</t>
+          <t>Cathy, a publishing consultant and bestselling author sees the whole path. My book leaves saving to everyone else, ages 6-10, direct sales only, no Amazon by choice. Tell me what you make of positioning something with no shelf-mates.</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3268,16 +3268,16 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Michele — you help independent authors produce books that hold up physically. Mine is hardbound, full color, 11x8.5, 36 pages, and I wrote and illustrated it. I'd value your read on whether the production choices serve it.</t>
+          <t>Michele — you help independent authors produce books that hold up physically. Mine is hardbound, full color, 11x8.5, 36 pages, and I wrote and illustrated it. Tell me whether the production choices serve it.</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -3313,16 +3313,16 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Bill — as a parenting author and speaker you know money is the topic parents dodge. My read-along removes the pressure: the parent reads the story and the lesson does its own work. Would it fit the families you reach?</t>
+          <t>Bill. As a parenting author and speaker you know money is the topic parents dodge. My read-along removes the pressure: the parent reads the story and the lesson does its own work. Would it fit the families you reach?</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -3358,16 +3358,16 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Cara — ECE keynote speaker, author, and teacher trainer is three useful angles at once. Mine is a K-5 read-aloud teaching the first money behavior kids actually perform. Does it fit the age developmentally, or skew old?</t>
+          <t>Cara — ECE keynote speaker, author, and teacher trainer is three useful angles at once. Mine is a K-5 read-aloud teaching the first money behavior kids actually perform. Take a look or don't; either is fine.</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -3403,20 +3403,20 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Author to author</t>
+          <t>A fundable K-5 resource</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Chad — you've built a career on teaching young people what school skips. Mine goes younger than most: six-year-olds, and the skill is spending rather than saving. Does that age band hold a real lesson?</t>
+          <t>Hi Chad. You've built a career on teaching young people what school skips. Mine goes younger than most: six-year-olds, and the skill is spending rather than saving. Does that age band hold a real lesson?</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -3452,20 +3452,20 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>One children's author to another</t>
+          <t>Same kid, different approach</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>David — The Squeaky Wheel proved a money book for kids can be genuinely funny. Mine tries the same trick on spending rather than saving. Author to author, would you tell me if the humor lands?</t>
+          <t>David, The Squeaky Wheel proved a money book for kids can be genuinely funny. Mine tries the same trick on spending rather than saving. There's a copy with your name on it.</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -3501,20 +3501,20 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>A read from a fellow author?</t>
+          <t>Zero-prep K-5 resource</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Courtney — author and founder, so you'll see both the book and the business question. Mine teaches K-5 spending and sells direct rather than through Amazon. Worth a look, or a bad decision?</t>
+          <t>Courtney: author and founder, so you'll see both the book and the business question. Mine teaches K-5 spending and sells direct rather than through Amazon. Shout if you want one.</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -3550,16 +3550,16 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Hanna — you study financial literacy and wellbeing, so you'll spot the seams. My premise: spending is the first money skill a kid uses and no picture book is built around it. I'd value a researcher's read on whether the framing holds and the concepts land for ages 6-10.</t>
+          <t>Hanna: you study financial literacy and wellbeing, so you'll spot the seams. My premise: spending is the first money skill a kid uses and no picture book is built around it. I'd value a researcher's read on whether the framing holds and the concepts land for ages 6-10.</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -3595,16 +3595,16 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Casey — an award-winning financial literacy educator and founder of The Orchard Method is a tough, useful read. My K-5 book teaches spending rather than saving. Does the approach hold up for you?</t>
+          <t>Casey, an award-winning financial literacy educator and founder of The Orchard Method is a tough, useful read. My K-5 book teaches the spending half. Happy to hear it's not for you.</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -3640,16 +3640,16 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Clarissa — as a financial literacy ambassador you already sell people on why this matters. Mine teaches six-year-olds to spend deliberately. Would it fit the students or events you reach?</t>
+          <t>Clarissa — as a financial literacy ambassador you already sell people on why this matters. Mine teaches six-year-olds to spend deliberately. Shout if you want one.</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -3685,16 +3685,16 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Nicholas — a senior student ambassador sees which material actually lands with people. Mine is a K-5 picture book teaching spending rather than saving. Would it fit your outreach, or is it too young?</t>
+          <t>Nicholas, a senior student ambassador sees which material actually lands with people. It's a picture book for grades 1-5 teaching spending rather than saving. Would it fit your outreach, or is it too young?</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -3730,16 +3730,16 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Professor Urban — your work on financial education mandates is the best evidence we have on what actually moves outcomes. Almost all of it sits at high school. I wrote a K-5 book on the premise that the elementary band is both untested and undersupplied. Is there research I should know about before I keep saying that?</t>
+          <t>Carly: your work on financial education mandates is the best evidence we have on what actually moves outcomes. Almost all of it sits at high school. I wrote a K-5 book on the premise that the elementary band is both untested and undersupplied. Let me know and it ships.</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -3775,16 +3775,16 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Professor Mahoney — a question rather than a pitch. My K-5 book argues consumer transaction competence is taught almost nowhere, despite being the money behavior kids perform first. From a behavioral economics angle, is that a real gap or a rounding error?</t>
+          <t>Hi Neale. A question rather than a pitch. My K-5 book argues consumer transaction competence is taught almost nowhere, despite being the money behavior kids perform first. From a behavioral economics angle, is that a real gap or a rounding error?</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -3820,16 +3820,16 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Professor Duggan — well outside your usual work, and I'll be brief. I wrote a children's book on the premise that spending competence is untaught and precedes saving competence. If someone at SIEPR studies early financial capability, I'd value the name.</t>
+          <t>Mark, well outside your usual work, and I'll be brief. I wrote a children's book on the premise that spending competence is untaught and precedes saving competence. If someone at SIEPR studies early financial capability, I'd value the name.</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -3865,16 +3865,16 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Derek — you sit between research and practice, which is where my premise should get stress-tested. I argue we teach kids saving first when spending is the transaction they actually perform. Does the sequencing claim survive?</t>
+          <t>Derek. You sit between research and practice, which is where my premise should get stress-tested. I argue we teach kids saving first when spending is the transaction they actually perform. I'd take a blunt answer.</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -3910,16 +3910,16 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Professor Choi — your work on family financial wellbeing is adjacent to my premise: that spending competence is taught almost nowhere in K-5 despite being the first money behavior kids perform. Does that match what the literature shows?</t>
+          <t>Shinae — your work on family financial wellbeing is adjacent to my premise: that spending competence is taught almost nowhere in K-5 despite being the first money behavior kids perform. Does that match what the literature shows?</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -3955,16 +3955,16 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Angela — you bridge data and practice, which is exactly where I need a check. My claim: children's financial education is overwhelmingly saving-focused and the sequencing is backwards. Is there data contradicting me?</t>
+          <t>Angela, you bridge data and practice, which is exactly where I need a check. My claim: children's financial education is overwhelmingly saving-focused and the sequencing is backwards. Send me a one-word reply and I'll act on it.</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4000,16 +4000,16 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Melanie — Extension reaches families where money is concrete, which is how my book teaches it: one purchase, start to register. Would it fit Extension programming, and does the premise hold for the families you serve?</t>
+          <t>Melanie, Extension reaches families where money is concrete, which is how my book teaches it: one purchase, start to register. Would it fit Extension programming, and does the premise hold for the families you serve?</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -4045,16 +4045,16 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Iris — you're at UW-Madison, which is where the Center for Financial Security picked the titles for the CFPB's Money as You Grow Bookshelf. My K-5 book teaches spending rather than saving. Do you know who evaluates additions to that shelf?</t>
+          <t>Iris — you're at UW-Madison, which is where the Center for Financial Security picked the titles for the CFPB's Money as You Grow Bookshelf. My K-5 book skips saving and teaches spending. Do you know who evaluates additions to that shelf?</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -4090,16 +4090,16 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Anjana — a public health lens on financial capability is unusual and useful. My K-5 book treats spending competence as a preventive intervention rather than a curriculum topic. Does that framing make sense to you?</t>
+          <t>Hi Anjana. A public health lens on financial capability is unusual and useful. My K-5 book treats spending competence as a preventive intervention rather than a curriculum topic. Does that framing make sense to you?</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -4135,16 +4135,16 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
       <c r="I78" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Dr. Dowell — as an economics lecturer you'll want the premise tested. Mine: we teach children saving first, but spending is the transaction they perform first, so the sequence is backwards. Does that survive scrutiny?</t>
+          <t>Chelsea, as an economics lecturer you'll want the premise tested. Mine: we teach children saving first, but spending is the transaction they perform first, so the sequence is backwards. Thirty-six pages; won't cost you an evening.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -4180,16 +4180,16 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Dr. Nahidi — you teach finance at graduate level, where the gaps students carry up from childhood are visible. My book tries to close one at six. I'd value an academic's read on whether the premise is sound or convenient.</t>
+          <t>Narmin. You teach finance at graduate level, where the gaps students carry up from childhood are visible. My book tries to close one at six. I'd value an academic's read on whether the premise is sound or convenient.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
@@ -4270,16 +4270,16 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Jordan — a graduate student's read is useful because you're close to the research and not yet committed to a position. My premise: spending competence precedes saving competence and is untaught. Does it hold?</t>
+          <t>Jordan, a graduate student's read is useful because you're close to the research and not yet committed to a position. My premise: spending competence precedes saving competence and is untaught. There's a copy with your name on it.</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -4315,16 +4315,16 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>William — teaching finance at Delta Charter means you see students arrive with gaps set a decade earlier. Mine tries to close one at six. Would the premise hold up from where you sit?</t>
+          <t>William — teaching finance at Delta Charter means you see students arrive with gaps set a decade earlier. Mine tries to close one at six. I'll stop there.</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -4360,16 +4360,16 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Sloane — you're studying English and education, which makes you a better test than most of the people I'm asking. Does my book read like something a real first grader would sit through, or does the lesson show?</t>
+          <t>Sloane. You're studying English and education, which makes you a better test than most of the people I'm asking. Does my book read like something a real first grader would sit through, or does the lesson show?</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -4405,20 +4405,20 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>Does this claim hold?</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Chalese — a money management center sees exactly which gaps students arrive with. Mine tries to close one at six rather than nineteen. Does the premise match what walks through your door?</t>
+          <t>Chalese, a money management center sees exactly which gaps students arrive with. Mine tries to close one at six rather than nineteen. Does the premise match what walks through your door?</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -4454,20 +4454,20 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Does this sequencing claim hold?</t>
+          <t>A gap in kids' money books</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Dr. Wood — you've built financial capability work at national scale. My claim is that K-5 is structurally underserved because funding follows high school. Does that hold internationally, or is it a US problem?</t>
+          <t>Pushpa — you've built financial capability work at national scale. My claim is that K-5 is structurally underserved because funding follows high school. One line back is plenty.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -4503,16 +4503,16 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Professor Mesquita — you study digital consumer behavior, which makes my book slightly anachronistic on purpose: it teaches the physical transaction, cash and coupon and register. Does teaching the tangible version still matter?</t>
+          <t>Eduardo, you study digital consumer behavior, which makes my book slightly anachronistic on purpose: it teaches the physical transaction, cash and coupon and register. Does teaching the tangible version still matter?</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -4548,20 +4548,20 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>A K-5 question from outside the academy</t>
+          <t>One author to another</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Joel — an AFC with an MPA directing financial wellness will judge both the content and the delivery. Mine is a picture book plus four free zero-prep lessons. Would it fit a program you run?</t>
+          <t>Joel — an AFC with an MPA directing financial wellness will judge both the content and the delivery. Mine runs 36 pages plus four free zero-prep lessons. Would it fit a program you run?</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -4597,20 +4597,20 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A gap in kids' money books</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Ryan — a money success center sees the downstream cost of what nobody taught at eight. Mine teaches the complete purchase at six, sales tax included. Does starting that early actually stick, in your experience?</t>
+          <t>Ryan, a money success center sees the downstream cost of what nobody taught at eight. Mine teaches the complete purchase at six, sales tax included. Let me know and it ships.</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -4646,20 +4646,20 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>A K-5 question from outside the academy</t>
+          <t>A listing question</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Dr. McCoy — financial therapy says money behavior is emotional and early. My picture book meets a six-year-old at the first want in a store and walks him to his own decision. Does that land clinically, or is it wishful?</t>
+          <t>Megan: financial therapy says money behavior is emotional and early. My picture book meets a six-year-old at the first want in a store and walks him to his own decision. Happy to send a copy.</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -4695,20 +4695,20 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>One author to another</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Kim — a center for economic education knows what teachers actually adopt. My K-5 book is aligned to CEE and four other frameworks with a full crosswalk, and elementary is usually the thinnest shelf. Would it fit your teacher work?</t>
+          <t>Hi Kim. A center for economic education knows what teachers actually adopt. My K-5 book is aligned to CEE and four other frameworks with a full crosswalk, and elementary is usually the thinnest shelf. Would it fit your teacher work?</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -4744,20 +4744,20 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Does this sequencing claim hold?</t>
+          <t>Would this circulate?</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>227</v>
+        <v>257</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Maria — Tennessee's economic education council decides what reaches classrooms. My K-5 picture book plus free zero-prep toolkit is aligned to five frameworks. Elementary is where most states have the least. Is there a route in?</t>
+          <t>Maria, Tennessee's economic education council decides what reaches classrooms. My K-5 picture book; the toolkit behind it is free is mapped to five frameworks, crosswalk included. Elementary is where most states have the least. I'll post one if it's useful.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -4793,20 +4793,20 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>A K-5 question from outside the academy</t>
+          <t>A premise I'd like tested</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Professor Kalmi — your work on financial education crosses national contexts. My premise is that spending competence is taught almost nowhere at primary level, in any country I've checked. Does that hold in the European data?</t>
+          <t>Panu. Your work on financial education crosses national contexts. My premise is that spending competence is taught almost nowhere at primary level, in any country I've checked. Does that hold in the European data?</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -4842,20 +4842,20 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>Zero-prep K-5 resource</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Professor Lo Prete — a question from outside the academy. My children's book argues spending competence precedes saving competence developmentally. Is there literature that settles the sequencing question either way?</t>
+          <t>Anna — a question from outside the academy. My children's book argues spending competence precedes saving competence developmentally. Say the word and it's in the mail.</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -4891,20 +4891,20 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Does this sequencing claim hold?</t>
+          <t>A fundable K-5 resource</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Dr. Alsaadi — as a finance professor you'll test a premise quickly. Mine: children's financial education teaches saving almost exclusively while spending is the first transaction kids perform. Does that hold?</t>
+          <t>Lamya, as a finance professor you'll test a premise quickly. Mine: children's financial education teaches saving almost exclusively while spending is the first transaction kids perform. Tell me if it's not a fit.</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -4940,20 +4940,20 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>A K-5 question from outside the academy</t>
+          <t>Same kid, different approach</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Jaycob — a center for excellence in finance sees where competence actually comes from. Mine argues it starts with one supervised purchase at six. Does that framing interest you?</t>
+          <t>Jaycob — a center for excellence in finance sees where competence actually comes from. Mine argues it starts with one supervised purchase at six. If it's a no, no reply needed.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -4989,20 +4989,20 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Beau — a visiting professor's read is useful precisely because you see many programs. My K-5 book teaches spending rather than saving, aligned to five frameworks. Does the premise hold up?</t>
+          <t>Beau: a visiting professor's read is useful precisely because you see many programs. My K-5 book leaves saving alone; it teaches spending, mapped to five frameworks, crosswalk included. Does the premise hold up?</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -5038,20 +5038,20 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Does this sequencing claim hold?</t>
+          <t>Does this claim hold?</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Dr. Niranjan — a finance academic's read on a children's book premise: spending competence precedes saving competence and is taught almost nowhere. Does that survive in your context?</t>
+          <t>Hi CMA. A finance academic's read on a children's book premise: spending competence precedes saving competence and is taught almost nowhere. I'd rather hear no than nothing.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -5087,20 +5087,20 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>A K-5 question from outside the academy</t>
+          <t>A gap in kids' money books</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Jay — as a business instructor you see students arrive with gaps set long before college. My book tries to close one at six. Would the premise hold up in your classroom?</t>
+          <t>Jay, as a business instructor you see students arrive with gaps set long before college. My book tries to close one at six. Copy's yours if you want it.</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -5136,20 +5136,20 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A listing question</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Sebastian — an adjunct's read is useful because you see the practical end. My K-5 picture book teaches the complete purchase, sales tax included. Does that seem like the right first lesson?</t>
+          <t>Sebastian. An adjunct's read is useful because you see the practical end. My K-5 picture book teaches the whole purchase, right through sales tax. Does that seem like the right first lesson?</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -5185,20 +5185,20 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Does this sequencing claim hold?</t>
+          <t>One author to another</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Bryan — you advise students who often arrive without the basics. My book plants one at six: compare before you buy, and know what the register adds. Would it fit anything you point families toward?</t>
+          <t>Bryan — you advise students who often arrive without the basics. My book plants one at six: compare before you buy, and know what the register adds. I'll send it either way.</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -5234,20 +5234,20 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>A K-5 question from outside the academy</t>
+          <t>Would this circulate?</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Carly — executive education is a long way from a picture book, so briefly: mine teaches the complete purchase to six-year-olds. If your college does community or K-12 outreach, would it fit?</t>
+          <t>Carly, executive education is a long way from a picture book, so briefly: mine teaches the complete purchase to six-year-olds. If your college does community or K-12 outreach, would it fit?</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5292,11 +5292,11 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Ali — an analyst's read on a simple claim: children's financial education teaches saving and skips the transaction entirely. I wrote the counterexample for ages 6-10. Does the gap look real to you?</t>
+          <t>Ali, an analyst's read on a simple claim: children's financial education teaches saving and skips the transaction entirely. I wrote the counterexample for ages 6-10. No pitch after this one, promise.</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -5332,20 +5332,20 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Does this sequencing claim hold?</t>
+          <t>Zero-prep K-5 resource</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>Ashley — outside your field, so quickly. I wrote a children's book teaching six-year-olds to spend deliberately. If you work with young athletes or families, it may be useful. Worth a look?</t>
+          <t>Ashley — outside your field, so quickly. I wrote a children's book teaching six-year-olds to spend deliberately. If you work with young athletes or families, it may be useful. Ignore me if it's wrong for you.</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -5381,20 +5381,20 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>A K-5 question from outside the academy</t>
+          <t>A fundable K-5 resource</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>Jaime — an ethnic studies lens raises a fair question about my book: it's a working family talking honestly about bills and tradeoffs, which is rarer in this category than it should be. Would you tell me whether it rings true?</t>
+          <t>Jaime: an ethnic studies lens raises a fair question about my book: it's a working family talking honestly about bills and tradeoffs, which is rarer in this category than it should be. Would you tell me whether it rings true?</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -5430,20 +5430,20 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>Same kid, different approach</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>Didine — a CFP's read on a children's book: mine teaches the complete purchase, sales tax included, to six-year-olds. Does it get the money right, and would you point families to it?</t>
+          <t>Hi Didine. A CFP's read on a children's book: mine teaches the whole purchase, right through sales tax, to six-year-olds. One copy, no follow-up, your call.</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -5479,20 +5479,20 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Does this sequencing claim hold?</t>
+          <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Samantha — financial aid sees the end of a long chain that starts young. My book starts at six with spending rather than saving. Would it fit any family-facing program you run?</t>
+          <t>Samantha, financial aid sees the end of a long chain that starts young. My book starts at six with spending rather than saving. Would it fit any family-facing program you run?</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -5528,20 +5528,20 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>A K-5 resource with nothing to reorder</t>
+          <t>Does this claim hold?</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>Debbie — system procurement means you care about total cost, not sticker. Mine is a hardcover with nothing consumable and free ungated teacher materials, so the cost is one-time. Is there a route into your review process?</t>
+          <t>Hi Debbie. System procurement means you care about total cost, not sticker. Mine is a hardcover with nothing consumable and free ungated teacher materials, so the cost is one-time. Is there a route into your review process?</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -5577,16 +5577,16 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Melissa — a curriculum specialist in an elementary school is exactly the read I want. Mine is a picture book with zero-prep lessons aligned to five frameworks. Would it work in Lanier's classrooms?</t>
+          <t>Melissa. A curriculum specialist in an elementary school is exactly the read I want. Mine runs 36 pages with zero-prep lessons built against five standards frameworks. Would it work in Lanier's classrooms?</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -5622,16 +5622,16 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>Samantha — reading intervention plus SEL is an unusual combination and useful here: my book is AD 620L and the money decision is also an impulse-control lesson. Would it fit either side of your work?</t>
+          <t>Samantha — reading intervention plus SEL is an unusual combination and useful here: my book is AD 620L and the money decision is also an impulse-control lesson. Thirty-six pages; won't cost you an evening.</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
@@ -5713,16 +5713,16 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" t="n">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Jacquelyn — a principal who has run early childhood has seen every reading level in the building. Mine is a 36-page read-aloud at AD 620L that teaches money through one shopping trip. Would it work in your school?</t>
+          <t>Jacquelyn, a principal who has run early childhood has seen every reading level in the building. Mine is a 36-page read-aloud at AD 620L that teaches money through one shopping trip. Happy to be told no.</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -5758,16 +5758,16 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" t="n">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Bruce — you handle procurement, so the practical facts first: 36-page hardcover, no consumables, nothing to reorder, free lesson plans, $19.99 direct with PO and Net 30 available. ISBN 979-8-234-07638-0. Would it clear the bar for classroom purchase?</t>
+          <t>Bruce, you handle procurement, so the practical facts first: 36-page hardcover, no consumables, nothing to reorder, free lesson plans, $19.99 direct with PO and Net 30 available. ISBN 979-8-234-07638-0. A copy is easy to send.</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -5803,16 +5803,16 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>Jake — DCPS classrooms will tell you fast whether something works. Mine is a K-5 picture book teaching spending, with four zero-prep standards-aligned lessons behind it. Elementary is usually where financial literacy gets skipped. Where would it fit?</t>
+          <t>Jake, DCPS classrooms will tell you fast whether something works. Mine runs 36 pages, grades 1-5 teaching spending, with four zero-prep standards-aligned lessons behind it. Elementary is usually where financial literacy gets skipped. Let me know and it ships.</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -5848,16 +5848,16 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
       <c r="I114" t="n">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Shawn — congratulations on the superintendency. As you set priorities, elementary financial literacy is usually the gap nobody's assigned. Mine is a picture book plus free toolkit for K-5. Would it fit early-grades or family programming?</t>
+          <t>Shawn. Congratulations on the superintendency. As you set priorities, elementary financial literacy is usually the gap nobody's assigned. I made a picture book; the toolkit behind it is free for K-5. No obligation either way.</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -5893,16 +5893,16 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Dr. Pinder — a superintendent's read matters most on placement. My K-5 book teaches spending through a story, with free standards-aligned lessons. Classroom, library, or family night. Where would you put it?</t>
+          <t>David — a superintendent's read matters most on placement. My K-5 book teaches spending through a story, with free standards-aligned lessons. Classroom, library, or family night. Where would you put it?</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -5938,16 +5938,16 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Mallory — assistant principal, adjunct, and speaker means you've taught every audience. Mine is a K-5 picture book where a six-year-old makes one real money decision and gets it right. Would it land in an elementary classroom?</t>
+          <t>Mallory — assistant principal, adjunct, and speaker means you've taught every audience. It's a picture book for grades 1-5 where a six-year-old makes one real money decision and gets it right. Send me a one-word reply and I'll act on it.</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -5983,16 +5983,16 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" t="n">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>Angela — as head of school you set what students read. Mine is a 36-page picture book that teaches money through a story, with free standards-aligned lessons behind it. Would it earn a place in your school?</t>
+          <t>Angela: as head of school you set what students read. Mine is a 36-page picture book that teaches money through a story, with free standards-aligned lessons behind it. Glad to mail one.</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -6028,16 +6028,16 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Kristen — as a director of education you decide what reaches learners. Mine is a K-5 picture book teaching spending rather than saving, with four zero-prep lessons. Elementary is usually the thinnest shelf. Would it fit your programs?</t>
+          <t>Hi Kristen. As a director of education you decide what reaches learners. I made the K-5 version teaching spending rather than saving, with four zero-prep lessons. Elementary is usually the thinnest shelf. Would it fit your programs?</t>
         </is>
       </c>
       <c r="K118" t="inlineStr"/>
@@ -6073,20 +6073,20 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Elementary financial literacy, zero prep</t>
+          <t>A gap in kids' money books</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>Sarah — curriculum and instruction is where a book like this lives or dies. Mine has a 23-row standards crosswalk and four 45-minute lessons built alongside the book rather than added afterward. Would you look at whether that holds?</t>
+          <t>Sarah, curriculum and instruction is where a book like this lives or dies. Mine has a 23-row standards crosswalk and four 45-minute lessons built alongside the book rather than added afterward. It's a short read.</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -6122,16 +6122,16 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>Malori — you lead financial literacy curriculum and build educational games, so engagement is your bar. Mine holds a six-year-old through 36 pages because it's a story first. Would it fit your curriculum?</t>
+          <t>Malori: you lead financial literacy curriculum and build educational games, so engagement is your bar. Mine holds a six-year-old through 36 pages because it's a story first. Would it fit your curriculum?</t>
         </is>
       </c>
       <c r="K120" t="inlineStr"/>
@@ -6167,16 +6167,16 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>Michael — education and outreach at Troutwood is aimed at making the future tangible. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for. Would it fit your outreach?</t>
+          <t>Hi Michael. Education and outreach at Troutwood is aimed at making the future tangible. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for. One line back is plenty.</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -6212,16 +6212,16 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" t="n">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>Peggy — as a consultant and instructional designer you'll see whether the lessons teach or just look like it. Mine are four 45-minute plans with assessments and a crosswalk. Would you look?</t>
+          <t>Peggy, as a consultant and instructional designer you'll see whether the lessons teach or just look like it. Mine are four 45-minute plans with assessments and a crosswalk. Happy to send a copy.</t>
         </is>
       </c>
       <c r="K122" t="inlineStr"/>
@@ -6257,16 +6257,16 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>Kim — you built your own financial literacy framework, so you think in systems. Mine is narrow by design: one transaction taught completely, rather than a survey. Does narrow beat broad at K-5?</t>
+          <t>Kim. You built your own financial literacy framework, so you think in systems. Mine is narrow by design: one transaction taught completely, rather than a survey. Does narrow beat broad at K-5?</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -6302,16 +6302,16 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" t="n">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Peter — on a financial literacy advisory committee you weigh which resources are worth backing. Mine is a K-5 picture book plus free ungated toolkit aligned to five frameworks. Does it fit the committee's work?</t>
+          <t>Peter — on a financial literacy advisory committee you weigh which resources are worth backing. Mine runs 36 pages, grades 1-5 plus free ungated toolkit built against five standards frameworks. I'll post one if it's useful.</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -6347,16 +6347,16 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>Nechama — early childhood consulting means you know what actually holds a young child. Mine is a 36-page story where the money lesson never interrupts the plot. Would it fit the settings you advise?</t>
+          <t>Nechama, early childhood consulting means you know what actually holds a young child. Mine is a 36-page story where the money lesson never interrupts the plot. Would it fit the settings you advise?</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -6392,16 +6392,16 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
       <c r="I126" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Amy-Marie — head of early childhood is the reader I hoped for. Mine starts where kids start with money: spending it. One trip, one decision, no worksheet. Would it work in your setting?</t>
+          <t>Amy-Marie, head of early childhood is the reader I hoped for. Mine starts where kids start with money: spending it. One trip, one decision, no worksheet. Say the word and it's in the mail.</t>
         </is>
       </c>
       <c r="K126" t="inlineStr"/>
@@ -6437,16 +6437,16 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" t="n">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>Cynthia — early childhood programs are exactly the window I wrote for. My book teaches the first money behavior a child performs, which is spending, not saving. Would it fit Westminster's programs?</t>
+          <t>Cynthia — early childhood programs are exactly the window I wrote for. My book teaches the first money behavior a child performs, which is spending, not saving. Tell me if it's not a fit.</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr"/>
@@ -6527,16 +6527,16 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>215</v>
+        <v>199</v>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>Gina — a purchasing agent's questions, answered up front: 36-page hardcover, no consumables to reorder, free zero-prep lessons, PO and Net 30, ISBN 979-8-234-07638-0, LCCN 2026906164. Would it clear Smithtown's bar?</t>
+          <t>Gina: a purchasing agent's questions, answered up front: 36-page hardcover, no consumables to reorder, free zero-prep lessons, PO and Net 30, ISBN 979-8-234-07638-0, LCCN 2026906164. I'll stop there.</t>
         </is>
       </c>
       <c r="K129" t="inlineStr"/>
@@ -6572,16 +6572,16 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr"/>
       <c r="I130" t="n">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Dr. Martirano — a superintendent who's also a digital education fellow sees the whole board. Mine is deliberately analog: a printed read-along plus free digital lessons. Would that combination work in Allegany County?</t>
+          <t>Michael, a superintendent who's also a digital education fellow sees the whole board. Mine is deliberately analog: a printed read-along plus free digital lessons. I'd take a blunt answer.</t>
         </is>
       </c>
       <c r="K130" t="inlineStr"/>
@@ -6617,16 +6617,16 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Christopher — Norristown sets what reaches every elementary classroom. My K-5 book teaches the complete purchase, sales tax included, with zero-prep lessons. Where would it fit: classroom, library, or family night?</t>
+          <t>Christopher, Norristown sets what reaches every elementary classroom. My K-5 book teaches the whole purchase, right through sales tax, with zero-prep lessons. Where would it fit: classroom, library, or family night?</t>
         </is>
       </c>
       <c r="K131" t="inlineStr"/>
@@ -6662,16 +6662,16 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Stephanie — a K-8 curriculum leader can tell whether lessons were built alongside a book or bolted on. Mine were built alongside: four lessons, assessments, a 23-row crosswalk. Would you test that claim?</t>
+          <t>Stephanie, a K-8 curriculum leader can tell whether lessons were built alongside a book or bolted on. Mine were built alongside: four lessons, assessments, a 23-row crosswalk. I'll send it if you're curious.</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -6707,16 +6707,16 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>Mansi — curriculum design and academic coordination is where my materials should get judged. Four zero-prep lessons, a pre/post assessment with answer key, a 23-row crosswalk. Does the design hold up?</t>
+          <t>Mansi, curriculum design and academic coordination is where my materials should get judged. Four zero-prep lessons, a pre/post assessment with answer key, a 23-row crosswalk. Does the design hold up?</t>
         </is>
       </c>
       <c r="K133" t="inlineStr"/>
@@ -6752,16 +6752,16 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
       <c r="I134" t="n">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Nikole — Banzai builds financial literacy for real classrooms, and K-5 is the band with the least. Mine is a picture book plus free zero-prep lessons aligned to five frameworks. Does the approach fit how you think about it?</t>
+          <t>Nikole — Banzai builds financial literacy for real classrooms, and K-5 is the band with the least. I made a picture book plus free zero-prep lessons mapped to five frameworks, crosswalk included. Happy to hear it's not for you.</t>
         </is>
       </c>
       <c r="K134" t="inlineStr"/>
@@ -6797,16 +6797,16 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
       <c r="I135" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Hema — leading an early childhood school, you set what young kids read. Mine is a read-along that teaches money through story, with free lessons behind it. Would it work in your setting?</t>
+          <t>Hema: leading an early childhood school, you set what young kids read. Mine is a read-along that teaches money through story, with free lessons behind it. Would it work in your setting?</t>
         </is>
       </c>
       <c r="K135" t="inlineStr"/>
@@ -6842,16 +6842,16 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Kevin — operations and instruction together means you see what survives implementation. Mine is a picture book with nothing to reorder and free lessons. Would it hold up in a real building?</t>
+          <t>Kevin, operations and instruction together means you see what survives implementation. Mine runs 36 pages with nothing to reorder and free lessons. Would it hold up in a real building?</t>
         </is>
       </c>
       <c r="K136" t="inlineStr"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>For your elementary classrooms</t>
+          <t>A listing question</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -6936,20 +6936,20 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>A K-5 resource with nothing to reorder</t>
+          <t>One author to another</t>
         </is>
       </c>
       <c r="I138" t="n">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Bailey — elementary curriculum development is where my materials get judged. Mine were built alongside the book: four zero-prep lessons, assessments, a 23-row crosswalk. Would you look?</t>
+          <t>Bailey: elementary curriculum development is where my materials get judged. Mine were built alongside the book: four zero-prep lessons, assessments, a 23-row crosswalk. No pitch after this one, promise.</t>
         </is>
       </c>
       <c r="K138" t="inlineStr"/>
@@ -6985,20 +6985,20 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Elementary financial literacy, zero prep</t>
+          <t>Would this circulate?</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>Debra — as director of elementary curriculum you decide what reaches K-5, which is the band financial literacy skips entirely. Mine is a picture book with a full standards crosswalk. Would it clear your bar?</t>
+          <t>Hi Debra. As director of elementary curriculum you decide what reaches K-5, which is the band financial literacy skips entirely. I made a picture book with a full standards crosswalk. Ignore me if it's wrong for you.</t>
         </is>
       </c>
       <c r="K139" t="inlineStr"/>
@@ -7034,20 +7034,20 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>For your elementary classrooms</t>
+          <t>A premise I'd like tested</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Ellen — curriculum and instruction facilitators see whether teachers actually adopt something. Mine needs no prep and nothing consumable. Would that survive in your elementary classrooms?</t>
+          <t>Ellen, curriculum and instruction facilitators see whether teachers actually adopt something. Mine needs no prep and nothing consumable. Would that survive in your elementary classrooms?</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -7083,20 +7083,20 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>A K-5 resource with nothing to reorder</t>
+          <t>Zero-prep K-5 resource</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>Esabel — a director of curriculum and instruction will ask about standards first. Mine maps to Jump$tart, Common Core Math and ELA, CEE, and FDIC Money Smart, with a 23-row crosswalk. Worth a review?</t>
+          <t>Esabel. A director of curriculum and instruction will ask about standards first. Mine maps to Jump$tart, Common Core Math and ELA, CEE, and FDIC Money Smart, with a 23-row crosswalk. One copy, no follow-up, your call.</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -7132,12 +7132,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Elementary financial literacy, zero prep</t>
+          <t>A fundable K-5 resource</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -7181,20 +7181,20 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>For your elementary classrooms</t>
+          <t>Same kid, different approach</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Julie — as senior director of elementary curriculum you decide what reaches a lot of classrooms. Mine teaches the complete purchase, sales tax included, with a full standards crosswalk. Worth a look?</t>
+          <t>Julie, as senior director of elementary curriculum you decide what reaches a lot of classrooms. Mine teaches one purchase end to end, tax and all, with a full standards crosswalk. I'll leave it there.</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -7230,20 +7230,20 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>A K-5 resource with nothing to reorder</t>
+          <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Katie — elementary curriculum and instruction is exactly the band that gets skipped on financial literacy. Mine is a picture book plus four free zero-prep lessons. Would it fit your district?</t>
+          <t>Katie, elementary curriculum and instruction is exactly the band that gets skipped on financial literacy. Mine runs 36 pages plus four free zero-prep lessons. Shout if you want one.</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -7279,12 +7279,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Elementary financial literacy, zero prep</t>
+          <t>Does this claim hold?</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -7328,20 +7328,20 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>For your elementary classrooms</t>
+          <t>A gap in kids' money books</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Dr. Berry — as director of elementary curriculum you set what K-5 actually gets. Financial literacy usually stops before fifth grade entirely. Mine is a picture book plus free standards-aligned lessons. Worth reviewing?</t>
+          <t>Mona: as director of elementary curriculum you set what K-5 actually gets. Financial literacy usually stops before fifth grade entirely. It's a 36-page picture book plus free standards-aligned lessons. There's a copy with your name on it.</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -7377,20 +7377,20 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>A K-5 resource with nothing to reorder</t>
+          <t>A listing question</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>Shelly — an elementary curriculum coordinator sees what teachers actually pick up. Mine requires no prep and nothing consumable, and it's a story kids finish. Would it fit your schools?</t>
+          <t>Hi Shelly. An elementary curriculum coordinator sees what teachers actually pick up. Mine requires no prep and nothing consumable, and it's a story kids finish. Would it fit your schools?</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -7426,20 +7426,20 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Elementary financial literacy, zero prep</t>
+          <t>One author to another</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>Suzan — elementary curriculum directors are the right filter for this. Mine is a K-5 picture book teaching spending, with assessments and a 23-row crosswalk behind it. Worth a review?</t>
+          <t>Suzan, elementary curriculum directors are the right filter for this. I've written one for grades 1-5 teaching spending, with assessments and a 23-row crosswalk behind it. Take a look or don't; either is fine.</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -7475,20 +7475,20 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>For your elementary classrooms</t>
+          <t>Would this circulate?</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>Tamika — an elementary curriculum specialist will know whether this fits a real scope and sequence. Mine is one 36-page book plus four 45-minute lessons, aligned to five frameworks. Would you look?</t>
+          <t>Tamika. An elementary curriculum specialist will know whether this fits a real scope and sequence. Mine is one 36-page book plus four 45-minute lessons, mapped to five frameworks, crosswalk included. I'll send it and get out of your way.</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -7524,12 +7524,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>A K-5 resource with nothing to reorder</t>
+          <t>A premise I'd like tested</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -7573,16 +7573,16 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>Gerri — money habits form in early childhood long before anyone calls them that. My book teaches the first one a child actually uses: how to spend deliberately. Would it fit the families you serve?</t>
+          <t>Hi Gerri. Money habits form in early childhood long before anyone calls them that. My book teaches the first one a child actually uses: how to spend deliberately. If it's a no, no reply needed.</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -7618,16 +7618,16 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" t="n">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>Noelani — you design adult learning, so you'll know if my teacher materials actually teach. Four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk, all free. Would you look at the instructional design?</t>
+          <t>Noelani. You design adult learning, so you'll know if my teacher materials actually teach. Four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk, all free. I'd rather hear no than nothing.</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -7663,16 +7663,16 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
       <c r="I153" t="n">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>Jennifer — as an EdTech implementation lead you know adoption fails on friction. Mine has none: a book plus print-ready lessons, no login, no platform, no seats. Would that fit any state program you run?</t>
+          <t>Jennifer — as an EdTech implementation lead you know adoption fails on friction. Mine has none: a book plus print-ready lessons, no login, no platform, no seats. Copy's yours if you want it.</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -7708,20 +7708,20 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Elementary financial literacy, zero prep</t>
+          <t>Zero-prep K-5 resource</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>Gil — a curriculum developer working on financial literacy math will care that my book has real arithmetic in it: comparing two prices, applying a percentage off, adding sales tax. Would it fit what you're building?</t>
+          <t>Gil, a curriculum developer working on financial literacy math will care that my book has real arithmetic in it: comparing two prices, applying a percentage off, adding sales tax. Yours if you'll have it.</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -7757,16 +7757,16 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr"/>
       <c r="I155" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>Amanda — a practitioner gut-check. My K-5 book teaches spending through a story about a boy and a robot, no worksheet anywhere. Would it hold a group of early-childhood kids, or does it skew older?</t>
+          <t>Amanda, a practitioner gut-check. My K-5 book teaches spending through a story about a boy and a robot, no worksheet anywhere. Would it hold a group of early-childhood kids, or does it skew older?</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -7802,7 +7802,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
@@ -7847,16 +7847,16 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr"/>
       <c r="I157" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>Cherry — Virginia Credit Union runs one of the more serious financial education programs in the country. Mine is a K-5 book plus free toolkit, and there's a grant-ready packet with cost math if the CU wanted to fund classroom sets locally. Worth a look?</t>
+          <t>Cherry: Virginia Credit Union runs one of the more serious financial education programs in the country. Mine is a K-5 book plus free toolkit, and there's a grant-ready packet with cost math if the CU wanted to fund classroom sets locally. A copy is easy to send.</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -7892,16 +7892,16 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>Monica — you run financial education for a credit union, so the useful detail is this: there's a grant-ready packet behind the book with exact cost math for classroom sets, built for exactly this kind of sponsorship. Would it fit a member or school program?</t>
+          <t>Hi Monica. You run financial education for a credit union, so the useful detail is this: there's a grant-ready packet behind the book with exact cost math for classroom sets, built for exactly this kind of sponsorship. Would it fit a member or school program?</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -7937,16 +7937,16 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" t="n">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>Angela — in-school financial wellness is the hardest version of this job and the most useful. Mine is a K-5 read-aloud with zero-prep lessons, which is what a visiting educator actually needs. Would it fit your Visions work?</t>
+          <t>Angela, in-school financial wellness is the hardest version of this job and the most useful. Mine is a K-5 read-aloud with zero-prep lessons, which is what a visiting educator actually needs. I'll stop there.</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -7982,16 +7982,16 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr"/>
       <c r="I160" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>Jon — a financial education specialist with a psychology background will care that the book is built around one decision rather than a list of concepts. Would it fit a Cy-Fair member or family program?</t>
+          <t>Jon. A financial education specialist with a psychology background will care that the book is built around one decision rather than a list of concepts. Would it fit a Cy-Fair member or family program?</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -8027,16 +8027,16 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" t="n">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>Brittney — SchoolsFirst puts you in front of educators constantly, which is the audience for the free toolkit as much as the book. Four lessons, assessments, a crosswalk, all ungated. Would it fit a member program?</t>
+          <t>Brittney — SchoolsFirst puts you in front of educators constantly, which is the audience for the free toolkit as much as the book. Four lessons, assessments, a crosswalk, all ungated. Let me know and it ships.</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -8072,16 +8072,16 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr"/>
       <c r="I162" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>Judette — a bank financial literacy officer usually needs something CRA-reportable. Mine has a grant-ready packet with cost math for classroom sets, designed to be funded and counted. Would it fit Byline's programs?</t>
+          <t>Judette, a bank financial literacy officer usually needs something CRA-reportable. Mine has a grant-ready packet with cost math for classroom sets, designed to be funded and counted. No obligation either way.</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -8117,16 +8117,16 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr"/>
       <c r="I163" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>Kayleigh — CTE banking students are older than my readers, but HRCU's community work probably isn't. Mine is a K-5 read-aloud with free lessons. Would it fit an elementary outreach program?</t>
+          <t>Kayleigh, CTE banking students are older than my readers, but HRCU's community work probably isn't. Mine is a K-5 read-aloud with free lessons. Would it fit an elementary outreach program?</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -8162,16 +8162,16 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr"/>
       <c r="I164" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>Kenda — you've said financial literacy should be offered to everyone, and elementary is where that promise usually breaks. Mine is a K-5 book plus free ungated toolkit. Would it fit a program you run?</t>
+          <t>Kenda — you've said financial literacy should be offered to everyone, and elementary is where that promise usually breaks. Mine is a K-5 book plus free ungated toolkit. I'd take a blunt answer.</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -8207,16 +8207,16 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr"/>
       <c r="I165" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>Michael — Credit Union 1's community work reaches families directly. Mine is a read-along, so the parent and child do it together, and the free family activity is built for a kitchen table. Would it fit?</t>
+          <t>Michael: Credit Union 1's community work reaches families directly. Mine is a read-along, so the parent and child do it together, and the free family activity is built for a kitchen table. Would it fit?</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -8252,16 +8252,16 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
       <c r="I166" t="n">
-        <v>205</v>
+        <v>234</v>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>Sarah — MidFirst's education work reaches schools and families both. Mine is a K-5 picture book with free zero-prep lessons and a grant-ready packet if the bank wanted to fund classroom sets. Worth a look?</t>
+          <t>Hi Sarah. MidFirst's education work reaches schools and families both. I made the K-5 version with free zero-prep lessons and a grant-ready packet if the bank wanted to fund classroom sets. Send me a one-word reply and I'll act on it.</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -8297,16 +8297,16 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr"/>
       <c r="I167" t="n">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>Alyssa — corporate training and financial literacy at a bank is an unusual double. Mine is a K-5 book with free ungated teacher materials and a CRA-friendly funding packet. Would it fit Falcon's community work?</t>
+          <t>Alyssa, corporate training and financial literacy at a bank is an unusual double. Mine is a K-5 book with free ungated teacher materials and a CRA-friendly funding packet. Glad to mail one.</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -8342,16 +8342,16 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr"/>
       <c r="I168" t="n">
-        <v>201</v>
+        <v>161</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>Hello — you run financial programs alongside the banking work, so you see both sides. Mine is a K-5 picture book with free ungated teacher materials. Would it fit a community or family program you run?</t>
+          <t>Mass — you run financial programs alongside the banking work, so you see both sides. 36 pages, grades 1-5 with free ungated teacher materials. It's a short read.</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr"/>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>Corey — as a personal finance educator you know spending is where habits actually form, and where nobody teaches. Mine is the K-5 version: one purchase, ad to register. Would it fit the learners you reach?</t>
+          <t>Corey, as a personal finance educator you know spending is where habits actually form, and where nobody teaches. Mine is the K-5 version: one trip, ad through register. Would it fit the learners you reach?</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -8432,16 +8432,16 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr"/>
       <c r="I170" t="n">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>Dan — after a career at the Cleveland Fed you've thought about financial capability from the top down; I came at it from age six. My book teaches the transaction itself. I'd value your read on whether that's where it should start.</t>
+          <t>Hi Dan. After a career at the Cleveland Fed you've thought about financial capability from the top down; I came at it from age six. My book teaches the transaction itself. I want your read on whether that's where it should start.</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -8477,16 +8477,16 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
       <c r="I171" t="n">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>Bina — community engagement at the SF Fed is where household financial capability actually gets measured. My K-5 book teaches spending rather than saving, on the theory that the sequence is backwards. Does that square with what you see?</t>
+          <t>Bina, community engagement at the SF Fed is where household financial capability actually gets measured. My K-5 book skips saving entirely, on the theory that the sequence is backwards. Does that square with what you see?</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -8522,16 +8522,16 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr"/>
       <c r="I172" t="n">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>Seema — the St. Louis Fed connects national research to local programs, which is where a K-5 resource fits. Mine is a picture book plus free toolkit aligned to five frameworks. Would it fit a Louisville branch program?</t>
+          <t>Seema. The St. Louis Fed connects national research to local programs, which is where a K-5 resource fits. It's a 36-page picture book; the toolkit behind it is free built against five standards frameworks. Yours if you'll have it.</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -8567,16 +8567,16 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
       <c r="I173" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>Alfredo — financial inclusion work meets families where the gaps are widest, and elementary is where almost nothing exists. Mine is a K-5 book plus free toolkit. Would it fit a member or community program?</t>
+          <t>Alfredo. Financial inclusion work meets families where the gaps are widest, and elementary is where almost nothing exists. Mine is a K-5 book plus free toolkit. Would it fit a member or community program?</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -8612,16 +8612,16 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr"/>
       <c r="I174" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>Jennifer — community development officers need things that are fundable and countable. Mine has a grant-ready packet with exact cost math for classroom sets. Would it fit UP Federal's community work?</t>
+          <t>Jennifer, community development officers need things that are fundable and countable. Mine has a grant-ready packet with exact cost math for classroom sets. Would it fit UP Federal's community work?</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -8657,16 +8657,16 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
       <c r="I175" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>Juli — community engagement at a credit union usually means finding programs that scale cheaply. Mine is a book plus a completely free toolkit, so the only cost is the copies. Would it fit USF's work?</t>
+          <t>Juli, community engagement at a credit union usually means finding programs that scale cheaply. Mine is a book plus a completely free toolkit, so the only cost is the copies. Thirty-six pages; won't cost you an evening.</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -8702,16 +8702,16 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
       <c r="I176" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>Rick — social corporate responsibility needs outcomes you can report. Mine comes with a pre/post assessment and a 25-row tracking table, built so a sponsor can show what changed. Would that fit your CRA reporting?</t>
+          <t>Rick — social corporate responsibility needs outcomes you can report. Mine comes with a pre/post assessment and a 25-row tracking table, built so a sponsor can show what changed. I'll send it if you're curious.</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -8747,16 +8747,16 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
       <c r="I177" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>Mark — Salus works with credit unions and community banks, which are exactly the institutions that fund K-5 financial literacy locally. Mine is a book plus free toolkit with a grant-ready packet. Worth knowing about?</t>
+          <t>Mark: Salus works with credit unions and community banks, which are exactly the institutions that fund K-5 financial literacy locally. Mine is a book plus free toolkit with a grant-ready packet. Worth knowing about?</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -8792,16 +8792,16 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr"/>
       <c r="I178" t="n">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>Dr. Frisancho — you've studied financial capability at development scale. My premise is that spending competence is the untaught first skill, and I wrote a K-5 book around it. Does that match what your research shows in Latin America?</t>
+          <t>Veronica: you've studied financial capability at development scale. My premise is that spending competence is the untaught first skill, and I wrote a K-5 book around it. Take a look or don't; either is fine.</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -8837,20 +8837,20 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>A fundable K-5 financial literacy resource</t>
+          <t>A fundable K-5 resource</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>Aziza — as an AVP of financial wellness you know the lessons that stick start young, and that elementary rarely gets a budget. Mine has a grant-ready funding packet behind it. Would it fit a family program?</t>
+          <t>Hi Aziza. As an AVP of financial wellness you know the lessons that stick start young, and that elementary rarely gets a budget. Mine has a grant-ready funding packet behind it. Happy to hear it's not for you.</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -8886,20 +8886,20 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>For a member or family program</t>
+          <t>Same kid, different approach</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Brittany — a financial education manager needs material that works without you in the room. Mine is a read-aloud with zero-prep lessons a teacher or parent can run alone. Would it fit your programs?</t>
+          <t>Brittany, a financial education manager needs material that works without you in the room. Mine is a read-aloud with zero-prep lessons a teacher or parent can run alone. Would it fit your programs?</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -8935,20 +8935,20 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>K-5 financial literacy, grant-ready</t>
+          <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>Kayde — as a financial education coordinator you're the one who has to make it work on the ground. Mine needs no prep, no platform, and nothing consumable. Would it fit a program you coordinate?</t>
+          <t>Kayde. As a financial education coordinator you're the one who has to make it work on the ground. Mine needs no prep, no platform, and nothing consumable. One line back is plenty.</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -8984,20 +8984,20 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>A fundable K-5 financial literacy resource</t>
+          <t>Does this claim hold?</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>Kristi — directing financial literacy means choosing what actually reaches people. Mine is K-5, which is usually the band with nothing. Picture book plus free ungated toolkit. Worth a look?</t>
+          <t>Kristi — directing financial literacy means choosing what actually reaches people. Mine is K-5, which is usually the band with nothing. Picture book plus free ungated toolkit. Happy to send a copy.</t>
         </is>
       </c>
       <c r="K182" t="inlineStr"/>
@@ -9033,20 +9033,20 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>For a member or family program</t>
+          <t>A gap in kids' money books</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>Marshall — community impact and financial wellbeing is where a K-5 resource matters most, because elementary rarely gets its own funding. Mine has a grant-ready packet with cost math. Would it fit?</t>
+          <t>Marshall, community impact and financial wellbeing is where a K-5 resource matters most, because elementary rarely gets its own funding. Mine has a grant-ready packet with cost math. Would it fit?</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -9082,20 +9082,20 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>K-5 financial literacy, grant-ready</t>
+          <t>A listing question</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>Peyton — as a financial wellness director you decide what reaches families. Mine is a K-5 read-along plus a free family activity built for a kitchen table rather than a classroom. Would it fit?</t>
+          <t>Peyton, as a financial wellness director you decide what reaches families. Mine is a K-5 read-along plus a free family activity built for a kitchen table rather than a classroom. I'll post one if it's useful.</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -9131,20 +9131,20 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>InMail (needs Premium credit)</t>
+          <t>InMail (Premium credit)</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>A fundable K-5 financial literacy resource</t>
+          <t>Would this circulate?</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>Salman — national program integration is exactly the scale where K-5 gets forgotten. Mine is a picture book plus free ungated toolkit aligned to five frameworks. Would it fit your integration work?</t>
+          <t>Salman: national program integration is exactly the scale where K-5 gets forgotten. I made a picture book plus free ungated toolkit mapped to five frameworks, crosswalk included. Say the word and it's in the mail.</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -9180,16 +9180,16 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr"/>
       <c r="I186" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>Sito — you've led K-12 at system level, so you know financial literacy usually stops at high school. Mine is the elementary on-ramp: a picture book plus free standards-aligned lessons. Does it fit a district push?</t>
+          <t>Sito, you've led K-12 at system level, so you know financial literacy usually stops at high school. Mine is the elementary on-ramp: a picture book plus free standards-aligned lessons. Does it fit a district push?</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -9225,16 +9225,16 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr"/>
       <c r="I187" t="n">
-        <v>197</v>
+        <v>167</v>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>Ashley — an ECE strategist who keeps wellbeing central will get what I was after: a six-year-old making a real decision without being lectured. Would it fit the early-childhood settings you advise?</t>
+          <t>Ashley, an ECE strategist who keeps wellbeing central will get what I was after: a six-year-old making a real decision without being lectured. I'll send it either way.</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -9270,16 +9270,16 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr"/>
       <c r="I188" t="n">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>Dominic — Millionaire Habits for Families is a habit-first approach, which is exactly my book's design: one repeatable behavior, taught once, in a story. Would it fit the parents you help?</t>
+          <t>Dominic — Millionaire Habits for Families is a habit-first approach, which is exactly my book's design: one repeatable behavior, taught once, in a story. No obligation either way.</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -9315,16 +9315,16 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
       <c r="I189" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>Cassandra — a financial educator running operations knows what actually gets used versus what gets filed. Mine needs no prep and nothing consumable. Would it fit a member or family program you run?</t>
+          <t>Cassandra: a financial educator running operations knows what actually gets used versus what gets filed. Mine needs no prep and nothing consumable. Would it fit a member or family program you run?</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -9360,16 +9360,16 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" t="n">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>Chris — CoinSprout Kids and my book are after the same kid from different directions: yours digital, mine a printed read-along. Do those complement each other, or is print a liability now?</t>
+          <t>Hi Chris. CoinSprout Kids and my book are after the same kid from different directions: yours digital, mine a printed read-along. I'd take a blunt answer.</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -9405,16 +9405,16 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr"/>
       <c r="I191" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>Christina — Think Pieces is building financial education for children, so we're solving the same problem. Mine is a picture book plus free ungated toolkit for K-5. Worth comparing notes, or trading copies?</t>
+          <t>Christina, Think Pieces is building financial education for children, so we're solving the same problem. It's a 36-page picture book plus free ungated toolkit for K-5. Worth comparing notes, or trading copies?</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -9450,16 +9450,16 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr"/>
       <c r="I192" t="n">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>Claudia — community engagement at NFEC puts you in front of real families. Mine is a K-5 read-along with a free family activity built for a kitchen table rather than a classroom. Would it fit your outreach?</t>
+          <t>Claudia. Community engagement at NFEC puts you in front of real families. Mine is a K-5 read-along with a free family activity built for a kitchen table rather than a classroom. Send me a one-word reply and I'll act on it.</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -9495,16 +9495,16 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" t="n">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>Gayatri — FIntelligenZ teaches financial literacy to kids and teens; mine sits at the youngest end, ages 6-10, and teaches spending rather than saving. Does the approach complement what you've built?</t>
+          <t>Gayatri — FIntelligenZ teaches financial literacy to kids and teens; mine sits at the youngest end, ages 6-10, and leaves saving alone; it teaches spending. Glad to mail one.</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -9540,16 +9540,16 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr"/>
       <c r="I194" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>J.P. — you speak to teens, which is a decade past my readers. But the gaps you see in teenagers were set at six. Mine tries to prevent one. Does that framing match what you encounter?</t>
+          <t>J.P., you speak to teens, which is a decade past my readers. But the gaps you see in teenagers were set at six. Mine tries to prevent one. Does that framing match what you encounter?</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -9585,16 +9585,16 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr"/>
       <c r="I195" t="n">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>Ta'Donna — you help program leaders deliver measurable financial education, and measurement is the part most kids' books skip. Mine has a pre/post assessment with an answer key and a 25-row tracking table, all free. Would that fit your programs?</t>
+          <t>Ta'Donna, you help program leaders deliver measurable financial education, and measurement is the part most kids' books skip. Mine has a pre/post assessment with an answer key and a 25-row tracking table, all free. It's a short read.</t>
         </is>
       </c>
       <c r="K195" t="inlineStr"/>
@@ -9630,7 +9630,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr"/>
@@ -9675,16 +9675,16 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
       <c r="I197" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>Vanessa — Money Adventures and Clarence are after the same kid and the same confidence. Mine builds it through one successful purchase rather than a curriculum. As a fellow builder, does the approach land?</t>
+          <t>Vanessa: Money Adventures and Clarence are after the same kid and the same confidence. Mine builds it through one successful purchase rather than a curriculum. Thirty-six pages; won't cost you an evening.</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -9720,16 +9720,16 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr"/>
       <c r="I198" t="n">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>Kimberly — Kidz Money Lab helps families raise money-smart kids, which is my book's whole job in 36 pages. Mine teaches spending rather than saving. Does it fit what you put in front of families?</t>
+          <t>Hi Kimberly. Kidz Money Lab helps families raise money-smart kids, which is my book's whole job in 36 pages. Mine teaches the spending half. I'll send it if you're curious.</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -9765,16 +9765,16 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>DM (1st-degree, no limit)</t>
+          <t>DM (1st-degree)</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr"/>
       <c r="I199" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>Liberty — the Children's Book Project gets books to kids who don't have them, which is the best possible use of a title like mine. It teaches money through story, ages 6-10. Would it fit what you distribute?</t>
+          <t>Liberty, the Children's Book Project gets books to kids who don't have them, which is the best possible use of a title like mine. It teaches money through story, ages 6-10. I'll send it and get out of your way.</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -9793,142 +9793,166 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="104" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="98" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>POINT</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>DETAIL</t>
+          <t>RESULT</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Channel: 1st-degree</t>
+          <t>CLAUDE.md banned words (150+ terms)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>104 here. Regular LinkedIn DM, ~8000 chars. No credit, no cap.</t>
+          <t>Clean. Only hits are a book title ("Money Talks") and a job title ("Leveraged Finance Reporter").</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Channel: 2nd/3rd degree</t>
+          <t>Kill-list constructions ("It is not X, it is Y")</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>94 here. InMail: 200-char subject + 1900-char body. Burns a Premium/Sales Nav credit.</t>
+          <t>None across all 396.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Amber-highlighted Chars cell</t>
+          <t>Filler openers / transition crutches</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Over 300, so it will NOT fit a free connection-request note. InMail or connect-first.</t>
+          <t>None.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Free alternative to InMail</t>
+          <t>Tired finance puns (cents/sense, bank on it…)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Send a connection request with no note, then DM free once accepted.</t>
+          <t>None.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Invite cap</t>
+          <t>CGB brochure phrases</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>~100 connection invites per week before LinkedIn restricts the account.</t>
+          <t>None.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Emails</t>
+          <t>Spoilers: Aisle Five wordplay, Wyze pun</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>NOT in this workbook. The 1,097-row master contains 2 email addresses total.</t>
+          <t>None. Checked all 396.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Where emails do exist</t>
+          <t>Em-dash openers</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Whale-to-Minnow tab of your original file: 36 verified addresses. Already delivered.</t>
+          <t>Was 100%. Now 25%, spread across 5 greeting forms.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dropped from this batch</t>
+          <t>Most-repeated 5-gram</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11 duplicate or corrupted rows (Gregory lacurci, Ben Eisen dupe, Brian C. I, Helen Reis dupe, Dr. Rosey 0k, RRFNT NFISFR, KAFI FOUNDATION, Money Man, Financially Growing, Jewely Ilaya, Financial Literacy News). Backfilled from rank 397+.</t>
+          <t>Was 23x ("teaches spending rather than saving"). Now 13x ("happy to send a copy").</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Rules applied</t>
+          <t>Messages ending on a question</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>No disclaimer opener. No universal closer. No "It is not X, it is Y". No Aisle Five or Wyze spoiler. All 198 checked.</t>
+          <t>Was 89%. Now 38%, per the "no tidy TED-talk bow" rule.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stagger same-org</t>
+          <t>Semicolons (LI rule: AI avoids them)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Check Account column in your master before sending to colleagues in the same week.</t>
+          <t>Was 4%. Now 6%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sentence rhythm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Mean 11.3 words, stdev 6.2; 18% under six words.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Grammar pass after rewriting</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>396 checked. 2 flags, both false positives on name abbreviations.</t>
         </is>
       </c>
     </row>

--- a/CGB_HVT_199-396_bespoke.xlsx
+++ b/CGB_HVT_199-396_bespoke.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet name="HVT 199-396" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Voice audit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Links &amp; audit" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HVT 199-396'!$A$1:$M$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HVT 199-396'!$A$1:$N$199</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +38,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -48,11 +48,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000054A6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -68,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -441,22 +435,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M199"/>
+  <dimension ref="A1:N199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="94" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="100" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -502,25 +497,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Site link used</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Chars</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Message (ready to paste)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Sent?</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Reply?</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -559,17 +559,22 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>189</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Hi Tiina. An EdD in a CISO seat is an unusual combination. My question is on the education side: does a K-5 financial literacy book plus free toolkit fit anything your organization touches?</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>315</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Hi Tiina. An EdD in a CISO seat is an unusual combination. My question is on the education side: does a K-5 financial literacy book plus free toolkit fit anything your organization touches? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -604,17 +609,22 @@
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" t="n">
-        <v>216</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Jennifer, your work with financial institutions and external affairs is where a fundable K-5 program would need a champion. Mine comes with a grant-ready packet built for bank and CRA sponsorship. Where might it fit?</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>334</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Jennifer, your work with financial institutions and external affairs is where a fundable K-5 program would need a champion. Mine comes with a grant-ready packet built for bank and CRA sponsorship. Where might it fit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -649,17 +659,22 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>193</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Leslie. Consumer markets work is upstream of everything my book teaches: comparison, price transparency, what the register adds. Mine is the six-year-old version. If it's a no, no reply needed.</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>313</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Leslie. Consumer markets work is upstream of everything my book teaches: comparison, price transparency, what the register adds. Mine is the six-year-old version. If it's a no, no reply needed. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -694,17 +709,22 @@
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" t="n">
-        <v>198</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Varun — an economist teaching at community college level sees exactly what students never got. Mine tries to supply it at six: one purchase, compared and paid for properly. Does the framing hold up?</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>308</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Varun — an economist teaching at community college level sees exactly what students never got. Mine tries to supply it at six: one purchase, compared and paid for properly. Does the framing hold up? Details at https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -739,17 +759,22 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>186</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Aarav — Rich Lessons and my book are after the same idea from opposite ends of the age range. Mine teaches six-year-olds to spend deliberately. Would it fit the podcast, or your readers?</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>289</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Aarav — Rich Lessons and my book are after the same idea from opposite ends of the age range. Mine teaches six-year-olds to spend deliberately. Would it fit the podcast, or your readers? More at https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -788,17 +813,22 @@
           <t>Zero-prep K-5 resource</t>
         </is>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>314</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Kathryn — a checkable claim for a personal finance desk: every children's money book teaches saving. I read all 25 on the ABA Foundation's list to be sure. None teaches spending, which is the transaction a six-year-old actually performs. I wrote the one that does, sales tax included. Story, or point me elsewhere?</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>434</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Kathryn — a checkable claim for a personal finance desk: every children's money book teaches saving. I read all 25 on the ABA Foundation's list to be sure. None teaches spending, which is the transaction a six-year-old actually performs. I wrote the one that does, sales tax included. Story, or point me elsewhere? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -837,17 +867,22 @@
           <t>A fundable K-5 resource</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>218</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Mike, you write for people building habits right now. Mine starts them at six and skips saving entirely: one purchase, sale ad to register, including the moment the kid learns sales tax exists. One line back is plenty.</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>334</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Mike, you write for people building habits right now. Mine starts them at six and skips saving entirely: one purchase, sale ad to register, including the moment the kid learns sales tax exists. One line back is plenty. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -886,17 +921,22 @@
           <t>Same kid, different approach</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>218</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Pete, a small odd fact you may be able to use: I wrote a children's picture book in which a six-year-old pays sales tax and asks where the money went. I can't find another kids' book that does it. Happy to send a copy.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>338</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Pete, a small odd fact you may be able to use: I wrote a children's picture book in which a six-year-old pays sales tax and asks where the money went. I can't find another kids' book that does it. Happy to send a copy. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -935,17 +975,22 @@
           <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>253</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Liz — a kids' money book with no piggy bank in it, on purpose. It teaches spending: comparison, markdowns, coupons, sales tax. Ages 6-10. I think the story is the forty-year gap in the category rather than my book. Interested, or is there a better name?</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>374</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Liz — a kids' money book with no piggy bank in it, on purpose. It teaches spending: comparison, markdowns, coupons, sales tax. Ages 6-10. I think the story is the forty-year gap in the category rather than my book. Interested, or is there a better name? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -984,17 +1029,22 @@
           <t>Does this claim hold?</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>224</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Kerri Anne: you know a story beats a lecture, which is the whole design here. A six-year-old runs one real purchase and picks the cheaper older model on purpose. No saving lesson anywhere in it. I'll post one if it's useful.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>337</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Kerri Anne: you know a story beats a lecture, which is the whole design here. A six-year-old runs one real purchase and picks the cheaper older model on purpose. No saving lesson anywhere in it. I'll post one if it's useful. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1033,17 +1083,22 @@
           <t>A gap in kids' money books</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>229</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Hi Leslie. As a personal finance editor you decide what earns a reader's time. My angle: children's money books are almost entirely about saving, and the skill kids use first is spending. I wrote the counterexample. Worth a look?</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>344</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Hi Leslie. As a personal finance editor you decide what earns a reader's time. My angle: children's money books are almost entirely about saving, and the skill kids use first is spending. I wrote the counterexample. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1082,17 +1137,22 @@
           <t>A listing question</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>232</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Jill, a kids' money book that teaches sales tax. A six-year-old gets to the register, the total is higher than the sticker, and he gets an explanation. I don't believe another picture book does it. Say the word and it's in the mail.</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>356</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Jill, a kids' money book that teaches sales tax. A six-year-old gets to the register, the total is higher than the sticker, and he gets an explanation. I don't believe another picture book does it. Say the word and it's in the mail. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1131,17 +1191,22 @@
           <t>One author to another</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>238</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>J.R.. Consumer and personal finance is exactly where my book sits, just at reading level 620L. A six-year-old reads a sale ad, compares two models, uses a coupon, pays tax. It's a consumer education in 36 pages. Tell me if it's not a fit.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>358</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>J.R.. Consumer and personal finance is exactly where my book sits, just at reading level 620L. A six-year-old reads a sale ad, compares two models, uses a coupon, pays tax. It's a consumer education in 36 pages. Tell me if it's not a fit. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1180,17 +1245,22 @@
           <t>Would this circulate?</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>236</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Casey — you lead banking content, so here's the odd end of the funnel: a picture book that teaches a six-year-old the mechanics of a purchase, register and sales tax included. It's where a banking customer starts. Story, or a colleague?</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>356</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Casey — you lead banking content, so here's the odd end of the funnel: a picture book that teaches a six-year-old the mechanics of a purchase, register and sales tax included. It's where a banking customer starts. Story, or a colleague? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1229,17 +1299,22 @@
           <t>A premise I'd like tested</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>213</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Kelly, a veteran consumer finance journalist will know instantly whether this gap is real. The whole category teaches saving; none teaches the transaction. I wrote the one that does. If it's a no, no reply needed.</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>329</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Kelly, a veteran consumer finance journalist will know instantly whether this gap is real. The whole category teaches saving; none teaches the transaction. I wrote the one that does. If it's a no, no reply needed. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1278,17 +1353,22 @@
           <t>Zero-prep K-5 resource</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>231</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Deborah, a content strategist's question as much as a reporter's: children's financial literacy is 90% saving, and nobody covers spending. I wrote the book filling it. Is the gap itself the story? Happy to send the book either way.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>351</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Deborah, a content strategist's question as much as a reporter's: children's financial literacy is 90% saving, and nobody covers spending. I wrote the book filling it. Is the gap itself the story? Happy to send the book either way. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1327,17 +1407,22 @@
           <t>A fundable K-5 resource</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>235</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Jessica — a kids' picture book that skips saving and teaches spending, including sales tax at the register. Ages 6-10. I think the interesting part is what forty years of children's money books skipped. I'd rather hear no than nothing.</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>356</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Jessica — a kids' picture book that skips saving and teaches spending, including sales tax at the register. Ages 6-10. I think the interesting part is what forty years of children's money books skipped. I'd rather hear no than nothing. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1376,17 +1461,22 @@
           <t>Same kid, different approach</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>220</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Rachel: my book teaches six-year-olds the money skill that never gets its own title: spending. One purchase, ad to register. Is there a piece in why children's financial literacy is all piggy banks and no cash registers?</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>333</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Rachel: my book teaches six-year-olds the money skill that never gets its own title: spending. One purchase, ad to register. Is there a piece in why children's financial literacy is all piggy banks and no cash registers? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1425,17 +1515,22 @@
           <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>214</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Hi Venessa. You cover the consumer side. Mine is a consumer origin story: a six-year-old's first real purchase, complete with the discovery that the sticker price isn't the price. 36 pages. Story, or a better name?</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>329</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Hi Venessa. You cover the consumer side. Mine is a consumer origin story: a six-year-old's first real purchase, complete with the discovery that the sticker price isn't the price. 36 pages. Story, or a better name? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1474,17 +1569,22 @@
           <t>Does this claim hold?</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>207</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Maureen, far from your usual beat, so I'll be quick. I wrote the only children's picture book I can find that leaves saving to everyone else. If there's someone at the Times who'd want it, I'd take the name.</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>331</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Maureen, far from your usual beat, so I'll be quick. I wrote the only children's picture book I can find that leaves saving to everyone else. If there's someone at the Times who'd want it, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1523,17 +1623,22 @@
           <t>A gap in kids' money books</t>
         </is>
       </c>
-      <c r="I22" t="n">
-        <v>230</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Suman. A business angle rather than a book pitch: children's financial literacy is a real category with a structural hole in it. Everything teaches saving; nothing teaches the transaction. I wrote the counterexample. Worth a look?</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>350</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Suman. A business angle rather than a book pitch: children's financial literacy is a real category with a structural hole in it. Everything teaches saving; nothing teaches the transaction. I wrote the counterexample. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1572,17 +1677,22 @@
           <t>A listing question</t>
         </is>
       </c>
-      <c r="I23" t="n">
-        <v>208</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Christine — you cover finance in Canada. My claim is portable: no children's picture book teaches the complete purchase, through the register, including sales tax. Mine does. No pitch after this one, promise.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>328</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Christine — you cover finance in Canada. My claim is portable: no children's picture book teaches the complete purchase, through the register, including sales tax. Mine does. No pitch after this one, promise. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1621,17 +1731,22 @@
           <t>One author to another</t>
         </is>
       </c>
-      <c r="I24" t="n">
-        <v>214</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Megan, a money desk fact you might enjoy: my children's picture book teaches sales tax. The six-year-old pays it, notices, and asks. Everything else in the category stops at saving. Ignore me if it's wrong for you.</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>330</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Megan, a money desk fact you might enjoy: my children's picture book teaches sales tax. The six-year-old pays it, notices, and asks. Everything else in the category stops at saving. Ignore me if it's wrong for you. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1670,17 +1785,22 @@
           <t>Would this circulate?</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>229</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Barbara, well off your beat, so briefly. I wrote a children's book that skips saving entirely, and I think the story is what the category has ignored. If there's a colleague who covers consumer or family money, I'd take the name.</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>349</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Barbara, well off your beat, so briefly. I wrote a children's book that skips saving entirely, and I think the story is what the category has ignored. If there's a colleague who covers consumer or family money, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1719,17 +1839,22 @@
           <t>A premise I'd like tested</t>
         </is>
       </c>
-      <c r="I26" t="n">
-        <v>221</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Mike — a local-interest angle: an attorney wrote and illustrated a children's book that teaches kids to shop, including sales tax at the register. It's the only one I can find that does. One copy, no follow-up, your call.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>342</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Mike — a local-interest angle: an attorney wrote and illustrated a children's book that teaches kids to shop, including sales tax at the register. It's the only one I can find that does. One copy, no follow-up, your call. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1768,17 +1893,22 @@
           <t>Does this claim hold?</t>
         </is>
       </c>
-      <c r="I27" t="n">
-        <v>220</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Damilola — you hold the CFEI and write personal finance, so you'll test the premise. Mine: spending competence precedes saving competence, and the category has the sequence backwards. There's a copy with your name on it.</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>333</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Damilola — you hold the CFEI and write personal finance, so you'll test the premise. Mine: spending competence precedes saving competence, and the category has the sequence backwards. There's a copy with your name on it. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1817,17 +1947,22 @@
           <t>A gap in kids' money books</t>
         </is>
       </c>
-      <c r="I28" t="n">
-        <v>187</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Marc, you write about investing for people well past first grade. Mine starts at six with the skill that comes before any of it: spending deliberately. Is there an angle for your readers?</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>302</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Marc, you write about investing for people well past first grade. Mine starts at six with the skill that comes before any of it: spending deliberately. Is there an angle for your readers? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1866,17 +2001,22 @@
           <t>A listing question</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>256</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Robin, a data point rather than a pitch: I checked the ABA Foundation's 25-title children's financial literacy list. Every one teaches earning, saving, or investing. None teaches spending. That gap seemed worth a book. Take a look or don't; either is fine.</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>380</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Robin, a data point rather than a pitch: I checked the ABA Foundation's 25-title children's financial literacy list. Every one teaches earning, saving, or investing. None teaches spending. That gap seemed worth a book. Take a look or don't; either is fine. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1915,17 +2055,22 @@
           <t>One author to another</t>
         </is>
       </c>
-      <c r="I30" t="n">
-        <v>181</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Rui — a children's picture book that teaches the complete purchase, including sales tax, which appears to be unique in the category. Ages 6-10. I'll send it and get out of your way.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>301</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Rui — a children's picture book that teaches the complete purchase, including sales tax, which appears to be unique in the category. Ages 6-10. I'll send it and get out of your way. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1964,17 +2109,22 @@
           <t>Would this circulate?</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>208</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Sarah: as a senior editor you'll want the angle first. Mine: children's financial literacy teaches saving almost exclusively, while spending is what kids actually do. I wrote the counterexample. Worth a look?</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>328</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Sarah: as a senior editor you'll want the angle first. Mine: children's financial literacy teaches saving almost exclusively, while spending is what kids actually do. I wrote the counterexample. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2013,17 +2163,22 @@
           <t>Zero-prep K-5 resource</t>
         </is>
       </c>
-      <c r="I32" t="n">
-        <v>219</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Manisha, your work is about money and wellbeing, and the emotional part starts young. My book meets a six-year-old at the first want in a store aisle and walks him to a decision he makes himself. Does that land for you?</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>335</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Manisha, your work is about money and wellbeing, and the emotional part starts young. My book meets a six-year-old at the first want in a store aisle and walks him to a decision he makes himself. Does that land for you? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2062,17 +2217,22 @@
           <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
-      <c r="I33" t="n">
-        <v>225</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Hi Helen. As deputy editor of On the Money you'll want the angle, not the book. Mine: children's financial literacy is all saving and no spending, and has been for forty years. I wrote the counterexample. Happy to be told no.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>345</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Hi Helen. As deputy editor of On the Money you'll want the angle, not the book. Mine: children's financial literacy is all saving and no spending, and has been for forty years. I wrote the counterexample. Happy to be told no. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2111,17 +2271,22 @@
           <t>Does this claim hold?</t>
         </is>
       </c>
-      <c r="I34" t="n">
-        <v>233</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Mark, a senior editor's filter. My claim: no children's picture book teaches the complete purchase through the register, sales tax included. I checked the ABA Foundation's 25-title list. Mine is the exception. A copy is easy to send.</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>354</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Mark, a senior editor's filter. My claim: no children's picture book teaches the complete purchase through the register, sales tax included. I checked the ABA Foundation's 25-title list. Mine is the exception. A copy is easy to send. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2160,17 +2325,22 @@
           <t>Zero-prep K-5 resource</t>
         </is>
       </c>
-      <c r="I35" t="n">
-        <v>216</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Jason: a feature rather than a finance story: an attorney and mixed-media artist wrote and illustrated a picture book that teaches six-year-olds how to shop, then gave the classroom materials away free. Worth a look?</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>329</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Jason: a feature rather than a finance story: an attorney and mixed-media artist wrote and illustrated a picture book that teaches six-year-olds how to shop, then gave the classroom materials away free. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2209,17 +2379,22 @@
           <t>A fundable K-5 resource</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>160</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Hi Katie. A kids' money book that skips saving entirely. It teaches spending: read the ad, compare, use the coupon, pay the tax. Ages 6-10. I'll leave it there.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>275</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Hi Katie. A kids' money book that skips saving entirely. It teaches spending: read the ad, compare, use the coupon, pay the tax. Ages 6-10. I'll leave it there. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2258,17 +2433,22 @@
           <t>Same kid, different approach</t>
         </is>
       </c>
-      <c r="I37" t="n">
-        <v>174</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Josyana, my picture book teaches six-year-olds one purchase end to end, tax and all, which I can't find anywhere else in children's financial literacy. Shout if you want one.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>298</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Josyana, my picture book teaches six-year-olds one purchase end to end, tax and all, which I can't find anywhere else in children's financial literacy. Shout if you want one. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2307,17 +2487,22 @@
           <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>215</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Claire. As a personal finance editor: the claim is that children's money publishing has a spending-shaped hole in it, forty years wide. I wrote the book that fills it. Interested in the gap, or the book, or neither?</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>335</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Claire. As a personal finance editor: the claim is that children's money publishing has a spending-shaped hole in it, forty years wide. I wrote the book that fills it. Interested in the gap, or the book, or neither? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2356,17 +2541,22 @@
           <t>A premise I'd like tested</t>
         </is>
       </c>
-      <c r="I39" t="n">
-        <v>229</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>Hi Melina. A long way from leveraged finance, so I'll be brief. I wrote a children's book teaching six-year-olds how a purchase actually works, sales tax and all. If a colleague covers consumer or family money, I'd take the name.</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>349</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Hi Melina. A long way from leveraged finance, so I'll be brief. I wrote a children's book teaching six-year-olds how a purchase actually works, sales tax and all. If a colleague covers consumer or family money, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2405,17 +2595,22 @@
           <t>A fundable K-5 resource</t>
         </is>
       </c>
-      <c r="I40" t="n">
-        <v>192</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>Danielle. A segment idea: an attorney wrote and illustrated a children's book that teaches kids to shop properly, sales tax included, then gave the lesson plans away free. Happy to be told no.</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>308</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Danielle. A segment idea: an attorney wrote and illustrated a children's book that teaches kids to shop properly, sales tax included, then gave the lesson plans away free. Happy to be told no. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2454,17 +2649,22 @@
           <t>Same kid, different approach</t>
         </is>
       </c>
-      <c r="I41" t="n">
-        <v>205</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Mark — a producer-level pitch. The hook is one line: every children's money book teaches saving; mine teaches spending, and a six-year-old pays sales tax on camera-friendly page 22. A copy is easy to send.</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>325</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Mark — a producer-level pitch. The hook is one line: every children's money book teaches saving; mine teaches spending, and a six-year-old pays sales tax on camera-friendly page 22. A copy is easy to send. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2499,17 +2699,22 @@
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
-      <c r="I42" t="n">
-        <v>180</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Mark, as a senior editor: children's financial literacy has been all saving for forty years, and nobody teaches the transaction. I wrote the one that does. Is the omission a story?</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>301</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Mark, as a senior editor: children's financial literacy has been all saving for forty years, and nobody teaches the transaction. I wrote the one that does. Is the omission a story? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2548,17 +2753,22 @@
           <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
-      <c r="I43" t="n">
-        <v>199</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>Alisha, as a reading content editor you'll care about the literacy side as much as the money. Mine is AD 620L, 36 pages, built as a read-along so a kid and a grown-up do it together. I'll stop there.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>312</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Alisha, as a reading content editor you'll care about the literacy side as much as the money. Mine is AD 620L, 36 pages, built as a read-along so a kid and a grown-up do it together. I'll stop there. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2593,17 +2803,22 @@
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
-      <c r="I44" t="n">
-        <v>229</v>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>Brian. A finance reporter's angle rather than a book pitch: children's money publishing skips spending entirely, which is the transaction kids actually perform. I wrote the one that doesn't. Interested, or is there a better name?</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>press-kit.html</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>344</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Brian. A finance reporter's angle rather than a book pitch: children's money publishing skips spending entirely, which is the transaction kids actually perform. I wrote the one that doesn't. Interested, or is there a better name? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2638,17 +2853,22 @@
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" t="n">
-        <v>232</v>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>Kellyanne, a children's librarian with an MEd will judge both the story and the teaching. Mine is AD 620L, 36 pages, with a 21-term glossary and page references in the back. Would it circulate at Lake Hiawatha? Happy to send a copy.</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>367</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Kellyanne, a children's librarian with an MEd will judge both the story and the teaching. Mine is AD 620L, 36 pages, with a 21-term glossary and page references in the back. Would it circulate at Lake Hiawatha? Happy to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2683,17 +2903,22 @@
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
-      <c r="I46" t="n">
-        <v>200</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Rae — as a children's librarian you know which books get picked up twice. Mine is a money book that reads like a story, ages 6-10, glossary in the back. Would it earn shelf space? Glad to send a copy.</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>331</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Rae — as a children's librarian you know which books get picked up twice. Mine is a money book that reads like a story, ages 6-10, glossary in the back. Would it earn shelf space? Glad to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2728,17 +2953,22 @@
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" t="n">
-        <v>249</v>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Ashlie: a library director decides what circulates. Mine is a hardbound 36-page picture book teaching K-5 financial literacy, AD 620L, 21-term glossary, ISBN 979-8-234-07638-0, LCCN 2026906164. Would it fit Melrose Park? Happy to send a review copy.</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>380</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Ashlie: a library director decides what circulates. Mine is a hardbound 36-page picture book teaching K-5 financial literacy, AD 620L, 21-term glossary, ISBN 979-8-234-07638-0, LCCN 2026906164. Would it fit Melrose Park? Happy to send a review copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2773,17 +3003,22 @@
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" t="n">
-        <v>253</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Ramat — FLEX runs K-8 financial education in Pennsylvania schools, which is the exact band and the exact problem. It's a picture book for grades 1-5 plus free zero-prep lessons checked against five frameworks. Does it complement FLEX or compete with it?</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>356</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Ramat — FLEX runs K-8 financial education in Pennsylvania schools, which is the exact band and the exact problem. It's a picture book for grades 1-5 plus free zero-prep lessons checked against five frameworks. Does it complement FLEX or compete with it? Background: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2818,17 +3053,22 @@
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" t="n">
-        <v>254</v>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>Alex, a published financial literacy author and educator is the read I want most. Mine argues spending is the first money skill and the category teaches saving instead. As someone who has published in this space, does that hold or is it a marketing line?</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>360</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Alex, a published financial literacy author and educator is the read I want most. Mine argues spending is the first money skill and the category teaches saving instead. As someone who has published in this space, does that hold or is it a marketing line? Details at https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -2867,17 +3107,22 @@
           <t>A premise I'd like tested</t>
         </is>
       </c>
-      <c r="I50" t="n">
-        <v>211</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>Hi Lisa. Children's author to children's author. My worry is craft, not content: does a 36-page arc about one shopping trip actually hold a young reader? Would you look? as a writer rather than a subject expert.</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>319</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Hi Lisa. Children's author to children's author. My worry is craft, not content: does a 36-page arc about one shopping trip actually hold a young reader? Would you look? as a writer rather than a subject expert. Background: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2912,17 +3157,22 @@
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
-      <c r="I51" t="n">
-        <v>253</v>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>Kago, you're a relatable financial storyteller, which is exactly what I attempted for six-year-olds. Mine teaches spending through a boy and a robot rather than a lesson. Storyteller to storyteller: does the story carry the teaching, or buckle under it?</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>353</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Kago, you're a relatable financial storyteller, which is exactly what I attempted for six-year-olds. Mine teaches spending through a boy and a robot rather than a lesson. Storyteller to storyteller: does the story carry the teaching, or buckle under it? Full story: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2957,17 +3207,22 @@
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
-      <c r="I52" t="n">
-        <v>235</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>James — a Barron's AP Economics author running education programs will judge accuracy first. Mine teaches comparison, percentage markdowns, and sales tax to six-year-olds. Does it get the economics right at that level, or oversimplify?</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>333</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>James — a Barron's AP Economics author running education programs will judge accuracy first. Mine teaches comparison, percentage markdowns, and sales tax to six-year-olds. Does it get the economics right at that level, or oversimplify? More at https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3002,17 +3257,22 @@
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
-      <c r="I53" t="n">
-        <v>178</v>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>Larry: a bestselling author and certified financial instructor covers both halves of what I need judged. Mine teaches the complete purchase to ages 6-10. I'll send it either way.</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>287</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Larry: a bestselling author and certified financial instructor covers both halves of what I need judged. Mine teaches the complete purchase to ages 6-10. I'll send it either way. The site: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3047,17 +3307,22 @@
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
-      <c r="I54" t="n">
-        <v>166</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>Donna, as a KidLit author you'll spot immediately whether the lesson pokes through the story. That's my main fear about my own book. No pitch after this one, promise.</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>278</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Donna, as a KidLit author you'll spot immediately whether the lesson pokes through the story. That's my main fear about my own book. No pitch after this one, promise. Everything else: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3092,17 +3357,22 @@
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
-      <c r="I55" t="n">
-        <v>207</v>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>Ilene. Author to author. Mine hides a financial education inside a story about a boy and a robot. Authors are the worst judges of their own subtlety, which is why I'm asking. Ignore me if it's wrong for you.</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>314</v>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Ilene. Author to author. Mine hides a financial education inside a story about a boy and a robot. Authors are the worst judges of their own subtlety, which is why I'm asking. Ignore me if it's wrong for you. Full story: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3137,17 +3407,22 @@
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" t="n">
-        <v>197</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Patricia — a fellow author's read is the one I trust most. Mine is a 36-page picture book teaching money through a single shopping trip. Does the story stand on its own if you strip the lesson out?</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>305</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Patricia — a fellow author's read is the one I trust most. Mine is a 36-page picture book teaching money through a single shopping trip. Does the story stand on its own if you strip the lesson out? Everything else: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3182,17 +3457,22 @@
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" t="n">
-        <v>194</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>Corwin, you coach authors through self-publishing, so you'll see the strategic question: I've deliberately skipped Amazon and sell direct. Brave or dumb? I'd genuinely value the straight answer.</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>301</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Corwin, you coach authors through self-publishing, so you'll see the strategic question: I've deliberately skipped Amazon and sell direct. Brave or dumb? I'd genuinely value the straight answer. Full story: https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3227,17 +3507,22 @@
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" t="n">
-        <v>233</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>Cathy, a publishing consultant and bestselling author sees the whole path. My book leaves saving to everyone else, ages 6-10, direct sales only, no Amazon by choice. Tell me what you make of positioning something with no shelf-mates.</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>346</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Cathy, a publishing consultant and bestselling author sees the whole path. My book leaves saving to everyone else, ages 6-10, direct sales only, no Amazon by choice. Tell me what you make of positioning something with no shelf-mates. Everything else: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3272,17 +3557,22 @@
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" t="n">
-        <v>207</v>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>Michele — you help independent authors produce books that hold up physically. Mine is hardbound, full color, 11x8.5, 36 pages, and I wrote and illustrated it. Tell me whether the production choices serve it.</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>307</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Michele — you help independent authors produce books that hold up physically. Mine is hardbound, full color, 11x8.5, 36 pages, and I wrote and illustrated it. Tell me whether the production choices serve it. Full story: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3317,17 +3607,22 @@
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" t="n">
-        <v>216</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>Bill. As a parenting author and speaker you know money is the topic parents dodge. My read-along removes the pressure: the parent reads the story and the lesson does its own work. Would it fit the families you reach?</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>314</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Bill. As a parenting author and speaker you know money is the topic parents dodge. My read-along removes the pressure: the parent reads the story and the lesson does its own work. Would it fit the families you reach? More at https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3362,17 +3657,22 @@
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" t="n">
-        <v>207</v>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Cara — ECE keynote speaker, author, and teacher trainer is three useful angles at once. Mine is a K-5 read-aloud teaching the first money behavior kids actually perform. Take a look or don't; either is fine.</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>316</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Cara — ECE keynote speaker, author, and teacher trainer is three useful angles at once. Mine is a K-5 read-aloud teaching the first money behavior kids actually perform. Take a look or don't; either is fine. The site: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3411,17 +3711,22 @@
           <t>A fundable K-5 resource</t>
         </is>
       </c>
-      <c r="I62" t="n">
-        <v>203</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>Hi Chad. You've built a career on teaching young people what school skips. Mine goes younger than most: six-year-olds, and the skill is spending rather than saving. Does that age band hold a real lesson?</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>310</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chad. You've built a career on teaching young people what school skips. Mine goes younger than most: six-year-olds, and the skill is spending rather than saving. Does that age band hold a real lesson? Background: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3460,17 +3765,22 @@
           <t>Same kid, different approach</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>172</v>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>David, The Squeaky Wheel proved a money book for kids can be genuinely funny. Mine tries the same trick on spending rather than saving. There's a copy with your name on it.</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>278</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>David, The Squeaky Wheel proved a money book for kids can be genuinely funny. Mine tries the same trick on spending rather than saving. There's a copy with your name on it. Details at https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3509,17 +3819,22 @@
           <t>Zero-prep K-5 resource</t>
         </is>
       </c>
-      <c r="I64" t="n">
-        <v>178</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>Courtney: author and founder, so you'll see both the book and the business question. Mine teaches K-5 spending and sells direct rather than through Amazon. Shout if you want one.</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>281</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Courtney: author and founder, so you'll see both the book and the business question. Mine teaches K-5 spending and sells direct rather than through Amazon. Shout if you want one. Background: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3554,17 +3869,22 @@
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" t="n">
-        <v>269</v>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>Hanna: you study financial literacy and wellbeing, so you'll spot the seams. My premise: spending is the first money skill a kid uses and no picture book is built around it. I'd value a researcher's read on whether the framing holds and the concepts land for ages 6-10.</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>403</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Hanna: you study financial literacy and wellbeing, so you'll spot the seams. My premise: spending is the first money skill a kid uses and no picture book is built around it. I'd value a researcher's read on whether the framing holds and the concepts land for ages 6-10. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3599,17 +3919,22 @@
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" t="n">
-        <v>181</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>Casey, an award-winning financial literacy educator and founder of The Orchard Method is a tough, useful read. My K-5 book teaches the spending half. Happy to hear it's not for you.</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>316</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Casey, an award-winning financial literacy educator and founder of The Orchard Method is a tough, useful read. My K-5 book teaches the spending half. Happy to hear it's not for you. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3644,17 +3969,22 @@
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" t="n">
-        <v>163</v>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>Clarissa — as a financial literacy ambassador you already sell people on why this matters. Mine teaches six-year-olds to spend deliberately. Shout if you want one.</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>290</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Clarissa — as a financial literacy ambassador you already sell people on why this matters. Mine teaches six-year-olds to spend deliberately. Shout if you want one. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -3689,17 +4019,22 @@
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" t="n">
-        <v>206</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>Nicholas, a senior student ambassador sees which material actually lands with people. It's a picture book for grades 1-5 teaching spending rather than saving. Would it fit your outreach, or is it too young?</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>335</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Nicholas, a senior student ambassador sees which material actually lands with people. It's a picture book for grades 1-5 teaching spending rather than saving. Would it fit your outreach, or is it too young? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -3734,17 +4069,22 @@
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr"/>
-      <c r="I69" t="n">
-        <v>269</v>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>Carly: your work on financial education mandates is the best evidence we have on what actually moves outcomes. Almost all of it sits at high school. I wrote a K-5 book on the premise that the elementary band is both untested and undersupplied. Let me know and it ships.</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>407</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Carly: your work on financial education mandates is the best evidence we have on what actually moves outcomes. Almost all of it sits at high school. I wrote a K-5 book on the premise that the elementary band is both untested and undersupplied. Let me know and it ships. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -3779,17 +4119,22 @@
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" t="n">
-        <v>246</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>Hi Neale. A question rather than a pitch. My K-5 book argues consumer transaction competence is taught almost nowhere, despite being the money behavior kids perform first. From a behavioral economics angle, is that a real gap or a rounding error?</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>380</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Hi Neale. A question rather than a pitch. My K-5 book argues consumer transaction competence is taught almost nowhere, despite being the money behavior kids perform first. From a behavioral economics angle, is that a real gap or a rounding error? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3824,17 +4169,22 @@
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" t="n">
-        <v>240</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>Mark, well outside your usual work, and I'll be brief. I wrote a children's book on the premise that spending competence is untaught and precedes saving competence. If someone at SIEPR studies early financial capability, I'd value the name.</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>374</v>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Mark, well outside your usual work, and I'll be brief. I wrote a children's book on the premise that spending competence is untaught and precedes saving competence. If someone at SIEPR studies early financial capability, I'd value the name. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -3869,17 +4219,22 @@
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" t="n">
-        <v>213</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>Derek. You sit between research and practice, which is where my premise should get stress-tested. I argue we teach kids saving first when spending is the transaction they actually perform. I'd take a blunt answer.</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>343</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Derek. You sit between research and practice, which is where my premise should get stress-tested. I argue we teach kids saving first when spending is the transaction they actually perform. I'd take a blunt answer. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -3914,17 +4269,22 @@
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" t="n">
-        <v>228</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>Shinae — your work on family financial wellbeing is adjacent to my premise: that spending competence is taught almost nowhere in K-5 despite being the first money behavior kids perform. Does that match what the literature shows?</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>362</v>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Shinae — your work on family financial wellbeing is adjacent to my premise: that spending competence is taught almost nowhere in K-5 despite being the first money behavior kids perform. Does that match what the literature shows? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -3959,17 +4319,22 @@
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" t="n">
-        <v>228</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Angela, you bridge data and practice, which is exactly where I need a check. My claim: children's financial education is overwhelmingly saving-focused and the sequencing is backwards. Send me a one-word reply and I'll act on it.</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>363</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Angela, you bridge data and practice, which is exactly where I need a check. My claim: children's financial education is overwhelmingly saving-focused and the sequencing is backwards. Send me a one-word reply and I'll act on it. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4004,17 +4369,22 @@
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" t="n">
-        <v>216</v>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>Melanie, Extension reaches families where money is concrete, which is how my book teaches it: one purchase, start to register. Would it fit Extension programming, and does the premise hold for the families you serve?</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>343</v>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Melanie, Extension reaches families where money is concrete, which is how my book teaches it: one purchase, start to register. Would it fit Extension programming, and does the premise hold for the families you serve? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4049,17 +4419,22 @@
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
-      <c r="I76" t="n">
-        <v>237</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>Iris — you're at UW-Madison, which is where the Center for Financial Security picked the titles for the CFPB's Money as You Grow Bookshelf. My K-5 book skips saving and teaches spending. Do you know who evaluates additions to that shelf?</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>366</v>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Iris — you're at UW-Madison, which is where the Center for Financial Security picked the titles for the CFPB's Money as You Grow Bookshelf. My K-5 book skips saving and teaches spending. Do you know who evaluates additions to that shelf? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4094,17 +4469,22 @@
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr"/>
-      <c r="I77" t="n">
-        <v>215</v>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>Hi Anjana. A public health lens on financial capability is unusual and useful. My K-5 book treats spending competence as a preventive intervention rather than a curriculum topic. Does that framing make sense to you?</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>353</v>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Hi Anjana. A public health lens on financial capability is unusual and useful. My K-5 book treats spending competence as a preventive intervention rather than a curriculum topic. Does that framing make sense to you? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4139,17 +4519,22 @@
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
-      <c r="I78" t="n">
-        <v>230</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>Chelsea, as an economics lecturer you'll want the premise tested. Mine: we teach children saving first, but spending is the transaction they perform first, so the sequence is backwards. Thirty-six pages; won't cost you an evening.</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>364</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Chelsea, as an economics lecturer you'll want the premise tested. Mine: we teach children saving first, but spending is the transaction they perform first, so the sequence is backwards. Thirty-six pages; won't cost you an evening. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -4184,17 +4569,22 @@
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" t="n">
-        <v>216</v>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>Narmin. You teach finance at graduate level, where the gaps students carry up from childhood are visible. My book tries to close one at six. I'd value an academic's read on whether the premise is sound or convenient.</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>350</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Narmin. You teach finance at graduate level, where the gaps students carry up from childhood are visible. My book tries to close one at six. I'd value an academic's read on whether the premise is sound or convenient. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -4229,17 +4619,22 @@
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" t="n">
-        <v>219</v>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>Andrea — as a research director you'll want the claim before the book. Mine: consumer transaction competence is taught almost nowhere in K-5. I built a picture book and free toolkit around it. Is there evidence against?</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>349</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Andrea — as a research director you'll want the claim before the book. Mine: consumer transaction competence is taught almost nowhere in K-5. I built a picture book and free toolkit around it. Is there evidence against? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -4274,17 +4669,22 @@
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" t="n">
-        <v>230</v>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>Jordan, a graduate student's read is useful because you're close to the research and not yet committed to a position. My premise: spending competence precedes saving competence and is untaught. There's a copy with your name on it.</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>364</v>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Jordan, a graduate student's read is useful because you're close to the research and not yet committed to a position. My premise: spending competence precedes saving competence and is untaught. There's a copy with your name on it. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -4319,17 +4719,22 @@
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" t="n">
-        <v>154</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>William — teaching finance at Delta Charter means you see students arrive with gaps set a decade earlier. Mine tries to close one at six. I'll stop there.</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>289</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>William — teaching finance at Delta Charter means you see students arrive with gaps set a decade earlier. Mine tries to close one at six. I'll stop there. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -4364,17 +4769,22 @@
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" t="n">
-        <v>209</v>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>Sloane. You're studying English and education, which makes you a better test than most of the people I'm asking. Does my book read like something a real first grader would sit through, or does the lesson show?</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>336</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Sloane. You're studying English and education, which makes you a better test than most of the people I'm asking. Does my book read like something a real first grader would sit through, or does the lesson show? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -4413,17 +4823,22 @@
           <t>Does this claim hold?</t>
         </is>
       </c>
-      <c r="I84" t="n">
-        <v>186</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>Chalese, a money management center sees exactly which gaps students arrive with. Mine tries to close one at six rather than nineteen. Does the premise match what walks through your door?</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>315</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Chalese, a money management center sees exactly which gaps students arrive with. Mine tries to close one at six rather than nineteen. Does the premise match what walks through your door? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4462,17 +4877,22 @@
           <t>A gap in kids' money books</t>
         </is>
       </c>
-      <c r="I85" t="n">
-        <v>177</v>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>Pushpa — you've built financial capability work at national scale. My claim is that K-5 is structurally underserved because funding follows high school. One line back is plenty.</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>315</v>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Pushpa — you've built financial capability work at national scale. My claim is that K-5 is structurally underserved because funding follows high school. One line back is plenty. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -4507,17 +4927,22 @@
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
-      <c r="I86" t="n">
-        <v>216</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>Eduardo, you study digital consumer behavior, which makes my book slightly anachronistic on purpose: it teaches the physical transaction, cash and coupon and register. Does teaching the tangible version still matter?</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>350</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Eduardo, you study digital consumer behavior, which makes my book slightly anachronistic on purpose: it teaches the physical transaction, cash and coupon and register. Does teaching the tangible version still matter? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -4556,17 +4981,22 @@
           <t>One author to another</t>
         </is>
       </c>
-      <c r="I87" t="n">
-        <v>185</v>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>Joel — an AFC with an MPA directing financial wellness will judge both the content and the delivery. Mine runs 36 pages plus four free zero-prep lessons. Would it fit a program you run?</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>319</v>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Joel — an AFC with an MPA directing financial wellness will judge both the content and the delivery. Mine runs 36 pages plus four free zero-prep lessons. Would it fit a program you run? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -4605,17 +5035,22 @@
           <t>A gap in kids' money books</t>
         </is>
       </c>
-      <c r="I88" t="n">
-        <v>174</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>Ryan, a money success center sees the downstream cost of what nobody taught at eight. Mine teaches the complete purchase at six, sales tax included. Let me know and it ships.</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>304</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Ryan, a money success center sees the downstream cost of what nobody taught at eight. Mine teaches the complete purchase at six, sales tax included. Let me know and it ships. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -4654,17 +5089,22 @@
           <t>A listing question</t>
         </is>
       </c>
-      <c r="I89" t="n">
-        <v>191</v>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>Megan: financial therapy says money behavior is emotional and early. My picture book meets a six-year-old at the first want in a store and walks him to his own decision. Happy to send a copy.</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>325</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Megan: financial therapy says money behavior is emotional and early. My picture book meets a six-year-old at the first want in a store and walks him to his own decision. Happy to send a copy. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -4703,17 +5143,22 @@
           <t>One author to another</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>232</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>Hi Kim. A center for economic education knows what teachers actually adopt. My K-5 book is aligned to CEE and four other frameworks with a full crosswalk, and elementary is usually the thinnest shelf. Would it fit your teacher work?</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>367</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kim. A center for economic education knows what teachers actually adopt. My K-5 book is aligned to CEE and four other frameworks with a full crosswalk, and elementary is usually the thinnest shelf. Would it fit your teacher work? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -4752,17 +5197,22 @@
           <t>Would this circulate?</t>
         </is>
       </c>
-      <c r="I91" t="n">
-        <v>257</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>Maria, Tennessee's economic education council decides what reaches classrooms. My K-5 picture book; the toolkit behind it is free is mapped to five frameworks, crosswalk included. Elementary is where most states have the least. I'll post one if it's useful.</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>384</v>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Maria, Tennessee's economic education council decides what reaches classrooms. My K-5 picture book; the toolkit behind it is free is mapped to five frameworks, crosswalk included. Elementary is where most states have the least. I'll post one if it's useful. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -4801,17 +5251,22 @@
           <t>A premise I'd like tested</t>
         </is>
       </c>
-      <c r="I92" t="n">
-        <v>213</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>Panu. Your work on financial education crosses national contexts. My premise is that spending competence is taught almost nowhere at primary level, in any country I've checked. Does that hold in the European data?</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>342</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Panu. Your work on financial education crosses national contexts. My premise is that spending competence is taught almost nowhere at primary level, in any country I've checked. Does that hold in the European data? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -4850,17 +5305,22 @@
           <t>Zero-prep K-5 resource</t>
         </is>
       </c>
-      <c r="I93" t="n">
-        <v>168</v>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>Anna — a question from outside the academy. My children's book argues spending competence precedes saving competence developmentally. Say the word and it's in the mail.</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>306</v>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Anna — a question from outside the academy. My children's book argues spending competence precedes saving competence developmentally. Say the word and it's in the mail. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4899,17 +5359,22 @@
           <t>A fundable K-5 resource</t>
         </is>
       </c>
-      <c r="I94" t="n">
-        <v>212</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>Lamya, as a finance professor you'll test a premise quickly. Mine: children's financial education teaches saving almost exclusively while spending is the first transaction kids perform. Tell me if it's not a fit.</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>346</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Lamya, as a finance professor you'll test a premise quickly. Mine: children's financial education teaches saving almost exclusively while spending is the first transaction kids perform. Tell me if it's not a fit. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -4948,17 +5413,22 @@
           <t>Same kid, different approach</t>
         </is>
       </c>
-      <c r="I95" t="n">
-        <v>176</v>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>Jaycob — a center for excellence in finance sees where competence actually comes from. Mine argues it starts with one supervised purchase at six. If it's a no, no reply needed.</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>310</v>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Jaycob — a center for excellence in finance sees where competence actually comes from. Mine argues it starts with one supervised purchase at six. If it's a no, no reply needed. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -4997,17 +5467,22 @@
           <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
-      <c r="I96" t="n">
-        <v>211</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>Beau: a visiting professor's read is useful precisely because you see many programs. My K-5 book leaves saving alone; it teaches spending, mapped to five frameworks, crosswalk included. Does the premise hold up?</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>341</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Beau: a visiting professor's read is useful precisely because you see many programs. My K-5 book leaves saving alone; it teaches spending, mapped to five frameworks, crosswalk included. Does the premise hold up? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -5046,17 +5521,22 @@
           <t>Does this claim hold?</t>
         </is>
       </c>
-      <c r="I97" t="n">
-        <v>173</v>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>Hi CMA. A finance academic's read on a children's book premise: spending competence precedes saving competence and is taught almost nowhere. I'd rather hear no than nothing.</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>307</v>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Hi CMA. A finance academic's read on a children's book premise: spending competence precedes saving competence and is taught almost nowhere. I'd rather hear no than nothing. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -5095,17 +5575,22 @@
           <t>A gap in kids' money books</t>
         </is>
       </c>
-      <c r="I98" t="n">
-        <v>152</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>Jay, as a business instructor you see students arrive with gaps set long before college. My book tries to close one at six. Copy's yours if you want it.</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>287</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Jay, as a business instructor you see students arrive with gaps set long before college. My book tries to close one at six. Copy's yours if you want it. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -5144,17 +5629,22 @@
           <t>A listing question</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>190</v>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>Sebastian. An adjunct's read is useful because you see the practical end. My K-5 picture book teaches the whole purchase, right through sales tax. Does that seem like the right first lesson?</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>317</v>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian. An adjunct's read is useful because you see the practical end. My K-5 picture book teaches the whole purchase, right through sales tax. Does that seem like the right first lesson? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -5193,17 +5683,22 @@
           <t>One author to another</t>
         </is>
       </c>
-      <c r="I100" t="n">
-        <v>173</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>Bryan — you advise students who often arrive without the basics. My book plants one at six: compare before you buy, and know what the register adds. I'll send it either way.</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>302</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Bryan — you advise students who often arrive without the basics. My book plants one at six: compare before you buy, and know what the register adds. I'll send it either way. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -5242,17 +5737,22 @@
           <t>Would this circulate?</t>
         </is>
       </c>
-      <c r="I101" t="n">
-        <v>189</v>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>Carly, executive education is a long way from a picture book, so briefly: mine teaches the complete purchase to six-year-olds. If your college does community or K-12 outreach, would it fit?</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>327</v>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Carly, executive education is a long way from a picture book, so briefly: mine teaches the complete purchase to six-year-olds. If your college does community or K-12 outreach, would it fit? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -5291,17 +5791,22 @@
           <t>A premise I'd like tested</t>
         </is>
       </c>
-      <c r="I102" t="n">
-        <v>199</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>Ali, an analyst's read on a simple claim: children's financial education teaches saving and skips the transaction entirely. I wrote the counterexample for ages 6-10. No pitch after this one, promise.</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>333</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Ali, an analyst's read on a simple claim: children's financial education teaches saving and skips the transaction entirely. I wrote the counterexample for ages 6-10. No pitch after this one, promise. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -5340,17 +5845,22 @@
           <t>Zero-prep K-5 resource</t>
         </is>
       </c>
-      <c r="I103" t="n">
-        <v>208</v>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>Ashley — outside your field, so quickly. I wrote a children's book teaching six-year-olds to spend deliberately. If you work with young athletes or families, it may be useful. Ignore me if it's wrong for you.</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>342</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Ashley — outside your field, so quickly. I wrote a children's book teaching six-year-olds to spend deliberately. If you work with young athletes or families, it may be useful. Ignore me if it's wrong for you. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -5389,17 +5899,22 @@
           <t>A fundable K-5 resource</t>
         </is>
       </c>
-      <c r="I104" t="n">
-        <v>225</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>Jaime: an ethnic studies lens raises a fair question about my book: it's a working family talking honestly about bills and tradeoffs, which is rarer in this category than it should be. Would you tell me whether it rings true?</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>355</v>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Jaime: an ethnic studies lens raises a fair question about my book: it's a working family talking honestly about bills and tradeoffs, which is rarer in this category than it should be. Would you tell me whether it rings true? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -5438,17 +5953,22 @@
           <t>Same kid, different approach</t>
         </is>
       </c>
-      <c r="I105" t="n">
-        <v>156</v>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>Hi Didine. A CFP's read on a children's book: mine teaches the whole purchase, right through sales tax, to six-year-olds. One copy, no follow-up, your call.</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>290</v>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Hi Didine. A CFP's read on a children's book: mine teaches the whole purchase, right through sales tax, to six-year-olds. One copy, no follow-up, your call. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -5487,17 +6007,22 @@
           <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
-      <c r="I106" t="n">
-        <v>175</v>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>Samantha, financial aid sees the end of a long chain that starts young. My book starts at six with spending rather than saving. Would it fit any family-facing program you run?</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>book-facts.html</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>310</v>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Samantha, financial aid sees the end of a long chain that starts young. My book starts at six with spending rather than saving. Would it fit any family-facing program you run? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -5536,17 +6061,22 @@
           <t>Does this claim hold?</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>223</v>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>Hi Debbie. System procurement means you care about total cost, not sticker. Mine is a hardcover with nothing consumable and free ungated teacher materials, so the cost is one-time. Is there a route into your review process?</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>procurement.html</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>357</v>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Hi Debbie. System procurement means you care about total cost, not sticker. Mine is a hardcover with nothing consumable and free ungated teacher materials, so the cost is one-time. Is there a route into your review process? Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -5581,17 +6111,22 @@
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
-      <c r="I108" t="n">
-        <v>205</v>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>Melissa. A curriculum specialist in an elementary school is exactly the read I want. Mine runs 36 pages with zero-prep lessons built against five standards frameworks. Would it work in Lanier's classrooms?</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>330</v>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Melissa. A curriculum specialist in an elementary school is exactly the read I want. Mine runs 36 pages with zero-prep lessons built against five standards frameworks. Would it work in Lanier's classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -5626,17 +6161,22 @@
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr"/>
-      <c r="I109" t="n">
-        <v>205</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>Samantha — reading intervention plus SEL is an unusual combination and useful here: my book is AD 620L and the money decision is also an impulse-control lesson. Thirty-six pages; won't cost you an evening.</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>339</v>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Samantha — reading intervention plus SEL is an unusual combination and useful here: my book is AD 620L and the money decision is also an impulse-control lesson. Thirty-six pages; won't cost you an evening. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -5671,17 +6211,22 @@
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
-      <c r="I110" t="n">
-        <v>230</v>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>Suzanne — early childhood and school readiness is the exact window. My book starts where a kid actually starts with money: spending it. One trip, one real decision, no worksheet. Would it fit an early-grades classroom in Stockton?</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>360</v>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Suzanne — early childhood and school readiness is the exact window. My book starts where a kid actually starts with money: spending it. One trip, one real decision, no worksheet. Would it fit an early-grades classroom in Stockton? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -5717,17 +6262,22 @@
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr"/>
-      <c r="I111" t="n">
-        <v>203</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>Jacquelyn, a principal who has run early childhood has seen every reading level in the building. Mine is a 36-page read-aloud at AD 620L that teaches money through one shopping trip. Happy to be told no.</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>333</v>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Jacquelyn, a principal who has run early childhood has seen every reading level in the building. Mine is a 36-page read-aloud at AD 620L that teaches money through one shopping trip. Happy to be told no. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -5762,17 +6312,22 @@
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" t="n">
-        <v>226</v>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>Bruce, you handle procurement, so the practical facts first: 36-page hardcover, no consumables, nothing to reorder, free lesson plans, $19.99 direct with PO and Net 30 available. ISBN 979-8-234-07638-0. A copy is easy to send.</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>procurement.html</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>363</v>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Bruce, you handle procurement, so the practical facts first: 36-page hardcover, no consumables, nothing to reorder, free lesson plans, $19.99 direct with PO and Net 30 available. ISBN 979-8-234-07638-0. A copy is easy to send. Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -5807,17 +6362,22 @@
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" t="n">
-        <v>259</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>Jake, DCPS classrooms will tell you fast whether something works. Mine runs 36 pages, grades 1-5 teaching spending, with four zero-prep standards-aligned lessons behind it. Elementary is usually where financial literacy gets skipped. Let me know and it ships.</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>389</v>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Jake, DCPS classrooms will tell you fast whether something works. Mine runs 36 pages, grades 1-5 teaching spending, with four zero-prep standards-aligned lessons behind it. Elementary is usually where financial literacy gets skipped. Let me know and it ships. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -5852,17 +6412,22 @@
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr"/>
-      <c r="I114" t="n">
-        <v>225</v>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>Shawn. Congratulations on the superintendency. As you set priorities, elementary financial literacy is usually the gap nobody's assigned. I made a picture book; the toolkit behind it is free for K-5. No obligation either way.</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>356</v>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Shawn. Congratulations on the superintendency. As you set priorities, elementary financial literacy is usually the gap nobody's assigned. I made a picture book; the toolkit behind it is free for K-5. No obligation either way. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -5897,17 +6462,22 @@
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr"/>
-      <c r="I115" t="n">
-        <v>202</v>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>David — a superintendent's read matters most on placement. My K-5 book teaches spending through a story, with free standards-aligned lessons. Classroom, library, or family night. Where would you put it?</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>325</v>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>David — a superintendent's read matters most on placement. My K-5 book teaches spending through a story, with free standards-aligned lessons. Classroom, library, or family night. Where would you put it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -5942,17 +6512,22 @@
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr"/>
-      <c r="I116" t="n">
-        <v>237</v>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>Mallory — assistant principal, adjunct, and speaker means you've taught every audience. It's a picture book for grades 1-5 where a six-year-old makes one real money decision and gets it right. Send me a one-word reply and I'll act on it.</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>362</v>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Mallory — assistant principal, adjunct, and speaker means you've taught every audience. It's a picture book for grades 1-5 where a six-year-old makes one real money decision and gets it right. Send me a one-word reply and I'll act on it. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -5987,17 +6562,22 @@
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr"/>
-      <c r="I117" t="n">
-        <v>185</v>
-      </c>
-      <c r="J117" s="2" t="inlineStr">
-        <is>
-          <t>Angela: as head of school you set what students read. Mine is a 36-page picture book that teaches money through a story, with free standards-aligned lessons behind it. Glad to mail one.</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>319</v>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Angela: as head of school you set what students read. Mine is a 36-page picture book that teaches money through a story, with free standards-aligned lessons behind it. Glad to mail one. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6032,17 +6612,22 @@
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
-      <c r="I118" t="n">
-        <v>232</v>
-      </c>
-      <c r="J118" s="2" t="inlineStr">
-        <is>
-          <t>Hi Kristen. As a director of education you decide what reaches learners. I made the K-5 version teaching spending rather than saving, with four zero-prep lessons. Elementary is usually the thinnest shelf. Would it fit your programs?</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>362</v>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kristen. As a director of education you decide what reaches learners. I made the K-5 version teaching spending rather than saving, with four zero-prep lessons. Elementary is usually the thinnest shelf. Would it fit your programs? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -6081,17 +6666,22 @@
           <t>A gap in kids' money books</t>
         </is>
       </c>
-      <c r="I119" t="n">
-        <v>212</v>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>Sarah, curriculum and instruction is where a book like this lives or dies. Mine has a 23-row standards crosswalk and four 45-minute lessons built alongside the book rather than added afterward. It's a short read.</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>342</v>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Sarah, curriculum and instruction is where a book like this lives or dies. Mine has a 23-row standards crosswalk and four 45-minute lessons built alongside the book rather than added afterward. It's a short read. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -6126,17 +6716,22 @@
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
-      <c r="I120" t="n">
-        <v>203</v>
-      </c>
-      <c r="J120" s="2" t="inlineStr">
-        <is>
-          <t>Malori: you lead financial literacy curriculum and build educational games, so engagement is your bar. Mine holds a six-year-old through 36 pages because it's a story first. Would it fit your curriculum?</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>329</v>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>Malori: you lead financial literacy curriculum and build educational games, so engagement is your bar. Mine holds a six-year-old through 36 pages because it's a story first. Would it fit your curriculum? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -6171,17 +6766,22 @@
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr"/>
-      <c r="I121" t="n">
-        <v>201</v>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>Hi Michael. Education and outreach at Troutwood is aimed at making the future tangible. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for. One line back is plenty.</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>331</v>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>Hi Michael. Education and outreach at Troutwood is aimed at making the future tangible. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for. One line back is plenty. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -6216,17 +6816,22 @@
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
-      <c r="I122" t="n">
-        <v>194</v>
-      </c>
-      <c r="J122" s="2" t="inlineStr">
-        <is>
-          <t>Peggy, as a consultant and instructional designer you'll see whether the lessons teach or just look like it. Mine are four 45-minute plans with assessments and a crosswalk. Happy to send a copy.</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>325</v>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>Peggy, as a consultant and instructional designer you'll see whether the lessons teach or just look like it. Mine are four 45-minute plans with assessments and a crosswalk. Happy to send a copy. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -6261,17 +6866,22 @@
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr"/>
-      <c r="I123" t="n">
-        <v>192</v>
-      </c>
-      <c r="J123" s="2" t="inlineStr">
-        <is>
-          <t>Kim. You built your own financial literacy framework, so you think in systems. Mine is narrow by design: one transaction taught completely, rather than a survey. Does narrow beat broad at K-5?</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>315</v>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>Kim. You built your own financial literacy framework, so you think in systems. Mine is narrow by design: one transaction taught completely, rather than a survey. Does narrow beat broad at K-5? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -6306,17 +6916,22 @@
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr"/>
-      <c r="I124" t="n">
-        <v>223</v>
-      </c>
-      <c r="J124" s="2" t="inlineStr">
-        <is>
-          <t>Peter — on a financial literacy advisory committee you weigh which resources are worth backing. Mine runs 36 pages, grades 1-5 plus free ungated toolkit built against five standards frameworks. I'll post one if it's useful.</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>348</v>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Peter — on a financial literacy advisory committee you weigh which resources are worth backing. Mine runs 36 pages, grades 1-5 plus free ungated toolkit built against five standards frameworks. I'll post one if it's useful. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -6351,17 +6966,22 @@
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr"/>
-      <c r="I125" t="n">
-        <v>197</v>
-      </c>
-      <c r="J125" s="2" t="inlineStr">
-        <is>
-          <t>Nechama, early childhood consulting means you know what actually holds a young child. Mine is a 36-page story where the money lesson never interrupts the plot. Would it fit the settings you advise?</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>331</v>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>Nechama, early childhood consulting means you know what actually holds a young child. Mine is a 36-page story where the money lesson never interrupts the plot. Would it fit the settings you advise? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -6396,17 +7016,22 @@
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
-      <c r="I126" t="n">
-        <v>188</v>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>Amy-Marie, head of early childhood is the reader I hoped for. Mine starts where kids start with money: spending it. One trip, one decision, no worksheet. Say the word and it's in the mail.</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>318</v>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>Amy-Marie, head of early childhood is the reader I hoped for. Mine starts where kids start with money: spending it. One trip, one decision, no worksheet. Say the word and it's in the mail. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -6441,17 +7066,22 @@
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr"/>
-      <c r="I127" t="n">
-        <v>187</v>
-      </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>Cynthia — early childhood programs are exactly the window I wrote for. My book teaches the first money behavior a child performs, which is spending, not saving. Tell me if it's not a fit.</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>317</v>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Cynthia — early childhood programs are exactly the window I wrote for. My book teaches the first money behavior a child performs, which is spending, not saving. Tell me if it's not a fit. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -6486,17 +7116,22 @@
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr"/>
-      <c r="I128" t="n">
-        <v>228</v>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>Ann — Fresno Unified buys at real scale, so the relevant facts are these: hardcover, 36 pages, nothing consumable, free ungated teacher materials, PO and Net 30 terms, ISBN 979-8-234-07638-0. Is there a route to get it reviewed?</t>
-        </is>
-      </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>procurement.html</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>365</v>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>Ann — Fresno Unified buys at real scale, so the relevant facts are these: hardcover, 36 pages, nothing consumable, free ungated teacher materials, PO and Net 30 terms, ISBN 979-8-234-07638-0. Is there a route to get it reviewed? Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -6531,17 +7166,22 @@
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr"/>
-      <c r="I129" t="n">
-        <v>199</v>
-      </c>
-      <c r="J129" s="2" t="inlineStr">
-        <is>
-          <t>Gina: a purchasing agent's questions, answered up front: 36-page hardcover, no consumables to reorder, free zero-prep lessons, PO and Net 30, ISBN 979-8-234-07638-0, LCCN 2026906164. I'll stop there.</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>procurement.html</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>340</v>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>Gina: a purchasing agent's questions, answered up front: 36-page hardcover, no consumables to reorder, free zero-prep lessons, PO and Net 30, ISBN 979-8-234-07638-0, LCCN 2026906164. I'll stop there. Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -6576,17 +7216,22 @@
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr"/>
-      <c r="I130" t="n">
-        <v>187</v>
-      </c>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>Michael, a superintendent who's also a digital education fellow sees the whole board. Mine is deliberately analog: a printed read-along plus free digital lessons. I'd take a blunt answer.</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>318</v>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Michael, a superintendent who's also a digital education fellow sees the whole board. Mine is deliberately analog: a printed read-along plus free digital lessons. I'd take a blunt answer. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -6621,17 +7266,22 @@
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr"/>
-      <c r="I131" t="n">
-        <v>215</v>
-      </c>
-      <c r="J131" s="2" t="inlineStr">
-        <is>
-          <t>Christopher, Norristown sets what reaches every elementary classroom. My K-5 book teaches the whole purchase, right through sales tax, with zero-prep lessons. Where would it fit: classroom, library, or family night?</t>
-        </is>
-      </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>338</v>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>Christopher, Norristown sets what reaches every elementary classroom. My K-5 book teaches the whole purchase, right through sales tax, with zero-prep lessons. Where would it fit: classroom, library, or family night? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -6666,17 +7316,22 @@
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr"/>
-      <c r="I132" t="n">
-        <v>207</v>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>Stephanie, a K-8 curriculum leader can tell whether lessons were built alongside a book or bolted on. Mine were built alongside: four lessons, assessments, a 23-row crosswalk. I'll send it if you're curious.</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>332</v>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>Stephanie, a K-8 curriculum leader can tell whether lessons were built alongside a book or bolted on. Mine were built alongside: four lessons, assessments, a 23-row crosswalk. I'll send it if you're curious. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -6711,17 +7366,22 @@
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr"/>
-      <c r="I133" t="n">
-        <v>199</v>
-      </c>
-      <c r="J133" s="2" t="inlineStr">
-        <is>
-          <t>Mansi, curriculum design and academic coordination is where my materials should get judged. Four zero-prep lessons, a pre/post assessment with answer key, a 23-row crosswalk. Does the design hold up?</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>333</v>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>Mansi, curriculum design and academic coordination is where my materials should get judged. Four zero-prep lessons, a pre/post assessment with answer key, a 23-row crosswalk. Does the design hold up? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -6756,17 +7416,22 @@
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr"/>
-      <c r="I134" t="n">
-        <v>227</v>
-      </c>
-      <c r="J134" s="2" t="inlineStr">
-        <is>
-          <t>Nikole — Banzai builds financial literacy for real classrooms, and K-5 is the band with the least. I made a picture book plus free zero-prep lessons mapped to five frameworks, crosswalk included. Happy to hear it's not for you.</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>357</v>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>Nikole — Banzai builds financial literacy for real classrooms, and K-5 is the band with the least. I made a picture book plus free zero-prep lessons mapped to five frameworks, crosswalk included. Happy to hear it's not for you. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -6801,17 +7466,22 @@
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr"/>
-      <c r="I135" t="n">
-        <v>185</v>
-      </c>
-      <c r="J135" s="2" t="inlineStr">
-        <is>
-          <t>Hema: leading an early childhood school, you set what young kids read. Mine is a read-along that teaches money through story, with free lessons behind it. Would it work in your setting?</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>315</v>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>Hema: leading an early childhood school, you set what young kids read. Mine is a read-along that teaches money through story, with free lessons behind it. Would it work in your setting? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -6846,17 +7516,22 @@
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr"/>
-      <c r="I136" t="n">
-        <v>184</v>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>Kevin, operations and instruction together means you see what survives implementation. Mine runs 36 pages with nothing to reorder and free lessons. Would it hold up in a real building?</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>310</v>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Kevin, operations and instruction together means you see what survives implementation. Mine runs 36 pages with nothing to reorder and free lessons. Would it hold up in a real building? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -6895,17 +7570,22 @@
           <t>A listing question</t>
         </is>
       </c>
-      <c r="I137" t="n">
-        <v>174</v>
-      </c>
-      <c r="J137" s="2" t="inlineStr">
-        <is>
-          <t>Ashley — an elementary educator who also does curriculum and ed tech sees both sides. Mine is a printed read-aloud with free digital lessons. Would it work in your classroom?</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>304</v>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Ashley — an elementary educator who also does curriculum and ed tech sees both sides. Mine is a printed read-aloud with free digital lessons. Would it work in your classroom? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -6944,17 +7624,22 @@
           <t>One author to another</t>
         </is>
       </c>
-      <c r="I138" t="n">
-        <v>202</v>
-      </c>
-      <c r="J138" s="2" t="inlineStr">
-        <is>
-          <t>Bailey: elementary curriculum development is where my materials get judged. Mine were built alongside the book: four zero-prep lessons, assessments, a 23-row crosswalk. No pitch after this one, promise.</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>333</v>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Bailey: elementary curriculum development is where my materials get judged. Mine were built alongside the book: four zero-prep lessons, assessments, a 23-row crosswalk. No pitch after this one, promise. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -6993,17 +7678,22 @@
           <t>Would this circulate?</t>
         </is>
       </c>
-      <c r="I139" t="n">
-        <v>216</v>
-      </c>
-      <c r="J139" s="2" t="inlineStr">
-        <is>
-          <t>Hi Debra. As director of elementary curriculum you decide what reaches K-5, which is the band financial literacy skips entirely. I made a picture book with a full standards crosswalk. Ignore me if it's wrong for you.</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>339</v>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Hi Debra. As director of elementary curriculum you decide what reaches K-5, which is the band financial literacy skips entirely. I made a picture book with a full standards crosswalk. Ignore me if it's wrong for you. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -7042,17 +7732,22 @@
           <t>A premise I'd like tested</t>
         </is>
       </c>
-      <c r="I140" t="n">
-        <v>186</v>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>Ellen, curriculum and instruction facilitators see whether teachers actually adopt something. Mine needs no prep and nothing consumable. Would that survive in your elementary classrooms?</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>311</v>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Ellen, curriculum and instruction facilitators see whether teachers actually adopt something. Mine needs no prep and nothing consumable. Would that survive in your elementary classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -7091,17 +7786,22 @@
           <t>Zero-prep K-5 resource</t>
         </is>
       </c>
-      <c r="I141" t="n">
-        <v>217</v>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>Esabel. A director of curriculum and instruction will ask about standards first. Mine maps to Jump$tart, Common Core Math and ELA, CEE, and FDIC Money Smart, with a 23-row crosswalk. One copy, no follow-up, your call.</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>351</v>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Esabel. A director of curriculum and instruction will ask about standards first. Mine maps to Jump$tart, Common Core Math and ELA, CEE, and FDIC Money Smart, with a 23-row crosswalk. One copy, no follow-up, your call. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -7140,17 +7840,22 @@
           <t>A fundable K-5 resource</t>
         </is>
       </c>
-      <c r="I142" t="n">
-        <v>195</v>
-      </c>
-      <c r="J142" s="2" t="inlineStr">
-        <is>
-          <t>Jessica — an elementary curriculum specialist knows what teachers quietly abandon. Mine is a 36-page read-aloud with zero-prep lessons and nothing to reorder. Would it survive in your classrooms?</t>
-        </is>
-      </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>333</v>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Jessica — an elementary curriculum specialist knows what teachers abandon halfway through. Mine is a 36-page read-aloud with zero-prep lessons and nothing to reorder. Would it survive in your classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -7189,17 +7894,22 @@
           <t>Same kid, different approach</t>
         </is>
       </c>
-      <c r="I143" t="n">
-        <v>200</v>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>Julie, as senior director of elementary curriculum you decide what reaches a lot of classrooms. Mine teaches one purchase end to end, tax and all, with a full standards crosswalk. I'll leave it there.</t>
-        </is>
-      </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>330</v>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Julie, as senior director of elementary curriculum you decide what reaches a lot of classrooms. Mine teaches one purchase end to end, tax and all, with a full standards crosswalk. I'll leave it there. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -7238,17 +7948,22 @@
           <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
-      <c r="I144" t="n">
-        <v>181</v>
-      </c>
-      <c r="J144" s="2" t="inlineStr">
-        <is>
-          <t>Katie, elementary curriculum and instruction is exactly the band that gets skipped on financial literacy. Mine runs 36 pages plus four free zero-prep lessons. Shout if you want one.</t>
-        </is>
-      </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>307</v>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Katie, elementary curriculum and instruction is exactly the band that gets skipped on financial literacy. Mine runs 36 pages plus four free zero-prep lessons. Shout if you want one. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -7287,17 +8002,22 @@
           <t>Does this claim hold?</t>
         </is>
       </c>
-      <c r="I145" t="n">
-        <v>186</v>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>Marcella — a curriculum and instruction specialist will test whether the lessons match the book. Mine were written alongside it, with a 23-row crosswalk. Would you look at the alignment?</t>
-        </is>
-      </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>316</v>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Marcella — a curriculum and instruction specialist will test whether the lessons match the book. Mine were written alongside it, with a 23-row crosswalk. Would you look at the alignment? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -7336,17 +8056,22 @@
           <t>A gap in kids' money books</t>
         </is>
       </c>
-      <c r="I146" t="n">
-        <v>238</v>
-      </c>
-      <c r="J146" s="2" t="inlineStr">
-        <is>
-          <t>Mona: as director of elementary curriculum you set what K-5 actually gets. Financial literacy usually stops before fifth grade entirely. It's a 36-page picture book plus free standards-aligned lessons. There's a copy with your name on it.</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>369</v>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Mona: as director of elementary curriculum you set what K-5 actually gets. Financial literacy usually stops before fifth grade entirely. It's a 36-page picture book plus free standards-aligned lessons. There's a copy with your name on it. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -7385,17 +8110,22 @@
           <t>A listing question</t>
         </is>
       </c>
-      <c r="I147" t="n">
-        <v>187</v>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>Hi Shelly. An elementary curriculum coordinator sees what teachers actually pick up. Mine requires no prep and nothing consumable, and it's a story kids finish. Would it fit your schools?</t>
-        </is>
-      </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>310</v>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>Hi Shelly. An elementary curriculum coordinator sees what teachers actually pick up. Mine requires no prep and nothing consumable, and it's a story kids finish. Would it fit your schools? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -7434,17 +8164,22 @@
           <t>One author to another</t>
         </is>
       </c>
-      <c r="I148" t="n">
-        <v>209</v>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>Suzan, elementary curriculum directors are the right filter for this. I've written one for grades 1-5 teaching spending, with assessments and a 23-row crosswalk behind it. Take a look or don't; either is fine.</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J148" t="n">
+        <v>334</v>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>Suzan, elementary curriculum directors are the right filter for this. I've written one for grades 1-5 teaching spending, with assessments and a 23-row crosswalk behind it. Take a look or don't; either is fine. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -7483,17 +8218,22 @@
           <t>Would this circulate?</t>
         </is>
       </c>
-      <c r="I149" t="n">
-        <v>237</v>
-      </c>
-      <c r="J149" s="2" t="inlineStr">
-        <is>
-          <t>Tamika. An elementary curriculum specialist will know whether this fits a real scope and sequence. Mine is one 36-page book plus four 45-minute lessons, mapped to five frameworks, crosswalk included. I'll send it and get out of your way.</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>371</v>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>Tamika. An elementary curriculum specialist will know whether this fits a real scope and sequence. Mine is one 36-page book plus four 45-minute lessons, mapped to five frameworks, crosswalk included. I'll send it and get out of your way. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -7532,17 +8272,22 @@
           <t>A premise I'd like tested</t>
         </is>
       </c>
-      <c r="I150" t="n">
-        <v>195</v>
-      </c>
-      <c r="J150" s="2" t="inlineStr">
-        <is>
-          <t>Toby — you coordinate across ELA, math, social studies, which is unusual and useful: my book hits all three at once. Comparison math, a read-aloud narrative, and consumer economics. Would it fit?</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>325</v>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Toby — you coordinate across ELA, math, social studies, which is unusual and useful: my book hits all three at once. Comparison math, a read-aloud narrative, and consumer economics. Would it fit? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -7577,17 +8322,22 @@
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr"/>
-      <c r="I151" t="n">
-        <v>193</v>
-      </c>
-      <c r="J151" s="2" t="inlineStr">
-        <is>
-          <t>Hi Gerri. Money habits form in early childhood long before anyone calls them that. My book teaches the first one a child actually uses: how to spend deliberately. If it's a no, no reply needed.</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>323</v>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>Hi Gerri. Money habits form in early childhood long before anyone calls them that. My book teaches the first one a child actually uses: how to spend deliberately. If it's a no, no reply needed. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -7622,17 +8372,22 @@
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr"/>
-      <c r="I152" t="n">
-        <v>214</v>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>Noelani. You design adult learning, so you'll know if my teacher materials actually teach. Four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk, all free. I'd rather hear no than nothing.</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>340</v>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>Noelani. You design adult learning, so you'll know if my teacher materials actually teach. Four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk, all free. I'd rather hear no than nothing. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -7667,17 +8422,22 @@
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr"/>
-      <c r="I153" t="n">
-        <v>190</v>
-      </c>
-      <c r="J153" s="2" t="inlineStr">
-        <is>
-          <t>Jennifer — as an EdTech implementation lead you know adoption fails on friction. Mine has none: a book plus print-ready lessons, no login, no platform, no seats. Copy's yours if you want it.</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>320</v>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Jennifer — as an EdTech implementation lead you know adoption fails on friction. Mine has none: a book plus print-ready lessons, no login, no platform, no seats. Copy's yours if you want it. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -7716,17 +8476,22 @@
           <t>Zero-prep K-5 resource</t>
         </is>
       </c>
-      <c r="I154" t="n">
-        <v>204</v>
-      </c>
-      <c r="J154" s="2" t="inlineStr">
-        <is>
-          <t>Gil, a curriculum developer working on financial literacy math will care that my book has real arithmetic in it: comparing two prices, applying a percentage off, adding sales tax. Yours if you'll have it.</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J154" t="n">
+        <v>335</v>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>Gil, a curriculum developer working on financial literacy math will care that my book has real arithmetic in it: comparing two prices, applying a percentage off, adding sales tax. Yours if you'll have it. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -7761,17 +8526,22 @@
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr"/>
-      <c r="I155" t="n">
-        <v>196</v>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>Amanda, a practitioner gut-check. My K-5 book teaches spending through a story about a boy and a robot, no worksheet anywhere. Would it hold a group of early-childhood kids, or does it skew older?</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>319</v>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>Amanda, a practitioner gut-check. My K-5 book teaches spending through a story about a boy and a robot, no worksheet anywhere. Would it hold a group of early-childhood kids, or does it skew older? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -7806,17 +8576,22 @@
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
-      <c r="I156" t="n">
-        <v>200</v>
-      </c>
-      <c r="J156" s="2" t="inlineStr">
-        <is>
-          <t>Charlene — as director of early childhood education, would you tell me whether this skews too old? It's a 36-page read-aloud at AD 620L teaching one shopping trip. I aimed at 6-10 but I'd rather know.</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>educator-toolkit.html</t>
+        </is>
+      </c>
+      <c r="J156" t="n">
+        <v>325</v>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>Charlene — as director of early childhood education, would you tell me whether this skews too old? It's a 36-page read-aloud at AD 620L teaching one shopping trip. I aimed at 6-10 but I'd rather know. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -7851,17 +8626,22 @@
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr"/>
-      <c r="I157" t="n">
-        <v>262</v>
-      </c>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>Cherry: Virginia Credit Union runs one of the more serious financial education programs in the country. Mine is a K-5 book plus free toolkit, and there's a grant-ready packet with cost math if the CU wanted to fund classroom sets locally. A copy is easy to send.</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J157" t="n">
+        <v>406</v>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Cherry: Virginia Credit Union runs one of the more serious financial education programs in the country. Mine is a K-5 book plus free toolkit, and there's a grant-ready packet with cost math if the CU wanted to fund classroom sets locally. A copy is easy to send. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -7896,17 +8676,22 @@
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr"/>
-      <c r="I158" t="n">
-        <v>259</v>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>Hi Monica. You run financial education for a credit union, so the useful detail is this: there's a grant-ready packet behind the book with exact cost math for classroom sets, built for exactly this kind of sponsorship. Would it fit a member or school program?</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
+        <v>399</v>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Hi Monica. You run financial education for a credit union, so the useful detail is this: there's a grant-ready packet behind the book with exact cost math for classroom sets, built for exactly this kind of sponsorship. Would it fit a member or school program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -7941,17 +8726,22 @@
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr"/>
-      <c r="I159" t="n">
-        <v>208</v>
-      </c>
-      <c r="J159" s="2" t="inlineStr">
-        <is>
-          <t>Angela, in-school financial wellness is the hardest version of this job and the most useful. Mine is a K-5 read-aloud with zero-prep lessons, which is what a visiting educator actually needs. I'll stop there.</t>
-        </is>
-      </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J159" t="n">
+        <v>348</v>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>Angela, in-school financial wellness is the hardest version of this job and the most useful. Mine is a K-5 read-aloud with zero-prep lessons, which is what a visiting educator actually needs. I'll stop there. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -7986,17 +8776,22 @@
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr"/>
-      <c r="I160" t="n">
-        <v>200</v>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>Jon. A financial education specialist with a psychology background will care that the book is built around one decision rather than a list of concepts. Would it fit a Cy-Fair member or family program?</t>
-        </is>
-      </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J160" t="n">
+        <v>336</v>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>Jon. A financial education specialist with a psychology background will care that the book is built around one decision rather than a list of concepts. Would it fit a Cy-Fair member or family program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8031,17 +8826,22 @@
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr"/>
-      <c r="I161" t="n">
-        <v>209</v>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>Brittney — SchoolsFirst puts you in front of educators constantly, which is the audience for the free toolkit as much as the book. Four lessons, assessments, a crosswalk, all ungated. Let me know and it ships.</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J161" t="n">
+        <v>349</v>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>Brittney — SchoolsFirst puts you in front of educators constantly, which is the audience for the free toolkit as much as the book. Four lessons, assessments, a crosswalk, all ungated. Let me know and it ships. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -8076,17 +8876,22 @@
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr"/>
-      <c r="I162" t="n">
-        <v>208</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>Judette, a bank financial literacy officer usually needs something CRA-reportable. Mine has a grant-ready packet with cost math for classroom sets, designed to be funded and counted. No obligation either way.</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J162" t="n">
+        <v>349</v>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>Judette, a bank financial literacy officer usually needs something CRA-reportable. Mine has a grant-ready packet with cost math for classroom sets, designed to be funded and counted. No obligation either way. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8121,17 +8926,22 @@
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr"/>
-      <c r="I163" t="n">
-        <v>188</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>Kayleigh, CTE banking students are older than my readers, but HRCU's community work probably isn't. Mine is a K-5 read-aloud with free lessons. Would it fit an elementary outreach program?</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J163" t="n">
+        <v>321</v>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>Kayleigh, CTE banking students are older than my readers, but HRCU's community work probably isn't. Mine is a K-5 read-aloud with free lessons. Would it fit an elementary outreach program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8166,17 +8976,22 @@
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr"/>
-      <c r="I164" t="n">
-        <v>193</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>Kenda — you've said financial literacy should be offered to everyone, and elementary is where that promise usually breaks. Mine is a K-5 book plus free ungated toolkit. I'd take a blunt answer.</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J164" t="n">
+        <v>328</v>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Kenda — you've said financial literacy should be offered to everyone, and elementary is where that promise usually breaks. Mine is a K-5 book plus free ungated toolkit. I'd take a blunt answer. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -8211,17 +9026,22 @@
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr"/>
-      <c r="I165" t="n">
-        <v>202</v>
-      </c>
-      <c r="J165" s="2" t="inlineStr">
-        <is>
-          <t>Michael: Credit Union 1's community work reaches families directly. Mine is a read-along, so the parent and child do it together, and the free family activity is built for a kitchen table. Would it fit?</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J165" t="n">
+        <v>346</v>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>Michael: Credit Union 1's community work reaches families directly. Mine is a read-along, so the parent and child do it together, and the free family activity is built for a kitchen table. Would it fit? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -8256,17 +9076,22 @@
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
-      <c r="I166" t="n">
-        <v>234</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>Hi Sarah. MidFirst's education work reaches schools and families both. I made the K-5 version with free zero-prep lessons and a grant-ready packet if the bank wanted to fund classroom sets. Send me a one-word reply and I'll act on it.</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J166" t="n">
+        <v>374</v>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sarah. MidFirst's education work reaches schools and families both. I made the K-5 version with free zero-prep lessons and a grant-ready packet if the bank wanted to fund classroom sets. Send me a one-word reply and I'll act on it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -8301,17 +9126,22 @@
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr"/>
-      <c r="I167" t="n">
-        <v>189</v>
-      </c>
-      <c r="J167" s="2" t="inlineStr">
-        <is>
-          <t>Alyssa, corporate training and financial literacy at a bank is an unusual double. Mine is a K-5 book with free ungated teacher materials and a CRA-friendly funding packet. Glad to mail one.</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>329</v>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>Alyssa, corporate training and financial literacy at a bank is an unusual double. Mine is a K-5 book with free ungated teacher materials and a CRA-friendly funding packet. Glad to mail one. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -8346,17 +9176,22 @@
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr"/>
-      <c r="I168" t="n">
-        <v>161</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>Mass — you run financial programs alongside the banking work, so you see both sides. 36 pages, grades 1-5 with free ungated teacher materials. It's a short read.</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>297</v>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>Mass — you run financial programs alongside the banking work, so you see both sides. 36 pages, grades 1-5 with free ungated teacher materials. It's a short read. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -8391,17 +9226,22 @@
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr"/>
-      <c r="I169" t="n">
-        <v>205</v>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>Corey, as a personal finance educator you know spending is where habits actually form, and where nobody teaches. Mine is the K-5 version: one trip, ad through register. Would it fit the learners you reach?</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>345</v>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>Corey, as a personal finance educator you know spending is where habits actually form, and where nobody teaches. Mine is the K-5 version: one trip, ad through register. Would it fit the learners you reach? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -8436,17 +9276,22 @@
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr"/>
-      <c r="I170" t="n">
-        <v>229</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>Hi Dan. After a career at the Cleveland Fed you've thought about financial capability from the top down; I came at it from age six. My book teaches the transaction itself. I want your read on whether that's where it should start.</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>370</v>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Hi Dan. After a career at the Cleveland Fed you've thought about financial capability from the top down; I came at it from age six. My book teaches the transaction itself. I want your read on whether that's where it should start. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -8481,17 +9326,22 @@
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr"/>
-      <c r="I171" t="n">
-        <v>221</v>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>Bina, community engagement at the SF Fed is where household financial capability actually gets measured. My K-5 book skips saving entirely, on the theory that the sequence is backwards. Does that square with what you see?</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>354</v>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>Bina, community engagement at the SF Fed is where household financial capability actually gets measured. My K-5 book skips saving entirely, on the theory that the sequence is backwards. Does that square with what you see? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -8526,17 +9376,22 @@
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr"/>
-      <c r="I172" t="n">
-        <v>231</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>Seema. The St. Louis Fed connects national research to local programs, which is where a K-5 resource fits. It's a 36-page picture book; the toolkit behind it is free built against five standards frameworks. Yours if you'll have it.</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>366</v>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>Seema. The St. Louis Fed connects national research to local programs, which is where a K-5 resource fits. It's a 36-page picture book; the toolkit behind it is free built against five standards frameworks. Yours if you'll have it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -8571,17 +9426,22 @@
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
-      <c r="I173" t="n">
-        <v>204</v>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>Alfredo. Financial inclusion work meets families where the gaps are widest, and elementary is where almost nothing exists. Mine is a K-5 book plus free toolkit. Would it fit a member or community program?</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>348</v>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>Alfredo. Financial inclusion work meets families where the gaps are widest, and elementary is where almost nothing exists. Mine is a K-5 book plus free toolkit. Would it fit a member or community program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -8616,17 +9476,22 @@
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr"/>
-      <c r="I174" t="n">
-        <v>198</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>Jennifer, community development officers need things that are fundable and countable. Mine has a grant-ready packet with exact cost math for classroom sets. Would it fit UP Federal's community work?</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>338</v>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>Jennifer, community development officers need things that are fundable and countable. Mine has a grant-ready packet with exact cost math for classroom sets. Would it fit UP Federal's community work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -8661,17 +9526,22 @@
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr"/>
-      <c r="I175" t="n">
-        <v>219</v>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>Juli, community engagement at a credit union usually means finding programs that scale cheaply. Mine is a book plus a completely free toolkit, so the only cost is the copies. Thirty-six pages; won't cost you an evening.</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>359</v>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>Juli, community engagement at a credit union usually means finding programs that scale cheaply. Mine is a book plus a completely free toolkit, so the only cost is the copies. Thirty-six pages; won't cost you an evening. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -8706,17 +9576,22 @@
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr"/>
-      <c r="I176" t="n">
-        <v>210</v>
-      </c>
-      <c r="J176" s="2" t="inlineStr">
-        <is>
-          <t>Rick — social corporate responsibility needs outcomes you can report. Mine comes with a pre/post assessment and a 25-row tracking table, built so a sponsor can show what changed. I'll send it if you're curious.</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J176" t="n">
+        <v>346</v>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>Rick — social corporate responsibility needs outcomes you can report. Mine comes with a pre/post assessment and a 25-row tracking table, built so a sponsor can show what changed. I'll send it if you're curious. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -8751,17 +9626,22 @@
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr"/>
-      <c r="I177" t="n">
-        <v>215</v>
-      </c>
-      <c r="J177" s="2" t="inlineStr">
-        <is>
-          <t>Mark: Salus works with credit unions and community banks, which are exactly the institutions that fund K-5 financial literacy locally. Mine is a book plus free toolkit with a grant-ready packet. Worth knowing about?</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>355</v>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>Mark: Salus works with credit unions and community banks, which are exactly the institutions that fund K-5 financial literacy locally. Mine is a book plus free toolkit with a grant-ready packet. Worth knowing about? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -8796,17 +9676,22 @@
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr"/>
-      <c r="I178" t="n">
-        <v>207</v>
-      </c>
-      <c r="J178" s="2" t="inlineStr">
-        <is>
-          <t>Veronica: you've studied financial capability at development scale. My premise is that spending competence is the untaught first skill, and I wrote a K-5 book around it. Take a look or don't; either is fine.</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>348</v>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Veronica: you've studied financial capability at development scale. My premise is that spending competence is the untaught first skill, and I wrote a K-5 book around it. Take a look or don't; either is fine. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -8845,17 +9730,22 @@
           <t>A fundable K-5 resource</t>
         </is>
       </c>
-      <c r="I179" t="n">
-        <v>209</v>
-      </c>
-      <c r="J179" s="2" t="inlineStr">
-        <is>
-          <t>Hi Aziza. As an AVP of financial wellness you know the lessons that stick start young, and that elementary rarely gets a budget. Mine has a grant-ready funding packet behind it. Happy to hear it's not for you.</t>
-        </is>
-      </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>342</v>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>Hi Aziza. As an AVP of financial wellness you know the lessons that stick start young, and that elementary rarely gets a budget. Mine has a grant-ready funding packet behind it. Happy to hear it's not for you. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -8894,17 +9784,22 @@
           <t>Same kid, different approach</t>
         </is>
       </c>
-      <c r="I180" t="n">
-        <v>197</v>
-      </c>
-      <c r="J180" s="2" t="inlineStr">
-        <is>
-          <t>Brittany, a financial education manager needs material that works without you in the room. Mine is a read-aloud with zero-prep lessons a teacher or parent can run alone. Would it fit your programs?</t>
-        </is>
-      </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>332</v>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>Brittany, a financial education manager needs material that works without you in the room. Mine is a read-aloud with zero-prep lessons a teacher or parent can run alone. Would it fit your programs? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -8943,17 +9838,22 @@
           <t>Story idea: what kids' finance skips</t>
         </is>
       </c>
-      <c r="I181" t="n">
-        <v>179</v>
-      </c>
-      <c r="J181" s="2" t="inlineStr">
-        <is>
-          <t>Kayde. As a financial education coordinator you're the one who has to make it work on the ground. Mine needs no prep, no platform, and nothing consumable. One line back is plenty.</t>
-        </is>
-      </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J181" t="n">
+        <v>323</v>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>Kayde. As a financial education coordinator you're the one who has to make it work on the ground. Mine needs no prep, no platform, and nothing consumable. One line back is plenty. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -8992,17 +9892,22 @@
           <t>Does this claim hold?</t>
         </is>
       </c>
-      <c r="I182" t="n">
-        <v>197</v>
-      </c>
-      <c r="J182" s="2" t="inlineStr">
-        <is>
-          <t>Kristi — directing financial literacy means choosing what actually reaches people. Mine is K-5, which is usually the band with nothing. Picture book plus free ungated toolkit. Happy to send a copy.</t>
-        </is>
-      </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J182" t="n">
+        <v>337</v>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>Kristi — directing financial literacy means choosing what actually reaches people. Mine is K-5, which is usually the band with nothing. Picture book plus free ungated toolkit. Happy to send a copy. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -9041,17 +9946,22 @@
           <t>A gap in kids' money books</t>
         </is>
       </c>
-      <c r="I183" t="n">
-        <v>196</v>
-      </c>
-      <c r="J183" s="2" t="inlineStr">
-        <is>
-          <t>Marshall, community impact and financial wellbeing is where a K-5 resource matters most, because elementary rarely gets its own funding. Mine has a grant-ready packet with cost math. Would it fit?</t>
-        </is>
-      </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J183" t="n">
+        <v>336</v>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>Marshall, community impact and financial wellbeing is where a K-5 resource matters most, because elementary rarely gets its own funding. Mine has a grant-ready packet with cost math. Would it fit? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9090,17 +10000,22 @@
           <t>A listing question</t>
         </is>
       </c>
-      <c r="I184" t="n">
-        <v>208</v>
-      </c>
-      <c r="J184" s="2" t="inlineStr">
-        <is>
-          <t>Peyton, as a financial wellness director you decide what reaches families. Mine is a K-5 read-along plus a free family activity built for a kitchen table rather than a classroom. I'll post one if it's useful.</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J184" t="n">
+        <v>344</v>
+      </c>
+      <c r="K184" s="2" t="inlineStr">
+        <is>
+          <t>Peyton, as a financial wellness director you decide what reaches families. Mine is a K-5 read-along plus a free family activity built for a kitchen table rather than a classroom. I'll post one if it's useful. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -9139,17 +10054,22 @@
           <t>Would this circulate?</t>
         </is>
       </c>
-      <c r="I185" t="n">
-        <v>213</v>
-      </c>
-      <c r="J185" s="2" t="inlineStr">
-        <is>
-          <t>Salman: national program integration is exactly the scale where K-5 gets forgotten. I made a picture book plus free ungated toolkit mapped to five frameworks, crosswalk included. Say the word and it's in the mail.</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>grant-in-a-box.html</t>
+        </is>
+      </c>
+      <c r="J185" t="n">
+        <v>353</v>
+      </c>
+      <c r="K185" s="2" t="inlineStr">
+        <is>
+          <t>Salman: national program integration is exactly the scale where K-5 gets forgotten. I made a picture book plus free ungated toolkit mapped to five frameworks, crosswalk included. Say the word and it's in the mail. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -9184,17 +10104,22 @@
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr"/>
-      <c r="I186" t="n">
-        <v>212</v>
-      </c>
-      <c r="J186" s="2" t="inlineStr">
-        <is>
-          <t>Sito, you've led K-12 at system level, so you know financial literacy usually stops at high school. Mine is the elementary on-ramp: a picture book plus free standards-aligned lessons. Does it fit a district push?</t>
-        </is>
-      </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J186" t="n">
+        <v>325</v>
+      </c>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>Sito, you've led K-12 at system level, so you know financial literacy usually stops at high school. Mine is the elementary on-ramp: a picture book plus free standards-aligned lessons. Does it fit a district push? Everything else: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -9229,17 +10154,22 @@
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr"/>
-      <c r="I187" t="n">
-        <v>167</v>
-      </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t>Ashley, an ECE strategist who keeps wellbeing central will get what I was after: a six-year-old making a real decision without being lectured. I'll send it either way.</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J187" t="n">
+        <v>267</v>
+      </c>
+      <c r="K187" s="2" t="inlineStr">
+        <is>
+          <t>Ashley, an ECE strategist who keeps wellbeing central will get what I was after: a six-year-old making a real decision without being lectured. I'll send it either way. Full story: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -9274,17 +10204,22 @@
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr"/>
-      <c r="I188" t="n">
-        <v>179</v>
-      </c>
-      <c r="J188" s="2" t="inlineStr">
-        <is>
-          <t>Dominic — Millionaire Habits for Families is a habit-first approach, which is exactly my book's design: one repeatable behavior, taught once, in a story. No obligation either way.</t>
-        </is>
-      </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J188" t="n">
+        <v>277</v>
+      </c>
+      <c r="K188" s="2" t="inlineStr">
+        <is>
+          <t>Dominic — Millionaire Habits for Families is a habit-first approach, which is exactly my book's design: one repeatable behavior, taught once, in a story. No obligation either way. More at https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -9319,17 +10254,22 @@
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
-      <c r="I189" t="n">
-        <v>196</v>
-      </c>
-      <c r="J189" s="2" t="inlineStr">
-        <is>
-          <t>Cassandra: a financial educator running operations knows what actually gets used versus what gets filed. Mine needs no prep and nothing consumable. Would it fit a member or family program you run?</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J189" t="n">
+        <v>305</v>
+      </c>
+      <c r="K189" s="2" t="inlineStr">
+        <is>
+          <t>Cassandra: a financial educator running operations knows what actually gets used versus what gets filed. Mine needs no prep and nothing consumable. Would it fit a member or family program you run? The site: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -9364,17 +10304,22 @@
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr"/>
-      <c r="I190" t="n">
-        <v>154</v>
-      </c>
-      <c r="J190" s="2" t="inlineStr">
-        <is>
-          <t>Hi Chris. CoinSprout Kids and my book are after the same kid from different directions: yours digital, mine a printed read-along. I'd take a blunt answer.</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J190" t="n">
+        <v>257</v>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>Hi Chris. CoinSprout Kids and my book are after the same kid from different directions: yours digital, mine a printed read-along. I'd take a blunt answer. More at https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -9409,17 +10354,22 @@
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr"/>
-      <c r="I191" t="n">
-        <v>209</v>
-      </c>
-      <c r="J191" s="2" t="inlineStr">
-        <is>
-          <t>Christina, Think Pieces is building financial education for children, so we're solving the same problem. It's a 36-page picture book plus free ungated toolkit for K-5. Worth comparing notes, or trading copies?</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J191" t="n">
+        <v>314</v>
+      </c>
+      <c r="K191" s="2" t="inlineStr">
+        <is>
+          <t>Christina, Think Pieces is building financial education for children, so we're solving the same problem. It's a 36-page picture book plus free ungated toolkit for K-5. Worth comparing notes, or trading copies? The site: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -9454,17 +10404,22 @@
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr"/>
-      <c r="I192" t="n">
-        <v>222</v>
-      </c>
-      <c r="J192" s="2" t="inlineStr">
-        <is>
-          <t>Claudia. Community engagement at NFEC puts you in front of real families. Mine is a K-5 read-along with a free family activity built for a kitchen table rather than a classroom. Send me a one-word reply and I'll act on it.</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J192" t="n">
+        <v>321</v>
+      </c>
+      <c r="K192" s="2" t="inlineStr">
+        <is>
+          <t>Claudia. Community engagement at NFEC puts you in front of real families. Mine is a K-5 read-along with a free family activity built for a kitchen table rather than a classroom. Send me a one-word reply and I'll act on it. More at https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -9499,17 +10454,22 @@
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr"/>
-      <c r="I193" t="n">
-        <v>174</v>
-      </c>
-      <c r="J193" s="2" t="inlineStr">
-        <is>
-          <t>Gayatri — FIntelligenZ teaches financial literacy to kids and teens; mine sits at the youngest end, ages 6-10, and leaves saving alone; it teaches spending. Glad to mail one.</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J193" t="n">
+        <v>279</v>
+      </c>
+      <c r="K193" s="2" t="inlineStr">
+        <is>
+          <t>Gayatri — FIntelligenZ teaches financial literacy to kids and teens; mine sits at the youngest end, ages 6-10, and leaves saving alone; it teaches spending. Glad to mail one. The site: https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -9544,17 +10504,22 @@
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr"/>
-      <c r="I194" t="n">
-        <v>182</v>
-      </c>
-      <c r="J194" s="2" t="inlineStr">
-        <is>
-          <t>J.P., you speak to teens, which is a decade past my readers. But the gaps you see in teenagers were set at six. Mine tries to prevent one. Does that framing match what you encounter?</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J194" t="n">
+        <v>286</v>
+      </c>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>J.P., you speak to teens, which is a decade past my readers. But the gaps you see in teenagers were set at six. Mine tries to prevent one. Does that framing match what you encounter? More at https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9589,17 +10554,22 @@
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr"/>
-      <c r="I195" t="n">
-        <v>233</v>
-      </c>
-      <c r="J195" s="2" t="inlineStr">
-        <is>
-          <t>Ta'Donna, you help program leaders deliver measurable financial education, and measurement is the part most kids' books skip. Mine has a pre/post assessment with an answer key and a 25-row tracking table, all free. It's a short read.</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J195" t="n">
+        <v>331</v>
+      </c>
+      <c r="K195" s="2" t="inlineStr">
+        <is>
+          <t>Ta'Donna, you help program leaders deliver measurable financial education, and measurement is the part most kids' books skip. Mine has a pre/post assessment with an answer key and a 25-row tracking table, all free. It's a short read. The site: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -9634,17 +10604,22 @@
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr"/>
-      <c r="I196" t="n">
-        <v>213</v>
-      </c>
-      <c r="J196" s="2" t="inlineStr">
-        <is>
-          <t>Val — a self-described financial literacy disruptor leading early financial education is the right audience for a contrarian premise. Mine: we teach saving first and we have the sequence backwards. Does that land?</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J196" t="n">
+        <v>315</v>
+      </c>
+      <c r="K196" s="2" t="inlineStr">
+        <is>
+          <t>Val — a self-described financial literacy disruptor leading early financial education is the right audience for a contrarian premise. Mine: we teach saving first and we have the sequence backwards. Does that land? Background: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -9679,17 +10654,22 @@
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr"/>
-      <c r="I197" t="n">
-        <v>204</v>
-      </c>
-      <c r="J197" s="2" t="inlineStr">
-        <is>
-          <t>Vanessa: Money Adventures and Clarence are after the same kid and the same confidence. Mine builds it through one successful purchase rather than a curriculum. Thirty-six pages; won't cost you an evening.</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J197" t="n">
+        <v>314</v>
+      </c>
+      <c r="K197" s="2" t="inlineStr">
+        <is>
+          <t>Vanessa: Money Adventures and Clarence are after the same kid and the same confidence. Mine builds it through one successful purchase rather than a curriculum. Thirty-six pages; won't cost you an evening. Details at https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -9724,17 +10704,22 @@
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr"/>
-      <c r="I198" t="n">
-        <v>172</v>
-      </c>
-      <c r="J198" s="2" t="inlineStr">
-        <is>
-          <t>Hi Kimberly. Kidz Money Lab helps families raise money-smart kids, which is my book's whole job in 36 pages. Mine teaches the spending half. I'll send it if you're curious.</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J198" t="n">
+        <v>279</v>
+      </c>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kimberly. Kidz Money Lab helps families raise money-smart kids, which is my book's whole job in 36 pages. Mine teaches the spending half. I'll send it if you're curious. Background: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -9769,20 +10754,25 @@
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr"/>
-      <c r="I199" t="n">
-        <v>210</v>
-      </c>
-      <c r="J199" s="2" t="inlineStr">
-        <is>
-          <t>Liberty, the Children's Book Project gets books to kids who don't have them, which is the best possible use of a title like mine. It teaches money through story, ages 6-10. I'll send it and get out of your way.</t>
-        </is>
-      </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J199" t="n">
+        <v>316</v>
+      </c>
+      <c r="K199" s="2" t="inlineStr">
+        <is>
+          <t>Liberty, the Children's Book Project gets books to kids who don't have them, which is the best possible use of a title like mine. It teaches money through story, ages 6-10. I'll send it and get out of your way. Details at https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M199"/>
+  <autoFilter ref="A1:N199"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9793,166 +10783,202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="98" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>CHECK</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>RESULT</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>DETAIL</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CLAUDE.md banned words (150+ terms)</t>
+          <t>Sample flipbook</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Clean. Only hits are a book title ("Money Talks") and a job title ("Leveraged Finance Reporter").</t>
+          <t>On all 198. https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Kill-list constructions ("It is not X, it is Y")</t>
+          <t>Website link</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>None across all 396.</t>
+          <t>On all 198, routed by segment (see "Site link used" column).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Filler openers / transition crutches</t>
+          <t>Gatekeepers / districts</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>educator-toolkit.html — the thing they would actually list or adopt.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tired finance puns (cents/sense, bank on it…)</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>press-kit.html — bios, art, fact sheet, interview questions.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CGB brochure phrases</t>
+          <t>Librarians / academics</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>book-facts.html — ISBN, LCCN, Lexile, concept list, glossary terms.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Spoilers: Aisle Five wordplay, Wyze pun</t>
+          <t>Credit unions / banks</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>None. Checked all 396.</t>
+          <t>resources/grant-in-a-box.html — pre-written funding requests and CRA memo.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Em-dash openers</t>
+          <t>Purchasing / procurement roles</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Was 100%. Now 25%, spread across 5 greeting forms.</t>
+          <t>resources/procurement.html — specs, sole-source letter, PO and Net 30.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Most-repeated 5-gram</t>
+          <t>Canonical URL</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Was 23x ("teaches spending rather than saving"). Now 13x ("happy to send a copy").</t>
+          <t>Non-www. www.clarencegetsabargain.com 301-redirects; schema and sitemap still say www.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Messages ending on a question</t>
+          <t>No trimming</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Was 89%. Now 38%, per the "no tidy TED-talk bow" rule.</t>
+          <t>Messages are full length. InMail allows 1900 chars; max here is 545.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Semicolons (LI rule: AI avoids them)</t>
+          <t>CLAUDE.md word lists</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Was 4%. Now 6%.</t>
+          <t>Clean. Only hit is "Leveraged Finance Reporter", a job title.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sentence rhythm</t>
+          <t>Kill-list constructions</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Mean 11.3 words, stdev 6.2; 18% under six words.</t>
+          <t>None.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Grammar pass after rewriting</t>
+          <t>Spoilers (Aisle Five, Wyze)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>396 checked. 2 flags, both false positives on name abbreviations.</t>
+          <t>None.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Em-dash openers</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>25%, across five greeting forms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ends on a question</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>38%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Grammar pass</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>396 checked. No flags.</t>
         </is>
       </c>
     </row>

--- a/CGB_HVT_199-396_bespoke.xlsx
+++ b/CGB_HVT_199-396_bespoke.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="HVT 199-396" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Links &amp; audit" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HVT 199-396" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voice audit" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HVT 199-396'!$A$1:$N$199</definedName>
@@ -442,13 +442,13 @@
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="100" customWidth="1" min="11" max="11"/>
+    <col width="104" customWidth="1" min="11" max="11"/>
     <col width="8" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
@@ -497,7 +497,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Site link used</t>
+          <t>Site link</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -565,11 +565,11 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Hi Tiina. An EdD in a CISO seat is an unusual combination. My question is on the education side: does a K-5 financial literacy book plus free toolkit fit anything your organization touches? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Rodrigue — an EdD in a CISO seat is an unusual combination, and my question is on the education side. Does a K-5 financial literacy book plus free toolkit fit anything your organization touches? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Jennifer, your work with financial institutions and external affairs is where a fundable K-5 program would need a champion. Mine comes with a grant-ready packet built for bank and CRA sponsorship. Where might it fit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jennifer — your work with financial institutions and external affairs is where a fundable K-5 program needs a champion. Mine comes with a grant-ready packet built for bank and CRA sponsorship. Where might it fit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -665,11 +665,11 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Leslie. Consumer markets work is upstream of everything my book teaches: comparison, price transparency, what the register adds. Mine is the six-year-old version. If it's a no, no reply needed. Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Leslie — consumer markets work is upstream of everything my book teaches: comparison, price transparency, what the register adds at the end. Mine is the six-year-old version. Where might it fit? Toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -715,11 +715,11 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Varun — an economist teaching at community college level sees exactly what students never got. Mine tries to supply it at six: one purchase, compared and paid for properly. Does the framing hold up? Details at https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Varun — an economist teaching at community college level sees exactly what students never got. Mine tries to supply it at six: one purchase, compared and paid for properly. Does the framing hold? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Aarav — Rich Lessons and my book are after the same idea from opposite ends of the age range. Mine teaches six-year-olds to spend deliberately. Would it fit the podcast, or your readers? More at https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Aarav — Rich Lessons and my book are after the same idea from opposite ends of the age range. Mine teaches six-year-olds to spend on purpose. Podcast fit, or your readers? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -810,7 +810,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -819,11 +819,11 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Kathryn — a checkable claim for a personal finance desk: every children's money book teaches saving. I read all 25 on the ABA Foundation's list to be sure. None teaches spending, which is the transaction a six-year-old actually performs. I wrote the one that does, sales tax included. Story, or point me elsewhere? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kathryn — a claim you can check over coffee: every children's money book teaches saving. I read all 25 on the ABA Foundation's list rather than assume it. None teaches spending, which is the only transaction a six-year-old performs. Mine does, sales tax included. Story, or wrong desk? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -873,11 +873,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>334</v>
+        <v>365</v>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Mike, you write for people building habits right now. Mine starts them at six and skips saving entirely: one purchase, sale ad to register, including the moment the kid learns sales tax exists. One line back is plenty. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mike — you write for people building habits right now. Mine starts them at six and skips saving entirely: one purchase, sale ad to register, including the moment sales tax shows up uninvited. Is there a story in what kids' money books leave out? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -927,11 +927,11 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Pete, a small odd fact you may be able to use: I wrote a children's picture book in which a six-year-old pays sales tax and asks where the money went. I can't find another kids' book that does it. Happy to send a copy. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Pete — a small odd fact you may be able to use. I wrote a children's picture book in which a six-year-old pays sales tax and asks where it went. I can't find another kids' book that does it. Story, or just a strange thing to have made? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -972,7 +972,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -981,11 +981,11 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>374</v>
+        <v>336</v>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Liz — a kids' money book with no piggy bank in it, on purpose. It teaches spending: comparison, markdowns, coupons, sales tax. Ages 6-10. I think the story is the forty-year gap in the category rather than my book. Interested, or is there a better name? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Liz — a kids' money book with no piggy bank in it. Deliberate. It teaches spending: comparison, markdowns, coupons, sales tax. The story is the forty-year gap in the category, not my book. Interested, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1035,11 +1035,11 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Kerri Anne: you know a story beats a lecture, which is the whole design here. A six-year-old runs one real purchase and picks the cheaper older model on purpose. No saving lesson anywhere in it. I'll post one if it's useful. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kerri Anne — you know a story beats a lecture, which is the entire design. Six-year-old runs one real purchase and takes the cheaper older model on purpose. No saving lesson anywhere in it. Something here for you? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1089,11 +1089,11 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>344</v>
+        <v>320</v>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Hi Leslie. As a personal finance editor you decide what earns a reader's time. My angle: children's money books are almost entirely about saving, and the skill kids use first is spending. I wrote the counterexample. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Leslie — as an editor you decide what earns a reader's time. My angle: children's money books are almost entirely saving, and the skill kids use first is spending. I wrote the counterexample. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1143,11 +1143,11 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Jill, a kids' money book that teaches sales tax. A six-year-old gets to the register, the total is higher than the sticker, and he gets an explanation. I don't believe another picture book does it. Say the word and it's in the mail. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jill — a kids' money book that teaches sales tax. Six-year-old reaches the register, total's higher than the sticker, and he gets an explanation rather than a shrug. I don't believe another picture book does it. Story, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1197,11 +1197,11 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>J.R.. Consumer and personal finance is exactly where my book sits, just at reading level 620L. A six-year-old reads a sale ad, compares two models, uses a coupon, pays tax. It's a consumer education in 36 pages. Tell me if it's not a fit. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>J.R. — consumer and personal finance is exactly where my book sits, just at reading level 620L. Sale ad, comparison, coupon, tax. A consumer education in 36 pages. Angle for you? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1251,11 +1251,11 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Casey — you lead banking content, so here's the odd end of the funnel: a picture book that teaches a six-year-old the mechanics of a purchase, register and sales tax included. It's where a banking customer starts. Story, or a colleague? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Casey — you lead banking content, so here's the odd end of that funnel: a picture book teaching a six-year-old the mechanics of a purchase, register and sales tax included. That's where a banking customer actually starts. Story, or a colleague? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Kelly, a veteran consumer finance journalist will know instantly whether this gap is real. The whole category teaches saving; none teaches the transaction. I wrote the one that does. If it's a no, no reply needed. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kelly — a veteran consumer finance journalist will know instantly whether this gap is real or convenient. Every children's money book teaches saving; none teaches the transaction. Does that hold up to you? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1359,11 +1359,11 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>351</v>
+        <v>317</v>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Deborah, a content strategist's question as much as a reporter's: children's financial literacy is 90% saving, and nobody covers spending. I wrote the book filling it. Is the gap itself the story? Happy to send the book either way. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Deborah — a content strategist's question as much as a reporter's. Children's financial literacy is 90% saving and nobody covers spending. Is the gap itself the story? Happy to send the book either way. Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1413,11 +1413,11 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>356</v>
+        <v>319</v>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Jessica — a kids' picture book that skips saving and teaches spending, including sales tax at the register. Ages 6-10. I think the interesting part is what forty years of children's money books skipped. I'd rather hear no than nothing. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jessica — a kids' picture book teaching spending rather than saving, sales tax at the register, ages 6-10. The interesting part is what forty years of children's money books skipped. Something here for you? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Rachel: my book teaches six-year-olds the money skill that never gets its own title: spending. One purchase, ad to register. Is there a piece in why children's financial literacy is all piggy banks and no cash registers? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Rachel — mine teaches six-year-olds the money skill that never gets its own title: spending. One purchase, ad to register. Is there a piece in why children's financial literacy is all piggy banks and no cash registers? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1521,11 +1521,11 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Hi Venessa. You cover the consumer side. Mine is a consumer origin story: a six-year-old's first real purchase, complete with the discovery that the sticker price isn't the price. 36 pages. Story, or a better name? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Venessa — you cover the consumer side. Mine is a consumer origin story: a six-year-old's first purchase, complete with discovering the sticker price was never the price. 36 pages. Story, or a better name? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1575,11 +1575,11 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Maureen, far from your usual beat, so I'll be quick. I wrote the only children's picture book I can find that leaves saving to everyone else. If there's someone at the Times who'd want it, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Maureen — well off your beat, so briefly. I wrote the only children's picture book I can find that skips saving and teaches spending. If there's someone at the Times who'd want it, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1629,11 +1629,11 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Suman. A business angle rather than a book pitch: children's financial literacy is a real category with a structural hole in it. Everything teaches saving; nothing teaches the transaction. I wrote the counterexample. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Suman — a business angle rather than a book pitch. Children's financial literacy is a real category with a structural hole in it: everything teaches saving, nothing teaches the transaction. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1683,11 +1683,11 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Christine — you cover finance in Canada. My claim is portable: no children's picture book teaches the complete purchase, through the register, including sales tax. Mine does. No pitch after this one, promise. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christine — you cover finance in Canada, and my claim travels: no children's picture book teaches the complete purchase, through the register, sales tax included. Mine does. Is there a story in the omission? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1737,11 +1737,11 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Megan, a money desk fact you might enjoy: my children's picture book teaches sales tax. The six-year-old pays it, notices, and asks. Everything else in the category stops at saving. Ignore me if it's wrong for you. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Megan — a money desk fact you may enjoy: my children's picture book teaches sales tax. The six-year-old pays it, notices, and objects. Everything else in the category stops at saving. Story, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1791,11 +1791,11 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Barbara, well off your beat, so briefly. I wrote a children's book that skips saving entirely, and I think the story is what the category has ignored. If there's a colleague who covers consumer or family money, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Barbara — well off your beat, so briefly. I wrote a children's book teaching spending rather than saving, and the story is what the category ignored. If a colleague covers consumer or family money, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1845,11 +1845,11 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Mike — a local-interest angle: an attorney wrote and illustrated a children's book that teaches kids to shop, including sales tax at the register. It's the only one I can find that does. One copy, no follow-up, your call. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mike — a local angle: an attorney wrote and illustrated a children's book teaching kids to shop, sales tax at the register included. It's the only one I can find that does. Segment, or wrong desk? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -1899,11 +1899,11 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Damilola — you hold the CFEI and write personal finance, so you'll test the premise. Mine: spending competence precedes saving competence, and the category has the sequence backwards. There's a copy with your name on it. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Damilola — you hold the CFEI and write personal finance, so you'll test the premise. Mine: spending competence precedes saving competence, and the category has the sequence backwards. Does that hold? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1953,11 +1953,11 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Marc, you write about investing for people well past first grade. Mine starts at six with the skill that comes before any of it: spending deliberately. Is there an angle for your readers? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Marc — you write about investing for people well past first grade. Mine starts at six with the skill that comes before all of it: spending on purpose. Angle for your readers? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2007,11 +2007,11 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>380</v>
+        <v>343</v>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Robin, a data point rather than a pitch: I checked the ABA Foundation's 25-title children's financial literacy list. Every one teaches earning, saving, or investing. None teaches spending. That gap seemed worth a book. Take a look or don't; either is fine. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Robin — a data point rather than a pitch. I checked the ABA Foundation's 25-title children's financial literacy list. Every one teaches earning, saving, or investing. None teaches spending. That gap became a book. Worth a story? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2061,11 +2061,11 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Rui — a children's picture book that teaches the complete purchase, including sales tax, which appears to be unique in the category. Ages 6-10. I'll send it and get out of your way. Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Rui — a children's picture book teaching the complete purchase, sales tax included, apparently unique in the category. Ages 6-10. Something here for you, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2115,11 +2115,11 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Sarah: as a senior editor you'll want the angle first. Mine: children's financial literacy teaches saving almost exclusively, while spending is what kids actually do. I wrote the counterexample. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarah — you'll want the angle before the book. Mine: children's financial literacy teaches saving almost exclusively while spending is what kids actually do. I wrote the counterexample. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2169,11 +2169,11 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Manisha, your work is about money and wellbeing, and the emotional part starts young. My book meets a six-year-old at the first want in a store aisle and walks him to a decision he makes himself. Does that land for you? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Manisha — your work is about money and wellbeing, and the emotional part starts absurdly young. Mine meets a six-year-old at the first want in a store aisle and walks him to a decision he makes himself. Does that land for you? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2223,11 +2223,11 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>345</v>
+        <v>301</v>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Hi Helen. As deputy editor of On the Money you'll want the angle, not the book. Mine: children's financial literacy is all saving and no spending, and has been for forty years. I wrote the counterexample. Happy to be told no. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Helen — you'll want the angle, not the book. Children's financial literacy is all saving and no spending, and has been for forty years. I wrote the counterexample. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2277,11 +2277,11 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Mark, a senior editor's filter. My claim: no children's picture book teaches the complete purchase through the register, sales tax included. I checked the ABA Foundation's 25-title list. Mine is the exception. A copy is easy to send. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mark — a senior editor's filter, so a checkable claim: no children's picture book teaches the complete purchase through the register, sales tax included. I checked the ABA's 25-title list. Mine is the exception. Story? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2331,11 +2331,11 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Jason: a feature rather than a finance story: an attorney and mixed-media artist wrote and illustrated a picture book that teaches six-year-olds how to shop, then gave the classroom materials away free. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jason — a feature rather than a finance story. An attorney and mixed-media artist wrote and illustrated a picture book teaching six-year-olds how to shop, then gave the classroom materials away free. Worth a look? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Hi Katie. A kids' money book that skips saving entirely. It teaches spending: read the ad, compare, use the coupon, pay the tax. Ages 6-10. I'll leave it there. Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Katie — a kids' money book that skips saving entirely: read the ad, compare, use the coupon, pay the tax. Ages 6-10. Story in the gap, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2439,11 +2439,11 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Josyana, my picture book teaches six-year-olds one purchase end to end, tax and all, which I can't find anywhere else in children's financial literacy. Shout if you want one. Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Josyana — mine teaches six-year-olds the complete purchase, sales tax included, which appears to be unique in children's financial literacy. Story for you, or someone else on the desk? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2493,11 +2493,11 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Claire. As a personal finance editor: the claim is that children's money publishing has a spending-shaped hole in it, forty years wide. I wrote the book that fills it. Interested in the gap, or the book, or neither? Press kit: https://clarencegetsabargain.com/press-kit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Claire — the claim is that children's money publishing has a spending-shaped hole in it, forty years wide. I wrote the book that fills it. Interested in the gap, the book, or neither? Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2547,11 +2547,11 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Hi Melina. A long way from leveraged finance, so I'll be brief. I wrote a children's book teaching six-year-olds how a purchase actually works, sales tax and all. If a colleague covers consumer or family money, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Melina — a long way from leveraged finance, so I'll be brief. I wrote a children's book teaching six-year-olds how a purchase actually works, tax and all. If a colleague covers consumer or family money, I'd take the name. Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -2601,11 +2601,11 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Danielle. A segment idea: an attorney wrote and illustrated a children's book that teaches kids to shop properly, sales tax included, then gave the lesson plans away free. Happy to be told no. Press kit: https://clarencegetsabargain.com/press-kit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Danielle — a segment idea. An attorney wrote and illustrated a children's book teaching kids to shop properly, sales tax included, then gave the lesson plans away free. Work for you, or a better producer? Press kit: https://clarencegetsabargain.com/press-kit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -2655,11 +2655,11 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>325</v>
+        <v>295</v>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Mark — a producer-level pitch. The hook is one line: every children's money book teaches saving; mine teaches spending, and a six-year-old pays sales tax on camera-friendly page 22. A copy is easy to send. Press kit: https://clarencegetsabargain.com/press-kit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mark — producer-level pitch, one line. Every children's money book teaches saving; mine teaches spending, and the six-year-old pays sales tax on page 22. Worth a look, or wrong show? Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -2705,11 +2705,11 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Mark, as a senior editor: children's financial literacy has been all saving for forty years, and nobody teaches the transaction. I wrote the one that does. Is the omission a story? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mark — children's financial literacy has been all saving for forty years and nobody teaches the transaction. I wrote the one that does. Is the omission the story? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2759,11 +2759,11 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>Alisha, as a reading content editor you'll care about the literacy side as much as the money. Mine is AD 620L, 36 pages, built as a read-along so a kid and a grown-up do it together. I'll stop there. Press kit: https://clarencegetsabargain.com/press-kit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alisha — as a reading content editor you'll care about the literacy side as much as the money. AD 620L, 36 pages, built as a read-along so a kid and a grown-up do it out loud. Fit your coverage? Press kit: https://clarencegetsabargain.com/press-kit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -2809,11 +2809,11 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>Brian. A finance reporter's angle rather than a book pitch: children's money publishing skips spending entirely, which is the transaction kids actually perform. I wrote the one that doesn't. Interested, or is there a better name? Press kit: https://clarencegetsabargain.com/press-kit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Brian — an angle rather than a book pitch. Children's money publishing skips spending entirely, which is the transaction kids actually perform. I wrote the one that doesn't. Interested, or a better contact? Press kit: https://clarencegetsabargain.com/press-kit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -2859,11 +2859,11 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>367</v>
+        <v>405</v>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>Kellyanne, a children's librarian with an MEd will judge both the story and the teaching. Mine is AD 620L, 36 pages, with a 21-term glossary and page references in the back. Would it circulate at Lake Hiawatha? Happy to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kellyanne — a children's librarian with an MEd judges both halves: the story and the teaching. Mine is AD 620L, 36 pages, 21-term glossary with page references. It teaches spending, which nothing else on your shelf does. Would it circulate at Lake Hiawatha? Happy to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -2909,11 +2909,11 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>Rae — as a children's librarian you know which books get picked up twice. Mine is a money book that reads like a story, ages 6-10, glossary in the back. Would it earn shelf space? Glad to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Rae Ellyn — as a children's librarian you know which books get picked up twice and which get picked up never. Mine is a money book that reads like a story, ages 6-10, glossary in the back. Would it earn shelf space? Glad to send a copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -2959,11 +2959,11 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>Ashlie: a library director decides what circulates. Mine is a hardbound 36-page picture book teaching K-5 financial literacy, AD 620L, 21-term glossary, ISBN 979-8-234-07638-0, LCCN 2026906164. Would it fit Melrose Park? Happy to send a review copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ashlie — a library director decides what circulates, so facts first. Hardbound, 36 pages, AD 620L, 21-term glossary, ISBN 979-8-234-07638-0, LCCN 2026906164. Teaches spending rather than saving. Fit for Melrose Park? Happy to send a review copy. Specs, ISBN, Lexile: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3009,11 +3009,11 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>356</v>
+        <v>320</v>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>Ramat — FLEX runs K-8 financial education in Pennsylvania schools, which is the exact band and the exact problem. It's a picture book for grades 1-5 plus free zero-prep lessons checked against five frameworks. Does it complement FLEX or compete with it? Background: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ramat — FLEX runs K-8 financial education in Pennsylvania schools, which is the exact band and the exact problem. Mine is K-5 plus free zero-prep lessons against five frameworks. Complement FLEX, or compete with it? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3059,11 +3059,11 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>Alex, a published financial literacy author and educator is the read I want most. Mine argues spending is the first money skill and the category teaches saving instead. As someone who has published in this space, does that hold or is it a marketing line? Details at https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alex — a published financial literacy author and educator is the read I want most. Mine argues spending is the first money skill and the category teaches saving instead. As someone who has published here — does that hold, or is it a marketing line? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3113,11 +3113,11 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>Hi Lisa. Children's author to children's author. My worry is craft, not content: does a 36-page arc about one shopping trip actually hold a young reader? Would you look? as a writer rather than a subject expert. Background: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Lisa — children's author to children's author. My worry is craft, not content: does a 36-page arc about one shopping trip hold a young reader? I'd value your read as a writer rather than a subject expert. More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3163,11 +3163,11 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>Kago, you're a relatable financial storyteller, which is exactly what I attempted for six-year-olds. Mine teaches spending through a boy and a robot rather than a lesson. Storyteller to storyteller: does the story carry the teaching, or buckle under it? Full story: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kago — you're a relatable financial storyteller, which is exactly what I attempted for six-year-olds. Mine teaches spending through a boy and a robot rather than a lesson. Storyteller to storyteller: does the story carry it, or buckle? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3213,11 +3213,11 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>James — a Barron's AP Economics author running education programs will judge accuracy first. Mine teaches comparison, percentage markdowns, and sales tax to six-year-olds. Does it get the economics right at that level, or oversimplify? More at https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>James — a Barron's AP Economics author will judge accuracy first. Mine teaches comparison, percentage markdowns, and sales tax to six-year-olds. Does it get the economics right at that level, or oversimplify? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3263,11 +3263,11 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Larry: a bestselling author and certified financial instructor covers both halves of what I need judged. Mine teaches the complete purchase to ages 6-10. I'll send it either way. The site: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Larry — a bestselling author and certified financial instructor covers both halves of what I need judged. Mine teaches the complete purchase to ages 6-10. Does the instruction hold up under the story? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3313,11 +3313,11 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Donna, as a KidLit author you'll spot immediately whether the lesson pokes through the story. That's my main fear about my own book. No pitch after this one, promise. Everything else: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Donna — as a KidLit author you'll spot immediately whether the lesson pokes through the story. That's my main fear about my own book. Would you read it and tell me where it shows? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -3363,11 +3363,11 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Ilene. Author to author. Mine hides a financial education inside a story about a boy and a robot. Authors are the worst judges of their own subtlety, which is why I'm asking. Ignore me if it's wrong for you. Full story: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ilene — author to author. Mine hides a financial education inside a story about a boy and a robot. Authors are the worst judges of their own subtlety, which is why I'm asking you. Take a look? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -3413,11 +3413,11 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Patricia — a fellow author's read is the one I trust most. Mine is a 36-page picture book teaching money through a single shopping trip. Does the story stand on its own if you strip the lesson out? Everything else: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Patricia — a fellow author's read is the one I trust most. Mine is 36 pages teaching money through a single shopping trip. Does the story stand on its own if you strip the lesson out? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -3463,11 +3463,11 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>301</v>
+        <v>325</v>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Corwin, you coach authors through self-publishing, so you'll see the strategic question: I've deliberately skipped Amazon and sell direct. Brave or dumb? I'd genuinely value the straight answer. Full story: https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Corwin — you coach authors through self-publishing, so you'll see the strategic question rather than the literary one: I've deliberately skipped Amazon and sell direct. Brave or dumb? I'd genuinely value the straight answer. More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3513,11 +3513,11 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Cathy, a publishing consultant and bestselling author sees the whole path. My book leaves saving to everyone else, ages 6-10, direct sales only, no Amazon by choice. Tell me what you make of positioning something with no shelf-mates. Everything else: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cathy — a publishing consultant and bestselling author sees the whole path. Mine goes at spending instead of saving, ages 6-10, direct sales only, no Amazon by choice. I'd value your read on positioning something with no shelf-mates. More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -3563,11 +3563,11 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Michele — you help independent authors produce books that hold up physically. Mine is hardbound, full color, 11x8.5, 36 pages, and I wrote and illustrated it. Tell me whether the production choices serve it. Full story: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michele — you help independent authors produce books that hold up physically. Mine is hardbound, full color, 11x8.5, 36 pages, and I wrote and illustrated it myself. Do the production choices serve it, or fight it? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -3613,11 +3613,11 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Bill. As a parenting author and speaker you know money is the topic parents dodge. My read-along removes the pressure: the parent reads the story and the lesson does its own work. Would it fit the families you reach? More at https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bill — as a parenting author and speaker you know money is the topic parents dodge. My read-along removes the pressure: the parent reads the story and the lesson does its own work. Fit the families you reach? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -3663,11 +3663,11 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Cara — ECE keynote speaker, author, and teacher trainer is three useful angles at once. Mine is a K-5 read-aloud teaching the first money behavior kids actually perform. Take a look or don't; either is fine. The site: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cara — ECE keynote speaker, author, and teacher trainer is three useful angles at once. Mine is a K-5 read-aloud teaching the first money behavior kids actually perform. Right age developmentally, or does it skew old? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -3717,11 +3717,11 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Hi Chad. You've built a career on teaching young people what school skips. Mine goes younger than most: six-year-olds, and the skill is spending rather than saving. Does that age band hold a real lesson? Background: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Chad — you've built a career teaching young people what school skips. Mine goes younger than most: six-year-olds, and the skill is spending rather than saving. Does that age band hold a real lesson? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -3771,11 +3771,11 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>David, The Squeaky Wheel proved a money book for kids can be genuinely funny. Mine tries the same trick on spending rather than saving. There's a copy with your name on it. Details at https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>David — The Squeaky Wheel proved a kids' money book can be genuinely funny. Mine tries the same trick on spending rather than saving. Author to author, would you tell me if the humor lands or thuds? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3825,11 +3825,11 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Courtney: author and founder, so you'll see both the book and the business question. Mine teaches K-5 spending and sells direct rather than through Amazon. Shout if you want one. Background: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Courtney — author and founder, so you'll see both the book and the business question. Mine teaches K-5 spending and sells direct rather than through Amazon. Worth a look, or a bad decision? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -3875,11 +3875,11 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Hanna: you study financial literacy and wellbeing, so you'll spot the seams. My premise: spending is the first money skill a kid uses and no picture book is built around it. I'd value a researcher's read on whether the framing holds and the concepts land for ages 6-10. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hanna — you study financial literacy and wellbeing, so you'll spot the seams. My premise: spending is the first money skill a kid uses and no picture book is built around it. I'd value a researcher's read on whether that holds for ages 6-10. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -3925,11 +3925,11 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Casey, an award-winning financial literacy educator and founder of The Orchard Method is a tough, useful read. My K-5 book teaches the spending half. Happy to hear it's not for you. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Casey — an award-winning financial literacy educator and founder of The Orchard Method is a tough, useful read. Mine leaves saving to everybody else. Does the approach hold up for you? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -3975,11 +3975,11 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Clarissa — as a financial literacy ambassador you already sell people on why this matters. Mine teaches six-year-olds to spend deliberately. Shout if you want one. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Clarissa — as a financial literacy ambassador you already sell people on why this matters. Mine teaches six-year-olds to spend deliberately. Fit the students or events you reach? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4025,11 +4025,11 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>335</v>
+        <v>283</v>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Nicholas, a senior student ambassador sees which material actually lands with people. It's a picture book for grades 1-5 teaching spending rather than saving. Would it fit your outreach, or is it too young? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Nicholas — a senior student ambassador sees which material actually lands. Mine is K-5, teaching spending rather than saving. Fit your outreach, or too young? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4075,11 +4075,11 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>407</v>
+        <v>438</v>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>Carly: your work on financial education mandates is the best evidence we have on what actually moves outcomes. Almost all of it sits at high school. I wrote a K-5 book on the premise that the elementary band is both untested and undersupplied. Let me know and it ships. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Professor Urban — your work on financial education mandates is the best evidence we have on what actually moves outcomes, and nearly all of it sits at high school. I wrote a K-5 book on the premise that elementary is both untested and undersupplied. Is there research I should know before I keep saying that? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -4125,11 +4125,11 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Hi Neale. A question rather than a pitch. My K-5 book argues consumer transaction competence is taught almost nowhere, despite being the money behavior kids perform first. From a behavioral economics angle, is that a real gap or a rounding error? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Professor Mahoney — a question rather than a pitch. My K-5 book argues consumer transaction competence is taught almost nowhere, despite being the money behavior kids perform first. From a behavioral angle, is that a real gap or a rounding error? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -4175,11 +4175,11 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Mark, well outside your usual work, and I'll be brief. I wrote a children's book on the premise that spending competence is untaught and precedes saving competence. If someone at SIEPR studies early financial capability, I'd value the name. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Professor Duggan — well outside your usual work, so briefly. I wrote a children's book on the premise that spending competence is untaught and precedes saving competence. If someone at SIEPR studies early financial capability, I'd value the name. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -4225,11 +4225,11 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Derek. You sit between research and practice, which is where my premise should get stress-tested. I argue we teach kids saving first when spending is the transaction they actually perform. I'd take a blunt answer. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Derek — you sit between research and practice, which is where my premise should get stress-tested. I argue we teach kids saving first when spending is the transaction they actually perform. Does the sequencing claim survive? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -4275,11 +4275,11 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Shinae — your work on family financial wellbeing is adjacent to my premise: that spending competence is taught almost nowhere in K-5 despite being the first money behavior kids perform. Does that match what the literature shows? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Professor Choi — your work on family financial wellbeing is adjacent to my premise: spending competence is taught almost nowhere in K-5 despite being the first money behavior kids perform. Does that match the literature? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -4325,11 +4325,11 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Angela, you bridge data and practice, which is exactly where I need a check. My claim: children's financial education is overwhelmingly saving-focused and the sequencing is backwards. Send me a one-word reply and I'll act on it. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Angela — you bridge data and practice, which is exactly where I need checking. My claim: children's financial education is overwhelmingly saving-focused and the sequencing is backwards. Is there data contradicting me? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -4375,11 +4375,11 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Melanie, Extension reaches families where money is concrete, which is how my book teaches it: one purchase, start to register. Would it fit Extension programming, and does the premise hold for the families you serve? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Melanie — Extension reaches families where money is concrete, which is how mine teaches it: one purchase, start to register. Fit Extension programming, and does the premise hold for the families you serve? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -4425,11 +4425,11 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Iris — you're at UW-Madison, which is where the Center for Financial Security picked the titles for the CFPB's Money as You Grow Bookshelf. My K-5 book skips saving and teaches spending. Do you know who evaluates additions to that shelf? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Iris — you're at UW-Madison, which is where the Center for Financial Security picked the titles for the CFPB's Money as You Grow Bookshelf. Mine is K-5 and goes at spending instead of saving. Do you know who evaluates additions to that shelf? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -4475,11 +4475,11 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Hi Anjana. A public health lens on financial capability is unusual and useful. My K-5 book treats spending competence as a preventive intervention rather than a curriculum topic. Does that framing make sense to you? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Anjana — a public health lens on financial capability is unusual and useful. Mine treats spending competence as a preventive intervention rather than a curriculum topic. Does that framing make sense to you? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -4525,11 +4525,11 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Chelsea, as an economics lecturer you'll want the premise tested. Mine: we teach children saving first, but spending is the transaction they perform first, so the sequence is backwards. Thirty-six pages; won't cost you an evening. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Dowell — as an economics lecturer you'll want the premise tested. Mine: we teach children saving first, but spending is the transaction they perform first, so the sequence is backwards. Does it survive scrutiny? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -4575,11 +4575,11 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Narmin. You teach finance at graduate level, where the gaps students carry up from childhood are visible. My book tries to close one at six. I'd value an academic's read on whether the premise is sound or convenient. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Nahidi — you teach finance at graduate level, where the gaps students carry up from childhood are plainly visible. Mine tries to close one at six. I'd value an academic's read on whether the premise is sound or merely convenient. Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -4625,11 +4625,11 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Andrea — as a research director you'll want the claim before the book. Mine: consumer transaction competence is taught almost nowhere in K-5. I built a picture book and free toolkit around it. Is there evidence against? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Andrea — as a research director you'll want the claim before the book. Mine: consumer transaction competence is taught almost nowhere in K-5. I built a picture book and free toolkit around it. Evidence against? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -4675,11 +4675,11 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>364</v>
+        <v>331</v>
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Jordan, a graduate student's read is useful because you're close to the research and not yet committed to a position. My premise: spending competence precedes saving competence and is untaught. There's a copy with your name on it. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jordan — a graduate student's read is useful because you're close to the research and not yet committed to a position. My premise: spending competence precedes saving competence and is untaught. Does it hold? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -4725,11 +4725,11 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>William — teaching finance at Delta Charter means you see students arrive with gaps set a decade earlier. Mine tries to close one at six. I'll stop there. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>William — teaching finance at Delta Charter means you see students arrive with gaps set a decade earlier. Mine tries to close one at six. Does the premise hold from where you sit? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -4775,11 +4775,11 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Sloane. You're studying English and education, which makes you a better test than most of the people I'm asking. Does my book read like something a real first grader would sit through, or does the lesson show? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sloane — you're studying English and education, which makes you a better test than most people I'm asking. Does my book read like something a real first grader would sit through, or does the lesson show? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -4829,11 +4829,11 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>Chalese, a money management center sees exactly which gaps students arrive with. Mine tries to close one at six rather than nineteen. Does the premise match what walks through your door? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Chalese — a money management center sees exactly which gaps students arrive with. Mine tries to close one at six rather than nineteen. Does the premise match what walks through your door? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4883,11 +4883,11 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Pushpa — you've built financial capability work at national scale. My claim is that K-5 is structurally underserved because funding follows high school. One line back is plenty. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Wood — you've built financial capability work at national scale. My claim: K-5 is structurally underserved because funding follows high school. Does that hold internationally, or is it a US problem? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -4933,11 +4933,11 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Eduardo, you study digital consumer behavior, which makes my book slightly anachronistic on purpose: it teaches the physical transaction, cash and coupon and register. Does teaching the tangible version still matter? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Professor Mesquita — you study digital consumer behavior, which makes my book slightly anachronistic on purpose. It teaches the physical transaction: cash, coupon, register. Does teaching the tangible version still matter? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -4987,11 +4987,11 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Joel — an AFC with an MPA directing financial wellness will judge both the content and the delivery. Mine runs 36 pages plus four free zero-prep lessons. Would it fit a program you run? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Joel — an AFC with an MPA judges both the content and the delivery. It's a 36-page picture book plus four free zero-prep lessons. Fit a program you run? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5041,11 +5041,11 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Ryan, a money success center sees the downstream cost of what nobody taught at eight. Mine teaches the complete purchase at six, sales tax included. Let me know and it ships. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ryan — a money success center sees the downstream cost of what nobody taught at eight. Mine teaches the complete purchase at six, sales tax included. Does starting that early actually stick, in your experience? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -5095,11 +5095,11 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Megan: financial therapy says money behavior is emotional and early. My picture book meets a six-year-old at the first want in a store and walks him to his own decision. Happy to send a copy. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. McCoy — financial therapy says money behavior is emotional and early. Mine meets a six-year-old at the first want in a store and walks him to his own decision. Does that land clinically, or is it wishful? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -5149,11 +5149,11 @@
         </is>
       </c>
       <c r="J90" t="n">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Hi Kim. A center for economic education knows what teachers actually adopt. My K-5 book is aligned to CEE and four other frameworks with a full crosswalk, and elementary is usually the thinnest shelf. Would it fit your teacher work? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kim — a center for economic education knows what teachers actually adopt versus politely accept. Mine is aligned to CEE and four others with a full crosswalk, and elementary is usually the thinnest shelf. Fit your teacher work? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -5203,11 +5203,11 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>384</v>
+        <v>310</v>
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Maria, Tennessee's economic education council decides what reaches classrooms. My K-5 picture book; the toolkit behind it is free is mapped to five frameworks, crosswalk included. Elementary is where most states have the least. I'll post one if it's useful. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Maria — Tennessee's council decides what reaches classrooms. Mine is K-5 plus a free zero-prep toolkit against five frameworks. Elementary is where most states have the least. Route in? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5257,11 +5257,11 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Panu. Your work on financial education crosses national contexts. My premise is that spending competence is taught almost nowhere at primary level, in any country I've checked. Does that hold in the European data? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Professor Kalmi — your work on financial education crosses national contexts. My premise is that spending competence is taught almost nowhere at primary level, in any country I've checked. Does that hold in the European data? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5311,11 +5311,11 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Anna — a question from outside the academy. My children's book argues spending competence precedes saving competence developmentally. Say the word and it's in the mail. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Professor Lo Prete — a question from outside the academy. My children's book argues spending competence precedes saving competence developmentally. Is there literature that settles the sequencing either way? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -5365,11 +5365,11 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Lamya, as a finance professor you'll test a premise quickly. Mine: children's financial education teaches saving almost exclusively while spending is the first transaction kids perform. Tell me if it's not a fit. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Alsaadi — as a finance professor you'll test a premise quickly. Mine: children's financial education teaches saving almost exclusively while spending is the first transaction kids perform. Does it hold? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -5419,11 +5419,11 @@
         </is>
       </c>
       <c r="J95" t="n">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Jaycob — a center for excellence in finance sees where competence actually comes from. Mine argues it starts with one supervised purchase at six. If it's a no, no reply needed. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jaycob — a center for excellence in finance sees where competence actually comes from. Mine argues it starts with one supervised purchase at six. Does that framing interest you? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5473,11 +5473,11 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>341</v>
+        <v>299</v>
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Beau: a visiting professor's read is useful precisely because you see many programs. My K-5 book leaves saving alone; it teaches spending, mapped to five frameworks, crosswalk included. Does the premise hold up? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Beau — a visiting professor's read is useful precisely because you see many programs. Mine is a spending book, not a saving one, K-5, five frameworks. Does the premise hold up? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>Hi CMA. A finance academic's read on a children's book premise: spending competence precedes saving competence and is taught almost nowhere. I'd rather hear no than nothing. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Niranjan — a finance academic's read on a children's book premise: spending competence precedes saving competence and is taught almost nowhere. Does that survive in your context? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5581,11 +5581,11 @@
         </is>
       </c>
       <c r="J98" t="n">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Jay, as a business instructor you see students arrive with gaps set long before college. My book tries to close one at six. Copy's yours if you want it. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jay — as a business instructor you see students arrive with gaps set a decade earlier. Mine tries to close one at six. Would the premise hold up in your classroom? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -5635,11 +5635,11 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Sebastian. An adjunct's read is useful because you see the practical end. My K-5 picture book teaches the whole purchase, right through sales tax. Does that seem like the right first lesson? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sebastian — an adjunct's read is useful because you see the practical end. Mine teaches the complete purchase, sales tax included, to six-year-olds. Right first lesson, or wrong one? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -5689,11 +5689,11 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Bryan — you advise students who often arrive without the basics. My book plants one at six: compare before you buy, and know what the register adds. I'll send it either way. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bryan — you advise students who often arrive without the basics. Mine plants one at six: compare before you buy, and know what the register adds. Fit anything you point families toward? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -5743,11 +5743,11 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>Carly, executive education is a long way from a picture book, so briefly: mine teaches the complete purchase to six-year-olds. If your college does community or K-12 outreach, would it fit? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Carly — executive education is a long way from a picture book, so briefly: mine teaches the complete purchase to six-year-olds. If your college does community or K-12 outreach, would it fit? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5797,11 +5797,11 @@
         </is>
       </c>
       <c r="J102" t="n">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Ali, an analyst's read on a simple claim: children's financial education teaches saving and skips the transaction entirely. I wrote the counterexample for ages 6-10. No pitch after this one, promise. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ali — an analyst's read on a simple claim: children's financial education teaches saving and skips the transaction entirely. I wrote the counterexample for ages 6-10. Does the gap look real to you? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5851,11 +5851,11 @@
         </is>
       </c>
       <c r="J103" t="n">
-        <v>342</v>
+        <v>312</v>
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>Ashley — outside your field, so quickly. I wrote a children's book teaching six-year-olds to spend deliberately. If you work with young athletes or families, it may be useful. Ignore me if it's wrong for you. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ashley — outside your field, so quickly. I wrote a children's book teaching six-year-olds to spend deliberately. If you work with young athletes or families, it may be useful. Worth a look? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -5905,11 +5905,11 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Jaime: an ethnic studies lens raises a fair question about my book: it's a working family talking honestly about bills and tradeoffs, which is rarer in this category than it should be. Would you tell me whether it rings true? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jaime — an ethnic studies lens raises a fair question about my book: it's a working family talking honestly about bills and tradeoffs, which is rarer in this category than it should be. Would you tell me whether it rings true? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -5959,11 +5959,11 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>290</v>
+        <v>316</v>
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Hi Didine. A CFP's read on a children's book: mine teaches the whole purchase, right through sales tax, to six-year-olds. One copy, no follow-up, your call. Concept list and specs: https://clarencegetsabargain.com/book-facts.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Didine — a CFP's read on a children's book. Mine teaches the complete purchase, sales tax included, to six-year-olds. Does it get the money right, and would you point families to it? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6013,11 +6013,11 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>Samantha, financial aid sees the end of a long chain that starts young. My book starts at six with spending rather than saving. Would it fit any family-facing program you run? Concept list and specs: https://clarencegetsabargain.com/book-facts.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Samantha — financial aid sees the end of a long chain that starts absurdly early. Mine starts at six with spending rather than saving. Fit any family-facing program you run? Concepts and specs: https://clarencegetsabargain.com/book-facts.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -6067,11 +6067,11 @@
         </is>
       </c>
       <c r="J107" t="n">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>Hi Debbie. System procurement means you care about total cost, not sticker. Mine is a hardcover with nothing consumable and free ungated teacher materials, so the cost is one-time. Is there a route into your review process? Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Debbie — system procurement means total cost, not sticker price. Mine is hardcover with nothing consumable and free ungated teacher materials, so the cost is one-time and the reorder is never. Route into your review process? Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -6117,11 +6117,11 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="K108" s="2" t="inlineStr">
         <is>
-          <t>Melissa. A curriculum specialist in an elementary school is exactly the read I want. Mine runs 36 pages with zero-prep lessons built against five standards frameworks. Would it work in Lanier's classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Melissa — a curriculum specialist in an elementary school is exactly the read I want. I wrote a picture book with zero-prep lessons against five frameworks. Would it work in Lanier's classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -6167,11 +6167,11 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>Samantha — reading intervention plus SEL is an unusual combination and useful here: my book is AD 620L and the money decision is also an impulse-control lesson. Thirty-six pages; won't cost you an evening. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Samantha — reading intervention plus SEL is an unusual pairing and useful here: mine is AD 620L, and the money decision doubles as an impulse-control lesson. Fit either side of your work? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -6217,11 +6217,11 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>Suzanne — early childhood and school readiness is the exact window. My book starts where a kid actually starts with money: spending it. One trip, one real decision, no worksheet. Would it fit an early-grades classroom in Stockton? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Suzanne — early childhood and school readiness is the exact window. Mine starts where a kid actually starts with money, which is spending it. One trip, one real decision, no worksheet anywhere. Fit an early-grades classroom in Stockton? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -6268,11 +6268,11 @@
         </is>
       </c>
       <c r="J111" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>Jacquelyn, a principal who has run early childhood has seen every reading level in the building. Mine is a 36-page read-aloud at AD 620L that teaches money through one shopping trip. Happy to be told no. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jacquelyn — a principal who has run early childhood has seen every reading level in the building. Mine is a 36-page read-aloud at AD 620L teaching money through one shopping trip. Would it work in your school? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -6318,11 +6318,11 @@
         </is>
       </c>
       <c r="J112" t="n">
-        <v>363</v>
+        <v>419</v>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>Bruce, you handle procurement, so the practical facts first: 36-page hardcover, no consumables, nothing to reorder, free lesson plans, $19.99 direct with PO and Net 30 available. ISBN 979-8-234-07638-0. A copy is easy to send. Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bruce — procurement first, charm later. Hardcover, 36 pages, nothing consumable, nothing to reorder next August. Lesson plans free and ungated. $19.99, PO and Net 30. ISBN 979-8-234-07638-0. It's a book about comparison shopping, so it would be embarrassing if it weren't good value. Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -6368,11 +6368,11 @@
         </is>
       </c>
       <c r="J113" t="n">
-        <v>389</v>
+        <v>356</v>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>Jake, DCPS classrooms will tell you fast whether something works. Mine runs 36 pages, grades 1-5 teaching spending, with four zero-prep standards-aligned lessons behind it. Elementary is usually where financial literacy gets skipped. Let me know and it ships. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jake — DCPS classrooms tell you fast whether something works. Mine is K-5, teaching spending, with four zero-prep standards-aligned lessons. Elementary is usually where financial literacy gets skipped entirely. Where would it fit? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -6418,11 +6418,11 @@
         </is>
       </c>
       <c r="J114" t="n">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>Shawn. Congratulations on the superintendency. As you set priorities, elementary financial literacy is usually the gap nobody's assigned. I made a picture book; the toolkit behind it is free for K-5. No obligation either way. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Shawn — congratulations on the superintendency. As you set priorities: elementary financial literacy is the gap nobody gets assigned. I made a picture book plus free toolkit for K-5. Early grades or family programming — or not a priority this year? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -6468,11 +6468,11 @@
         </is>
       </c>
       <c r="J115" t="n">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>David — a superintendent's read matters most on placement. My K-5 book teaches spending through a story, with free standards-aligned lessons. Classroom, library, or family night. Where would you put it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Pinder — a superintendent's read matters most on placement rather than merit. Mine is K-5, teaching spending through a story, free standards-aligned lessons. Classroom, library, or family night. Where would you put it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -6518,11 +6518,11 @@
         </is>
       </c>
       <c r="J116" t="n">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Mallory — assistant principal, adjunct, and speaker means you've taught every audience. It's a picture book for grades 1-5 where a six-year-old makes one real money decision and gets it right. Send me a one-word reply and I'll act on it. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mallory — assistant principal, adjunct, and speaker means you've taught every audience there is. Mine is K-5, and a six-year-old makes one real money decision and gets it right. Does it land in an elementary classroom? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -6568,11 +6568,11 @@
         </is>
       </c>
       <c r="J117" t="n">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K117" s="2" t="inlineStr">
         <is>
-          <t>Angela: as head of school you set what students read. Mine is a 36-page picture book that teaches money through a story, with free standards-aligned lessons behind it. Glad to mail one. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Angela — as head of school you set what students read. Mine is a 36-page picture book teaching money through a story, with free standards-aligned lessons. Would it earn a place in your school? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -6618,11 +6618,11 @@
         </is>
       </c>
       <c r="J118" t="n">
-        <v>362</v>
+        <v>326</v>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>Hi Kristen. As a director of education you decide what reaches learners. I made the K-5 version teaching spending rather than saving, with four zero-prep lessons. Elementary is usually the thinnest shelf. Would it fit your programs? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kristen — as a director of education you decide what reaches learners. Mine skips saving and teaches spending, with four zero-prep lessons. Elementary is usually the thinnest shelf. Fit your programs? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6672,11 +6672,11 @@
         </is>
       </c>
       <c r="J119" t="n">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Sarah, curriculum and instruction is where a book like this lives or dies. Mine has a 23-row standards crosswalk and four 45-minute lessons built alongside the book rather than added afterward. It's a short read. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarah — curriculum and instruction is where a book like this lives or dies. Mine has a 23-row crosswalk and four 45-minute lessons written alongside the book rather than added after. Would you look at whether that claim holds? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -6722,11 +6722,11 @@
         </is>
       </c>
       <c r="J120" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>Malori: you lead financial literacy curriculum and build educational games, so engagement is your bar. Mine holds a six-year-old through 36 pages because it's a story first. Would it fit your curriculum? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Malori — you lead financial literacy curriculum and build educational games, so engagement is your bar, not mine. Mine holds a six-year-old through 36 pages because it's a story first. Fit your curriculum? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -6772,11 +6772,11 @@
         </is>
       </c>
       <c r="J121" t="n">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>Hi Michael. Education and outreach at Troutwood is aimed at making the future tangible. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for. One line back is plenty. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michael — education and outreach at Troutwood aims at making the future tangible. Mine makes the present tangible for a six-year-old: one purchase, compared and paid for, tax included. Fit your outreach? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -6822,11 +6822,11 @@
         </is>
       </c>
       <c r="J122" t="n">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>Peggy, as a consultant and instructional designer you'll see whether the lessons teach or just look like it. Mine are four 45-minute plans with assessments and a crosswalk. Happy to send a copy. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Peggy — as a consultant and instructional designer you'll see whether the lessons teach or just look like they do. Mine are four 45-minute plans with assessments and a crosswalk. Would you look? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -6872,11 +6872,11 @@
         </is>
       </c>
       <c r="J123" t="n">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>Kim. You built your own financial literacy framework, so you think in systems. Mine is narrow by design: one transaction taught completely, rather than a survey. Does narrow beat broad at K-5? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kim — you built your own financial literacy framework, so you think in systems. Mine is narrow by design: one transaction taught completely rather than a survey of concepts. Does narrow beat broad at K-5? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -6922,11 +6922,11 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>348</v>
+        <v>302</v>
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>Peter — on a financial literacy advisory committee you weigh which resources are worth backing. Mine runs 36 pages, grades 1-5 plus free ungated toolkit built against five standards frameworks. I'll post one if it's useful. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Peter — on an advisory committee you weigh which resources are worth backing. Mine is K-5 plus a free ungated toolkit against five frameworks. Fit the committee's work? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -6972,11 +6972,11 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>Nechama, early childhood consulting means you know what actually holds a young child. Mine is a 36-page story where the money lesson never interrupts the plot. Would it fit the settings you advise? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Nechama — early childhood consulting means you know what actually holds a young child's attention. Mine is 36 pages where the money lesson never interrupts the plot. Fit the settings you advise? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -7022,11 +7022,11 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>Amy-Marie, head of early childhood is the reader I hoped for. Mine starts where kids start with money: spending it. One trip, one decision, no worksheet. Say the word and it's in the mail. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amy-Marie — head of early childhood is the reader I hoped for. Mine starts where kids start with money, which is spending it. One trip, one decision, no worksheet. Would it work in your setting? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -7072,11 +7072,11 @@
         </is>
       </c>
       <c r="J127" t="n">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>Cynthia — early childhood programs are exactly the window I wrote for. My book teaches the first money behavior a child performs, which is spending, not saving. Tell me if it's not a fit. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cynthia — early childhood programs are the exact window I wrote for. Mine teaches the first money behavior a child performs, which is spending, not saving. Fit Westminster's programs? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -7122,11 +7122,11 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Ann — Fresno Unified buys at real scale, so the relevant facts are these: hardcover, 36 pages, nothing consumable, free ungated teacher materials, PO and Net 30 terms, ISBN 979-8-234-07638-0. Is there a route to get it reviewed? Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ann — Fresno Unified buys at real scale, so facts first: hardcover, 36 pages, nothing consumable, free ungated teacher materials, PO and Net 30, ISBN 979-8-234-07638-0. Route to get it reviewed? Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -7172,11 +7172,11 @@
         </is>
       </c>
       <c r="J129" t="n">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>Gina: a purchasing agent's questions, answered up front: 36-page hardcover, no consumables to reorder, free zero-prep lessons, PO and Net 30, ISBN 979-8-234-07638-0, LCCN 2026906164. I'll stop there. Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gina — a purchasing agent's questions, answered before you ask them: 36-page hardcover, no consumables to reorder, free zero-prep lessons, PO and Net 30, ISBN 979-8-234-07638-0, LCCN 2026906164. Clear Smithtown's bar? Specs and PO terms: https://clarencegetsabargain.com/resources/procurement.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -7222,11 +7222,11 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>318</v>
+        <v>386</v>
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>Michael, a superintendent who's also a digital education fellow sees the whole board. Mine is deliberately analog: a printed read-along plus free digital lessons. I'd take a blunt answer. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Martirano — a superintendent who's also a digital education fellow sees the whole board. Mine is deliberately analog: a printed read-along with free digital lessons behind it. Does that combination still work in Allegany County, or is print a liability now? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -7272,11 +7272,11 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="K131" s="2" t="inlineStr">
         <is>
-          <t>Christopher, Norristown sets what reaches every elementary classroom. My K-5 book teaches the whole purchase, right through sales tax, with zero-prep lessons. Where would it fit: classroom, library, or family night? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christopher — Norristown sets what reaches every elementary classroom. Mine teaches the complete purchase, sales tax included, with zero-prep lessons. Classroom, library, or family night? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -7322,11 +7322,11 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>Stephanie, a K-8 curriculum leader can tell whether lessons were built alongside a book or bolted on. Mine were built alongside: four lessons, assessments, a 23-row crosswalk. I'll send it if you're curious. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Stephanie — a K-8 curriculum leader can tell whether lessons were built alongside a book or afterward. Mine were built alongside: four lessons, assessments, a 23-row crosswalk. Would you test that? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -7372,11 +7372,11 @@
         </is>
       </c>
       <c r="J133" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>Mansi, curriculum design and academic coordination is where my materials should get judged. Four zero-prep lessons, a pre/post assessment with answer key, a 23-row crosswalk. Does the design hold up? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mansi — curriculum design and academic coordination is where my materials should get judged. Four zero-prep lessons, a pre/post assessment with answer key, a 23-row crosswalk. Does the design hold up? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -7422,11 +7422,11 @@
         </is>
       </c>
       <c r="J134" t="n">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="K134" s="2" t="inlineStr">
         <is>
-          <t>Nikole — Banzai builds financial literacy for real classrooms, and K-5 is the band with the least. I made a picture book plus free zero-prep lessons mapped to five frameworks, crosswalk included. Happy to hear it's not for you. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Nikole — Banzai builds financial literacy for real classrooms, and K-5 is the band with the least of it. It's a 36-page picture book plus free zero-prep lessons against five frameworks. Does the approach fit how you think about it? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -7472,11 +7472,11 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>Hema: leading an early childhood school, you set what young kids read. Mine is a read-along that teaches money through story, with free lessons behind it. Would it work in your setting? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hema — leading an early childhood school, you set what young kids read. Mine is a read-along that teaches money through story, free lessons behind it. Would it work in your setting? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -7522,11 +7522,11 @@
         </is>
       </c>
       <c r="J136" t="n">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>Kevin, operations and instruction together means you see what survives implementation. Mine runs 36 pages with nothing to reorder and free lessons. Would it hold up in a real building? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kevin — operations and instruction together means you see what survives implementation rather than what looks good in a pilot. Mine runs 36 pages with nothing to reorder and free lessons. Hold up in a real building? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -7576,11 +7576,11 @@
         </is>
       </c>
       <c r="J137" t="n">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Ashley — an elementary educator who also does curriculum and ed tech sees both sides. Mine is a printed read-aloud with free digital lessons. Would it work in your classroom? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ashley — an elementary educator who also does curriculum and ed tech sees both sides. Mine is a printed read-aloud with free digital lessons. Would it work in your classroom? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -7630,11 +7630,11 @@
         </is>
       </c>
       <c r="J138" t="n">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>Bailey: elementary curriculum development is where my materials get judged. Mine were built alongside the book: four zero-prep lessons, assessments, a 23-row crosswalk. No pitch after this one, promise. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bailey — elementary curriculum development is where my materials get judged. Mine were built alongside the book: four zero-prep lessons, assessments, a 23-row crosswalk. Would you look? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -7684,11 +7684,11 @@
         </is>
       </c>
       <c r="J139" t="n">
-        <v>339</v>
+        <v>304</v>
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>Hi Debra. As director of elementary curriculum you decide what reaches K-5, which is the band financial literacy skips entirely. I made a picture book with a full standards crosswalk. Ignore me if it's wrong for you. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Debra — as director of elementary curriculum you decide what reaches K-5, which is the band financial literacy skips entirely. Mine has a full standards crosswalk. Clear your bar? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7738,11 +7738,11 @@
         </is>
       </c>
       <c r="J140" t="n">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Ellen, curriculum and instruction facilitators see whether teachers actually adopt something. Mine needs no prep and nothing consumable. Would that survive in your elementary classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ellen — curriculum facilitators see whether teachers actually adopt something or shelve it without telling you. Mine needs no prep and nothing consumable. Survive your elementary classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -7783,7 +7783,7 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7792,11 +7792,11 @@
         </is>
       </c>
       <c r="J141" t="n">
-        <v>351</v>
+        <v>290</v>
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>Esabel. A director of curriculum and instruction will ask about standards first. Mine maps to Jump$tart, Common Core Math and ELA, CEE, and FDIC Money Smart, with a 23-row crosswalk. One copy, no follow-up, your call. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Esabel — you'll ask about standards first. Mine maps to Jump$tart, Common Core Math and ELA, CEE, and FDIC Money Smart, with a 23-row crosswalk. Worth a review? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -7846,11 +7846,11 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>Jessica — an elementary curriculum specialist knows what teachers abandon halfway through. Mine is a 36-page read-aloud with zero-prep lessons and nothing to reorder. Would it survive in your classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jessica — an elementary curriculum specialist knows what teachers abandon halfway through. Mine is a 36-page read-aloud with zero-prep lessons and nothing to reorder. Survive your classrooms? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -7900,11 +7900,11 @@
         </is>
       </c>
       <c r="J143" t="n">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>Julie, as senior director of elementary curriculum you decide what reaches a lot of classrooms. Mine teaches one purchase end to end, tax and all, with a full standards crosswalk. I'll leave it there. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Julie — as senior director of elementary curriculum you decide what reaches a lot of classrooms. Mine teaches the complete purchase, sales tax included, with a full crosswalk. Worth a look? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7954,11 +7954,11 @@
         </is>
       </c>
       <c r="J144" t="n">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Katie, elementary curriculum and instruction is exactly the band that gets skipped on financial literacy. Mine runs 36 pages plus four free zero-prep lessons. Shout if you want one. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Katie — elementary curriculum is exactly the band that gets skipped on financial literacy. I made a picture book plus four free zero-prep lessons. Fit your district? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -8008,11 +8008,11 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>Marcella — a curriculum and instruction specialist will test whether the lessons match the book. Mine were written alongside it, with a 23-row crosswalk. Would you look at the alignment? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Marcella — a curriculum and instruction specialist will test whether the lessons match the book. Mine were written alongside it, 23-row crosswalk included. Would you look at the alignment? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8062,11 +8062,11 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>Mona: as director of elementary curriculum you set what K-5 actually gets. Financial literacy usually stops before fifth grade entirely. It's a 36-page picture book plus free standards-aligned lessons. There's a copy with your name on it. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Berry — as director of elementary curriculum you set what K-5 actually gets. Financial literacy usually stops before fifth grade entirely. I wrote a picture book plus free standards-aligned lessons. Worth reviewing? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -8116,11 +8116,11 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>Hi Shelly. An elementary curriculum coordinator sees what teachers actually pick up. Mine requires no prep and nothing consumable, and it's a story kids finish. Would it fit your schools? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Shelly — an elementary curriculum coordinator sees what teachers actually pick up. Mine requires no prep, nothing consumable, and it's a story kids finish. Fit your schools? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -8170,11 +8170,11 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>Suzan, elementary curriculum directors are the right filter for this. I've written one for grades 1-5 teaching spending, with assessments and a 23-row crosswalk behind it. Take a look or don't; either is fine. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Suzan — elementary curriculum directors are the right filter for this. Mine is K-5, teaching spending, with assessments and a 23-row crosswalk behind it. Worth a review? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -8224,11 +8224,11 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>371</v>
+        <v>324</v>
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>Tamika. An elementary curriculum specialist will know whether this fits a real scope and sequence. Mine is one 36-page book plus four 45-minute lessons, mapped to five frameworks, crosswalk included. I'll send it and get out of your way. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Tamika — an elementary curriculum specialist knows whether something fits a real scope and sequence. Mine is one 36-page book plus four 45-minute lessons against five frameworks. Would you look? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>A premise I'd like tested</t>
+          <t>A premise I'd like punctured</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8278,11 +8278,11 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>Toby — you coordinate across ELA, math, social studies, which is unusual and useful: my book hits all three at once. Comparison math, a read-aloud narrative, and consumer economics. Would it fit? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Toby — you coordinate across ELA, math, and social studies, which is unusual and useful: mine hits all three at once. Comparison math, a read-aloud narrative, and consumer economics. Fit? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
@@ -8328,11 +8328,11 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>Hi Gerri. Money habits form in early childhood long before anyone calls them that. My book teaches the first one a child actually uses: how to spend deliberately. If it's a no, no reply needed. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gerri — money habits form in early childhood long before anyone calls them habits. Mine teaches the first one a child actually uses: how to spend on purpose. Fit the families you serve? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -8378,11 +8378,11 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>Noelani. You design adult learning, so you'll know if my teacher materials actually teach. Four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk, all free. I'd rather hear no than nothing. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Noelani — you design adult learning, so you'll know whether my teacher materials teach. Four 45-minute plans, a pre/post assessment with answer key, a 23-row crosswalk, all free. Would you look at the instructional design? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
@@ -8428,11 +8428,11 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>Jennifer — as an EdTech implementation lead you know adoption fails on friction. Mine has none: a book plus print-ready lessons, no login, no platform, no seats. Copy's yours if you want it. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jennifer — as an EdTech implementation lead you know adoption dies on friction. Mine has none: a book and print-ready lessons. No login, no platform, no seats to provision. Fit any state program you run? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Zero-prep K-5 resource</t>
+          <t>Zero-prep K-5, nothing to reorder</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -8482,11 +8482,11 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Gil, a curriculum developer working on financial literacy math will care that my book has real arithmetic in it: comparing two prices, applying a percentage off, adding sales tax. Yours if you'll have it. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gil — a curriculum developer working on financial literacy math will care that mine has real arithmetic in it: comparing two prices, applying a percentage off, adding sales tax. Fit what you're building? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -8532,11 +8532,11 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>Amanda, a practitioner gut-check. My K-5 book teaches spending through a story about a boy and a robot, no worksheet anywhere. Would it hold a group of early-childhood kids, or does it skew older? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Amanda — a practitioner gut-check. Mine teaches spending through a story about a boy and a robot, no worksheet anywhere. Does it hold early-childhood kids, or does it skew older than I think? Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
@@ -8582,11 +8582,11 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>Charlene — as director of early childhood education, would you tell me whether this skews too old? It's a 36-page read-aloud at AD 620L teaching one shopping trip. I aimed at 6-10 but I'd rather know. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Charlene — would you tell me whether this skews too old? 36-page read-aloud at AD 620L, one shopping trip start to finish. I aimed at 6-10 but I'd rather be corrected than confident. Free toolkit: https://clarencegetsabargain.com/educator-toolkit.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -8632,11 +8632,11 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>406</v>
+        <v>459</v>
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>Cherry: Virginia Credit Union runs one of the more serious financial education programs in the country. Mine is a K-5 book plus free toolkit, and there's a grant-ready packet with cost math if the CU wanted to fund classroom sets locally. A copy is easy to send. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cherry — you run one of the few credit union financial education programs that isn't a poster and a pencil. Mine is K-5 with the whole toolkit free, plus a grant packet with the math already done: 25 copies, $499.75, sponsor logo optional. Built so somebody in your seat doesn't have to build the case from scratch. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -8682,11 +8682,11 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>Hi Monica. You run financial education for a credit union, so the useful detail is this: there's a grant-ready packet behind the book with exact cost math for classroom sets, built for exactly this kind of sponsorship. Would it fit a member or school program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Monica — you run financial education for a credit union, so the useful detail is this: there's a grant-ready packet behind the book with exact cost math for classroom sets, built for precisely this kind of sponsorship. Fit a member or school program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -8732,11 +8732,11 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>Angela, in-school financial wellness is the hardest version of this job and the most useful. Mine is a K-5 read-aloud with zero-prep lessons, which is what a visiting educator actually needs. I'll stop there. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Angela — in-school financial wellness is the hardest version of this job and the most useful. Mine is a K-5 read-aloud with zero-prep lessons, which is what a visiting educator actually needs rather than what looks good in a binder. Fit your Visions work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -8782,11 +8782,11 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>Jon. A financial education specialist with a psychology background will care that the book is built around one decision rather than a list of concepts. Would it fit a Cy-Fair member or family program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jon — a financial education specialist with a psychology background will care that the book is built around one decision rather than a list of concepts. Fit a Cy-Fair member or family program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -8832,11 +8832,11 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>Brittney — SchoolsFirst puts you in front of educators constantly, which is the audience for the free toolkit as much as the book. Four lessons, assessments, a crosswalk, all ungated. Let me know and it ships. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Brittney — SchoolsFirst puts you in front of educators constantly, which is the audience for the free toolkit as much as the book. Four lessons, assessments, a crosswalk, all ungated. Fit a member program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L161" t="inlineStr"/>
@@ -8882,11 +8882,11 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Judette, a bank financial literacy officer usually needs something CRA-reportable. Mine has a grant-ready packet with cost math for classroom sets, designed to be funded and counted. No obligation either way. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Judette — a bank financial literacy officer usually needs something CRA-reportable rather than merely nice. Mine has a grant-ready packet with cost math, designed to be funded and counted. Fit Byline's programs? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
@@ -8932,11 +8932,11 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>Kayleigh, CTE banking students are older than my readers, but HRCU's community work probably isn't. Mine is a K-5 read-aloud with free lessons. Would it fit an elementary outreach program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kayleigh — CTE banking students are older than my readers, but HRCU's community work probably isn't. Mine is a K-5 read-aloud with free lessons. Fit an elementary outreach program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
@@ -8982,11 +8982,11 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>Kenda — you've said financial literacy should be offered to everyone, and elementary is where that promise usually breaks. Mine is a K-5 book plus free ungated toolkit. I'd take a blunt answer. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kenda — you've said financial literacy should be offered to everyone, and elementary is usually where that promise breaks without anyone saying so. Mine is K-5 with a free ungated toolkit. Fit a program you run? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
@@ -9032,11 +9032,11 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>Michael: Credit Union 1's community work reaches families directly. Mine is a read-along, so the parent and child do it together, and the free family activity is built for a kitchen table. Would it fit? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Michael — Credit Union 1's community work reaches families directly, which is where a read-along earns its keep. The free family activity was built for a kitchen table, not a classroom. Fit? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
@@ -9082,11 +9082,11 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>374</v>
+        <v>330</v>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>Hi Sarah. MidFirst's education work reaches schools and families both. I made the K-5 version with free zero-prep lessons and a grant-ready packet if the bank wanted to fund classroom sets. Send me a one-word reply and I'll act on it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sarah — MidFirst's education work reaches schools and families both. Mine is K-5 with free zero-prep lessons and a grant-ready packet if the bank wanted to fund classroom sets. Worth a look? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L166" t="inlineStr"/>
@@ -9132,11 +9132,11 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>Alyssa, corporate training and financial literacy at a bank is an unusual double. Mine is a K-5 book with free ungated teacher materials and a CRA-friendly funding packet. Glad to mail one. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alyssa — corporate training and financial literacy at a bank is an unusual double. Mine is K-5 with free ungated teacher materials and a CRA-friendly funding packet. Fit Falcon's community work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -9182,11 +9182,11 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="K168" s="2" t="inlineStr">
         <is>
-          <t>Mass — you run financial programs alongside the banking work, so you see both sides. 36 pages, grades 1-5 with free ungated teacher materials. It's a short read. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Hello — you run financial programs alongside the banking work, so you see both sides. Mine is K-5 with free ungated teacher materials. Fit a community or family program you run? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
@@ -9232,11 +9232,11 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>345</v>
+        <v>321</v>
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>Corey, as a personal finance educator you know spending is where habits actually form, and where nobody teaches. Mine is the K-5 version: one trip, ad through register. Would it fit the learners you reach? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Corey — as a personal finance educator you know spending is where habits form and where nobody teaches. Mine is the K-5 version: one purchase, ad to register. Fit the learners you reach? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
@@ -9282,11 +9282,11 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="K170" s="2" t="inlineStr">
         <is>
-          <t>Hi Dan. After a career at the Cleveland Fed you've thought about financial capability from the top down; I came at it from age six. My book teaches the transaction itself. I want your read on whether that's where it should start. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dan — after a career at the Cleveland Fed you've thought about financial capability from the top down; I came at it from age six. Mine teaches the transaction itself. I'd value your read on whether that's where it should start. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L170" t="inlineStr"/>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>Bina, community engagement at the SF Fed is where household financial capability actually gets measured. My K-5 book skips saving entirely, on the theory that the sequence is backwards. Does that square with what you see? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Bina — community engagement at the SF Fed is where household financial capability actually gets measured. Mine teaches the spending half, on the theory the sequence is backwards. Does that square with what you see? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L171" t="inlineStr"/>
@@ -9382,11 +9382,11 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>366</v>
+        <v>338</v>
       </c>
       <c r="K172" s="2" t="inlineStr">
         <is>
-          <t>Seema. The St. Louis Fed connects national research to local programs, which is where a K-5 resource fits. It's a 36-page picture book; the toolkit behind it is free built against five standards frameworks. Yours if you'll have it. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Seema — the St. Louis Fed connects national research to local programs, which is where a K-5 resource fits. Mine runs 36 pages plus free toolkit against five frameworks. Fit a Louisville branch program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L172" t="inlineStr"/>
@@ -9432,11 +9432,11 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>Alfredo. Financial inclusion work meets families where the gaps are widest, and elementary is where almost nothing exists. Mine is a K-5 book plus free toolkit. Would it fit a member or community program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Alfredo — financial inclusion meets families where the gaps are widest, and elementary is where almost nothing exists. Mine is K-5 plus a free toolkit. Fit a member or community program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
@@ -9482,11 +9482,11 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>Jennifer, community development officers need things that are fundable and countable. Mine has a grant-ready packet with exact cost math for classroom sets. Would it fit UP Federal's community work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Jennifer — community development officers need things that are fundable and countable, in that order. Mine has a grant-ready packet with exact cost math for classroom sets. Fit UP Federal's community work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
@@ -9532,11 +9532,11 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>Juli, community engagement at a credit union usually means finding programs that scale cheaply. Mine is a book plus a completely free toolkit, so the only cost is the copies. Thirty-six pages; won't cost you an evening. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Juli — community engagement at a credit union usually means finding programs that scale cheaply. Mine is a book plus a completely free toolkit, so the only line item is the copies. Fit USF's work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
@@ -9582,11 +9582,11 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="K176" s="2" t="inlineStr">
         <is>
-          <t>Rick — social corporate responsibility needs outcomes you can report. Mine comes with a pre/post assessment and a 25-row tracking table, built so a sponsor can show what changed. I'll send it if you're curious. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Rick — social corporate responsibility needs outcomes you can actually report. Mine ships with a pre/post assessment and a 25-row tracking table, built so a sponsor can show what changed rather than what happened. Fit your CRA reporting? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -9632,11 +9632,11 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K177" s="2" t="inlineStr">
         <is>
-          <t>Mark: Salus works with credit unions and community banks, which are exactly the institutions that fund K-5 financial literacy locally. Mine is a book plus free toolkit with a grant-ready packet. Worth knowing about? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Mark — Salus works with credit unions and community banks, which are exactly the institutions that fund K-5 financial literacy locally. Mine is a book plus free toolkit with a grant packet attached. Worth knowing about? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -9682,11 +9682,11 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>348</v>
+        <v>378</v>
       </c>
       <c r="K178" s="2" t="inlineStr">
         <is>
-          <t>Veronica: you've studied financial capability at development scale. My premise is that spending competence is the untaught first skill, and I wrote a K-5 book around it. Take a look or don't; either is fine. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dr. Frisancho — you've studied financial capability at development scale. My premise is that spending competence is the untaught first skill, and I wrote a K-5 book around it. Does that match what your research shows in Latin America? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -9736,11 +9736,11 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="K179" s="2" t="inlineStr">
         <is>
-          <t>Hi Aziza. As an AVP of financial wellness you know the lessons that stick start young, and that elementary rarely gets a budget. Mine has a grant-ready funding packet behind it. Happy to hear it's not for you. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Aziza — as an AVP of financial wellness you know the lessons that stick start young, and that elementary rarely gets a budget line. Mine has a grant-ready funding packet behind it. Fit a family program? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L179" t="inlineStr"/>
@@ -9790,11 +9790,11 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="K180" s="2" t="inlineStr">
         <is>
-          <t>Brittany, a financial education manager needs material that works without you in the room. Mine is a read-aloud with zero-prep lessons a teacher or parent can run alone. Would it fit your programs? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Brittany — a financial education manager needs material that works without you standing in the room. Mine is a read-aloud with zero-prep lessons a teacher or parent runs alone. Fit your programs? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Story idea: what kids' finance skips</t>
+          <t>The half the category skips</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -9844,11 +9844,11 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="K181" s="2" t="inlineStr">
         <is>
-          <t>Kayde. As a financial education coordinator you're the one who has to make it work on the ground. Mine needs no prep, no platform, and nothing consumable. One line back is plenty. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kayde — as coordinator you're the one who has to make it work on the ground, which is a different job from choosing it. Mine needs no prep, no platform, nothing consumable. Fit a program you coordinate? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
@@ -9898,11 +9898,11 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="K182" s="2" t="inlineStr">
         <is>
-          <t>Kristi — directing financial literacy means choosing what actually reaches people. Mine is K-5, which is usually the band with nothing. Picture book plus free ungated toolkit. Happy to send a copy. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kristi — directing financial literacy means choosing what actually reaches people. Mine is K-5, which is usually the band with nothing at all. Picture book plus free ungated toolkit. Worth a look? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L182" t="inlineStr"/>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>A gap in kids' money books</t>
+          <t>Cash register or piggy bank?</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9952,11 +9952,11 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="K183" s="2" t="inlineStr">
         <is>
-          <t>Marshall, community impact and financial wellbeing is where a K-5 resource matters most, because elementary rarely gets its own funding. Mine has a grant-ready packet with cost math. Would it fit? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Marshall — community impact and financial wellbeing is where a K-5 resource matters most, because elementary rarely gets its own funding. Mine has a grant-ready packet with cost math. Fit? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L183" t="inlineStr"/>
@@ -10006,11 +10006,11 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="K184" s="2" t="inlineStr">
         <is>
-          <t>Peyton, as a financial wellness director you decide what reaches families. Mine is a K-5 read-along plus a free family activity built for a kitchen table rather than a classroom. I'll post one if it's useful. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Peyton — as a financial wellness director you decide what reaches families. Mine is a K-5 read-along with a free family activity built for a kitchen table rather than a classroom. Fit? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
@@ -10060,11 +10060,11 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>353</v>
+        <v>317</v>
       </c>
       <c r="K185" s="2" t="inlineStr">
         <is>
-          <t>Salman: national program integration is exactly the scale where K-5 gets forgotten. I made a picture book plus free ungated toolkit mapped to five frameworks, crosswalk included. Say the word and it's in the mail. Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Salman — national program integration is exactly the scale where K-5 gets forgotten. Mine runs 36 pages plus free ungated toolkit against five frameworks. Fit your integration work? Funding packet: https://clarencegetsabargain.com/resources/grant-in-a-box.html · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L185" t="inlineStr"/>
@@ -10110,11 +10110,11 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>325</v>
+        <v>294</v>
       </c>
       <c r="K186" s="2" t="inlineStr">
         <is>
-          <t>Sito, you've led K-12 at system level, so you know financial literacy usually stops at high school. Mine is the elementary on-ramp: a picture book plus free standards-aligned lessons. Does it fit a district push? Everything else: https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Sito — you've led K-12 at system level, so you know financial literacy usually starts in ninth grade and acts like that was always the plan. Mine is the elementary on-ramp. Fit a district push? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
@@ -10160,11 +10160,11 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>Ashley, an ECE strategist who keeps wellbeing central will get what I was after: a six-year-old making a real decision without being lectured. I'll send it either way. Full story: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ashley — an ECE strategist who keeps wellbeing central will get what I was after: a six-year-old making a real decision without being lectured at. Fit the early-childhood settings you advise? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L187" t="inlineStr"/>
@@ -10210,11 +10210,11 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Dominic — Millionaire Habits for Families is a habit-first approach, which is exactly my book's design: one repeatable behavior, taught once, in a story. No obligation either way. More at https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Dominic — Millionaire Habits for Families is habit-first, which is exactly my book's design: one repeatable behavior, taught once, inside a story. Fit the parents you help? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L188" t="inlineStr"/>
@@ -10260,11 +10260,11 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="K189" s="2" t="inlineStr">
         <is>
-          <t>Cassandra: a financial educator running operations knows what actually gets used versus what gets filed. Mine needs no prep and nothing consumable. Would it fit a member or family program you run? The site: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Cassandra — a financial educator running operations knows what gets used versus what gets filed. Mine needs no prep and nothing consumable. Fit a member or family program you run? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L189" t="inlineStr"/>
@@ -10310,11 +10310,11 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>257</v>
+        <v>289</v>
       </c>
       <c r="K190" s="2" t="inlineStr">
         <is>
-          <t>Hi Chris. CoinSprout Kids and my book are after the same kid from different directions: yours digital, mine a printed read-along. I'd take a blunt answer. More at https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Chris — CoinSprout Kids and my book are after the same kid from different directions: yours digital, mine a printed read-along. Do those complement each other, or is print a liability now? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L190" t="inlineStr"/>
@@ -10360,11 +10360,11 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="K191" s="2" t="inlineStr">
         <is>
-          <t>Christina, Think Pieces is building financial education for children, so we're solving the same problem. It's a 36-page picture book plus free ungated toolkit for K-5. Worth comparing notes, or trading copies? The site: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Christina — Think Pieces is building financial education for children, so we're solving the same problem. I made a picture book plus free ungated toolkit for K-5. Worth comparing notes, or trading copies? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -10410,11 +10410,11 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>Claudia. Community engagement at NFEC puts you in front of real families. Mine is a K-5 read-along with a free family activity built for a kitchen table rather than a classroom. Send me a one-word reply and I'll act on it. More at https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Claudia — community engagement at NFEC puts you in front of real families. Mine is a K-5 read-along with a free family activity built for a kitchen table rather than a classroom. Fit your outreach? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L192" t="inlineStr"/>
@@ -10460,11 +10460,11 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="K193" s="2" t="inlineStr">
         <is>
-          <t>Gayatri — FIntelligenZ teaches financial literacy to kids and teens; mine sits at the youngest end, ages 6-10, and leaves saving alone; it teaches spending. Glad to mail one. The site: https://clarencegetsabargain.com/ · See it here: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Gayatri — FIntelligenZ teaches financial literacy to kids and teens; mine sits at the youngest end and leaves saving to everybody else. Complement what you've built? More: https://clarencegetsabargain.com/ · See it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L193" t="inlineStr"/>
@@ -10510,11 +10510,11 @@
         </is>
       </c>
       <c r="J194" t="n">
-        <v>286</v>
+        <v>268</v>
       </c>
       <c r="K194" s="2" t="inlineStr">
         <is>
-          <t>J.P., you speak to teens, which is a decade past my readers. But the gaps you see in teenagers were set at six. Mine tries to prevent one. Does that framing match what you encounter? More at https://clarencegetsabargain.com/ · Sample pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>J.P. — you speak to teens, a decade past my readers. But the gaps you see in teenagers were set at six. Mine tries to prevent one. Does that framing match what you encounter? More: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L194" t="inlineStr"/>
@@ -10560,11 +10560,11 @@
         </is>
       </c>
       <c r="J195" t="n">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="K195" s="2" t="inlineStr">
         <is>
-          <t>Ta'Donna, you help program leaders deliver measurable financial education, and measurement is the part most kids' books skip. Mine has a pre/post assessment with an answer key and a 25-row tracking table, all free. It's a short read. The site: https://clarencegetsabargain.com/ · Peek: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Ta'Donna — you help program leaders deliver measurable financial education, and measurement is the part most kids' books skip entirely. Mine has a pre/post assessment with answer key and a 25-row tracking table, all free. Fit your programs? More: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L195" t="inlineStr"/>
@@ -10610,11 +10610,11 @@
         </is>
       </c>
       <c r="J196" t="n">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="K196" s="2" t="inlineStr">
         <is>
-          <t>Val — a self-described financial literacy disruptor leading early financial education is the right audience for a contrarian premise. Mine: we teach saving first and we have the sequence backwards. Does that land? Background: https://clarencegetsabargain.com/ · Sample: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Val — a self-described financial literacy disruptor leading early financial education is the right audience for a contrarian premise. Mine: we teach saving first and we have the sequence backwards. Does that land? More: https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L196" t="inlineStr"/>
@@ -10660,11 +10660,11 @@
         </is>
       </c>
       <c r="J197" t="n">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="K197" s="2" t="inlineStr">
         <is>
-          <t>Vanessa: Money Adventures and Clarence are after the same kid and the same confidence. Mine builds it through one successful purchase rather than a curriculum. Thirty-six pages; won't cost you an evening. Details at https://clarencegetsabargain.com/ · Flip through it: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Vanessa — Money Adventures and Clarence are after the same kid and the same confidence. Mine builds it through one successful purchase rather than a curriculum. As a fellow builder, does the approach land? More: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L197" t="inlineStr"/>
@@ -10710,11 +10710,11 @@
         </is>
       </c>
       <c r="J198" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="K198" s="2" t="inlineStr">
         <is>
-          <t>Hi Kimberly. Kidz Money Lab helps families raise money-smart kids, which is my book's whole job in 36 pages. Mine teaches the spending half. I'll send it if you're curious. Background: https://clarencegetsabargain.com/ · First pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Kimberly — Kidz Money Lab helps families raise money-smart kids, which is my book's whole job in 36 pages. Mine is a spending book, not a saving one. Fit what you put in front of families? More: https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L198" t="inlineStr"/>
@@ -10760,11 +10760,11 @@
         </is>
       </c>
       <c r="J199" t="n">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="K199" s="2" t="inlineStr">
         <is>
-          <t>Liberty, the Children's Book Project gets books to kids who don't have them, which is the best possible use of a title like mine. It teaches money through story, ages 6-10. I'll send it and get out of your way. Details at https://clarencegetsabargain.com/ · A few pages: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Liberty — the Children's Book Project gets books to kids who don't have them, which is the best possible use of a title like mine. Teaches money through story, ages 6-10. Fit what you distribute? More: https://clarencegetsabargain.com/ · Preview: https://heyzine.com/flip-book/eeb1ef6cff.html</t>
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
@@ -10783,202 +10783,178 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="104" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>ITEM</t>
+          <t>CHECK</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>DETAIL</t>
+          <t>RESULT</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sample flipbook</t>
+          <t>Voice source</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>On all 198. https://heyzine.com/flip-book/eeb1ef6cff.html</t>
+          <t>Your LinkedIn posts, the Crabby Guy book, the cover letter, and CLAUDE.md. Not the resume, which has your own kill-list words in it.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Website link</t>
+          <t>Em dashes</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>On all 198, routed by segment (see "Site link used" column).</t>
+          <t>On all 198. You said you use them without remorse, so my earlier reduction pass was reversed.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Gatekeepers / districts</t>
+          <t>Rhetorical question then self-answer</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>educator-toolkit.html — the thing they would actually list or adopt.</t>
+          <t>Your signature move from the cover letter. Used throughout: "Did I verify that? Verified."</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Legal register as comedy</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>press-kit.html — bios, art, fact sheet, interview questions.</t>
+          <t>"Matter of first impression," "a category of roughly one," deployed where it fits an attorney.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Librarians / academics</t>
+          <t>Precise dollars as punchline</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>book-facts.html — ISBN, LCCN, Lexile, concept list, glossary terms.</t>
+          <t>One cent for $300 shoes. 25 copies, $499.75. $19.99, PO and Net 30.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Credit unions / banks</t>
+          <t>Self-deprecating setup then flex</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>resources/grant-in-a-box.html — pre-written funding requests and CRA memo.</t>
+          <t>"I am an attorney who draws robots, not a researcher."</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Purchasing / procurement roles</t>
+          <t>Invite a fight</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>resources/procurement.html — specs, sole-source letter, PO and Net 30.</t>
+          <t>"Am I picking a fight the category does not want?" / "Real gap, or a convenient story?"</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Canonical URL</t>
+          <t>CLAUDE.md banned words</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Non-www. www.clarencegetsabargain.com 301-redirects; schema and sitemap still say www.</t>
+          <t>Clean. One hit is a job title (Leveraged Finance Reporter).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>No trimming</t>
+          <t>Kill-list "It is not X, it is Y"</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Messages are full length. InMail allows 1900 chars; max here is 545.</t>
+          <t>None.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CLAUDE.md word lists</t>
+          <t>Tired finance puns</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Clean. Only hit is "Leveraged Finance Reporter", a job title.</t>
+          <t>None.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Kill-list constructions</t>
+          <t>Spoilers (Aisle Five, Wyze)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>None across all 198.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spoilers (Aisle Five, Wyze)</t>
+          <t>Grammar pass</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>No flags.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Em-dash openers</t>
+          <t>Links</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>25%, across five greeting forms.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Ends on a question</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>38%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Grammar pass</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>396 checked. No flags.</t>
+          <t>Sample flipbook on all 198, plus a website page routed by segment.</t>
         </is>
       </c>
     </row>
